--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8068</v>
+        <v>8.4476</v>
       </c>
       <c r="C2" t="n">
-        <v>2.73238</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.721838724031263</v>
+        <v>2.9913</v>
       </c>
       <c r="E2" t="n">
-        <v>84.66549999999999</v>
+        <v>8.4476</v>
       </c>
       <c r="F2" t="n">
-        <v>40.61527708019392</v>
+        <v>4.2542</v>
       </c>
       <c r="G2" t="n">
-        <v>44.05022824796092</v>
+        <v>4.1934</v>
       </c>
       <c r="H2" t="n">
-        <v>71.72119184544866</v>
+        <v>4.5552</v>
       </c>
       <c r="I2" t="n">
-        <v>46.55111319780063</v>
+        <v>3.6921</v>
       </c>
       <c r="J2" t="n">
-        <v>44.05022824796092</v>
+        <v>4.1934</v>
       </c>
       <c r="K2" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="L2" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M2" t="n">
-        <v>90.60129999999999</v>
+        <v>7.8855</v>
       </c>
       <c r="N2" t="n">
-        <v>184</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4384</v>
+        <v>7.9685</v>
       </c>
       <c r="C3" t="n">
-        <v>2.60344</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.490862592084085</v>
+        <v>2.7977</v>
       </c>
       <c r="E3" t="n">
-        <v>77.4808</v>
+        <v>7.9685</v>
       </c>
       <c r="F3" t="n">
-        <v>26.50065115937733</v>
+        <v>4.5038</v>
       </c>
       <c r="G3" t="n">
-        <v>50.9801114588616</v>
+        <v>3.4647</v>
       </c>
       <c r="H3" t="n">
-        <v>30.28278923106507</v>
+        <v>5.5593</v>
       </c>
       <c r="I3" t="n">
-        <v>25.82607685366305</v>
+        <v>4.506</v>
       </c>
       <c r="J3" t="n">
-        <v>50.9801114588616</v>
+        <v>3.4647</v>
       </c>
       <c r="K3" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M3" t="n">
-        <v>76.8062</v>
+        <v>7.970700000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0801</v>
+        <v>5.9462</v>
       </c>
       <c r="C4" t="n">
-        <v>2.128035</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.756416233941158</v>
+        <v>1.9808</v>
       </c>
       <c r="E4" t="n">
-        <v>54.6351</v>
+        <v>5.9462</v>
       </c>
       <c r="F4" t="n">
-        <v>20.38674475185807</v>
+        <v>3.4836</v>
       </c>
       <c r="G4" t="n">
-        <v>34.24833215415138</v>
+        <v>2.4626</v>
       </c>
       <c r="H4" t="n">
-        <v>20.84481328194477</v>
+        <v>3.4836</v>
       </c>
       <c r="I4" t="n">
-        <v>17.7770860442246</v>
+        <v>2.8235</v>
       </c>
       <c r="J4" t="n">
-        <v>34.24833215415138</v>
+        <v>2.4626</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -633,7 +621,7 @@
         <v>106</v>
       </c>
       <c r="M4" t="n">
-        <v>52.0254</v>
+        <v>5.2861</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -642,722 +630,722 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8865</v>
+        <v>5.2624</v>
       </c>
       <c r="C5" t="n">
-        <v>2.060275</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.665158567008348</v>
+        <v>1.7045</v>
       </c>
       <c r="E5" t="n">
-        <v>51.7964</v>
+        <v>5.2624</v>
       </c>
       <c r="F5" t="n">
-        <v>35.6042042679681</v>
+        <v>2.3149</v>
       </c>
       <c r="G5" t="n">
-        <v>16.19221198643176</v>
+        <v>2.9475</v>
       </c>
       <c r="H5" t="n">
-        <v>52.80889425513562</v>
+        <v>2.3149</v>
       </c>
       <c r="I5" t="n">
-        <v>45.03701925154962</v>
+        <v>1.8763</v>
       </c>
       <c r="J5" t="n">
-        <v>16.19221198643176</v>
+        <v>2.9475</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M5" t="n">
-        <v>61.2292</v>
+        <v>4.8238</v>
       </c>
       <c r="N5" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7005</v>
+        <v>5.1224</v>
       </c>
       <c r="C6" t="n">
-        <v>1.645175</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.168436882655367</v>
+        <v>1.648</v>
       </c>
       <c r="E6" t="n">
-        <v>36.3454</v>
+        <v>5.1224</v>
       </c>
       <c r="F6" t="n">
-        <v>14.69223856668522</v>
+        <v>4.515</v>
       </c>
       <c r="G6" t="n">
-        <v>21.65315480311471</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>14.69223856668522</v>
+        <v>5.6043</v>
       </c>
       <c r="I6" t="n">
-        <v>9.536094465923995</v>
+        <v>4.5424</v>
       </c>
       <c r="J6" t="n">
-        <v>21.65315480311471</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="L6" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>31.1892</v>
+        <v>5.1498</v>
       </c>
       <c r="N6" t="n">
-        <v>184</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.77</v>
+        <v>3.5063</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9694999999999999</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5499982947809381</v>
+        <v>0.9951</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1082</v>
+        <v>3.5063</v>
       </c>
       <c r="F7" t="n">
-        <v>17.10824493241236</v>
+        <v>4.2838</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.7775</v>
       </c>
       <c r="H7" t="n">
-        <v>17.0616721640149</v>
+        <v>4.6741</v>
       </c>
       <c r="I7" t="n">
-        <v>21.89044730477384</v>
+        <v>3.7885</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.7775</v>
       </c>
       <c r="K7" t="n">
         <v>170</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>21.8904</v>
+        <v>3.011</v>
       </c>
       <c r="N7" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5688</v>
+        <v>3.2809</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8990799999999999</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4967070203821425</v>
+        <v>0.904</v>
       </c>
       <c r="E8" t="n">
-        <v>15.4506</v>
+        <v>3.2809</v>
       </c>
       <c r="F8" t="n">
-        <v>15.45056674717703</v>
+        <v>4.2124</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.9315</v>
       </c>
       <c r="H8" t="n">
-        <v>15.41858412765441</v>
+        <v>4.3871</v>
       </c>
       <c r="I8" t="n">
-        <v>18.73503429850837</v>
+        <v>3.5559</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.9315</v>
       </c>
       <c r="K8" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>18.735</v>
+        <v>2.6244</v>
       </c>
       <c r="N8" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2106</v>
+        <v>3.2514</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7737099999999999</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4063054197724232</v>
+        <v>0.8921</v>
       </c>
       <c r="E9" t="n">
-        <v>12.6385</v>
+        <v>3.2514</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.22741844686934</v>
+        <v>2.9632</v>
       </c>
       <c r="G9" t="n">
-        <v>28.86595333833088</v>
+        <v>0.2882</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.16790887957647</v>
+        <v>2.9632</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.78848078031804</v>
+        <v>2.4017</v>
       </c>
       <c r="J9" t="n">
-        <v>28.86595333833088</v>
+        <v>0.2882</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="L9" t="n">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>15.0775</v>
+        <v>2.6899</v>
       </c>
       <c r="N9" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0953</v>
+        <v>3.1165</v>
       </c>
       <c r="C10" t="n">
-        <v>0.733355</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3783873987557731</v>
+        <v>0.8376</v>
       </c>
       <c r="E10" t="n">
-        <v>11.7701</v>
+        <v>3.1165</v>
       </c>
       <c r="F10" t="n">
-        <v>11.77011703250923</v>
+        <v>3.0282</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0883</v>
       </c>
       <c r="H10" t="n">
-        <v>11.77011703250923</v>
+        <v>3.0282</v>
       </c>
       <c r="I10" t="n">
-        <v>15.1012822303892</v>
+        <v>2.4544</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0883</v>
       </c>
       <c r="K10" t="n">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M10" t="n">
-        <v>15.1013</v>
+        <v>2.5427</v>
       </c>
       <c r="N10" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7042</v>
+        <v>2.9205</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5964699999999999</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2877632370694364</v>
+        <v>0.7585</v>
       </c>
       <c r="E11" t="n">
-        <v>8.9512</v>
+        <v>2.9205</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.699652603742026</v>
+        <v>2.9205</v>
       </c>
       <c r="G11" t="n">
-        <v>18.65081479650595</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.699652603742026</v>
+        <v>2.9205</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.272156560172444</v>
+        <v>2.9205</v>
       </c>
       <c r="J11" t="n">
-        <v>18.65081479650595</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="L11" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>10.3787</v>
+        <v>2.9205</v>
       </c>
       <c r="N11" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6221</v>
+        <v>2.8023</v>
       </c>
       <c r="C12" t="n">
-        <v>0.567735</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2695070365386125</v>
+        <v>0.7107</v>
       </c>
       <c r="E12" t="n">
-        <v>8.3833</v>
+        <v>2.8023</v>
       </c>
       <c r="F12" t="n">
-        <v>9.582380473607353</v>
+        <v>2.8574</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.199095587337573</v>
+        <v>-0.0551</v>
       </c>
       <c r="H12" t="n">
-        <v>9.582380473607353</v>
+        <v>2.8574</v>
       </c>
       <c r="I12" t="n">
-        <v>11.93277568411482</v>
+        <v>2.316</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.199095587337573</v>
+        <v>-0.0551</v>
       </c>
       <c r="K12" t="n">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M12" t="n">
-        <v>10.7337</v>
+        <v>2.2609</v>
       </c>
       <c r="N12" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7388</v>
+        <v>2.0848</v>
       </c>
       <c r="C13" t="n">
-        <v>0.25858</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08872912643504487</v>
+        <v>0.4209</v>
       </c>
       <c r="E13" t="n">
-        <v>2.76</v>
+        <v>2.0848</v>
       </c>
       <c r="F13" t="n">
-        <v>20.15323346625561</v>
+        <v>3.0848</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.39322558605965</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>20.54958758853547</v>
+        <v>3.0848</v>
       </c>
       <c r="I13" t="n">
-        <v>13.33784552916265</v>
+        <v>2.5003</v>
       </c>
       <c r="J13" t="n">
-        <v>-17.39322558605965</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.0554</v>
+        <v>1.5003</v>
       </c>
       <c r="N13" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6942</v>
+        <v>2.0835</v>
       </c>
       <c r="C14" t="n">
-        <v>0.24297</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08030527504186058</v>
+        <v>0.4203</v>
       </c>
       <c r="E14" t="n">
-        <v>2.498</v>
+        <v>2.0835</v>
       </c>
       <c r="F14" t="n">
-        <v>18.37620886671182</v>
+        <v>2.0835</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.8782332769364</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>18.4357084518353</v>
+        <v>2.0835</v>
       </c>
       <c r="I14" t="n">
-        <v>22.95767467587037</v>
+        <v>2.0835</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.8782332769364</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.0794</v>
+        <v>2.0835</v>
       </c>
       <c r="N14" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6121</v>
+        <v>1.8016</v>
       </c>
       <c r="C15" t="n">
-        <v>0.214235</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06499582906730596</v>
+        <v>0.3064</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0218</v>
+        <v>1.8016</v>
       </c>
       <c r="F15" t="n">
-        <v>16.95950510410855</v>
+        <v>1.8016</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.93774508444964</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>16.9073531595452</v>
+        <v>1.8016</v>
       </c>
       <c r="I15" t="n">
-        <v>21.69245311035988</v>
+        <v>1.8016</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.93774508444964</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6.7547</v>
+        <v>1.8016</v>
       </c>
       <c r="N15" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3179</v>
+        <v>1.7698</v>
       </c>
       <c r="C16" t="n">
-        <v>0.111265</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01188487305654489</v>
+        <v>0.2936</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3697</v>
+        <v>1.7698</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3696908175378681</v>
+        <v>-0.1795</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.9493</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3696908175378681</v>
+        <v>-0.1795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4492092198007303</v>
+        <v>-0.1455</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.9493</v>
       </c>
       <c r="K16" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4492</v>
+        <v>1.8038</v>
       </c>
       <c r="N16" t="n">
-        <v>161</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2993</v>
+        <v>1.6265</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.104755</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1002397466708035</v>
+        <v>0.2357</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.1181</v>
+        <v>1.6265</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.11805719086842</v>
+        <v>1.3515</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.11805719086842</v>
+        <v>1.3515</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.788733643243892</v>
+        <v>1.0954</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="K17" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7887</v>
+        <v>1.3704</v>
       </c>
       <c r="N17" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.342</v>
+        <v>1.5564</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1197</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1084415998859327</v>
+        <v>0.2074</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3732</v>
+        <v>1.5564</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.373184006779753</v>
+        <v>1.5564</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.373184006779753</v>
+        <v>1.5564</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.87675315295179</v>
+        <v>1.5564</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8768</v>
+        <v>1.5564</v>
       </c>
       <c r="N18" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4748</v>
+        <v>1.3463</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.16618</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.134346277079567</v>
+        <v>0.1225</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.179</v>
+        <v>1.3463</v>
       </c>
       <c r="F19" t="n">
-        <v>22.47709819896553</v>
+        <v>0.3791</v>
       </c>
       <c r="G19" t="n">
-        <v>-26.65607299915182</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>23.68392591264064</v>
+        <v>0.3791</v>
       </c>
       <c r="I19" t="n">
-        <v>15.37220851688373</v>
+        <v>0.3073</v>
       </c>
       <c r="J19" t="n">
-        <v>-26.65607299915182</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="L19" t="n">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.2839</v>
+        <v>1.2745</v>
       </c>
       <c r="N19" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.2832</v>
+        <v>0.8068</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.4491199999999999</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3055659311492328</v>
+        <v>-0.0954</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.504899999999999</v>
+        <v>0.8068</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.504932729262178</v>
+        <v>0.8068</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-9.504932729262178</v>
+        <v>0.8068</v>
       </c>
       <c r="I20" t="n">
-        <v>-12.19500802999676</v>
+        <v>0.8068</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1369,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-12.195</v>
+        <v>0.8068</v>
       </c>
       <c r="N20" t="n">
         <v>170</v>
@@ -1378,78 +1366,78 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.3185</v>
+        <v>0.7914</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.461475</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3136072275206584</v>
+        <v>-0.1017</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.755100000000001</v>
+        <v>0.7914</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.528107189549532</v>
+        <v>0.7914</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.226958075034891</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.528107189549532</v>
+        <v>0.7914</v>
       </c>
       <c r="I21" t="n">
-        <v>-11.86519008509942</v>
+        <v>0.7914</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.226958075034891</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-12.0921</v>
+        <v>0.7914</v>
       </c>
       <c r="N21" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.6258</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.5690299999999999</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3857179895668081</v>
+        <v>-0.1141</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.9981</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.99814236328672</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.99814236328672</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-10.23237801548226</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1461,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-10.2324</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>113</v>
@@ -1470,553 +1458,553 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>r3salt</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.7414</v>
+        <v>0.6334</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.60949</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4138760509243652</v>
+        <v>-0.1655</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.874</v>
+        <v>0.6334</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.87402691619948</v>
+        <v>1.6334</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>-12.87402691619948</v>
+        <v>1.6334</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.967322317949865</v>
+        <v>1.3239</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.9673</v>
+        <v>0.3239000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>82</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2.1976</v>
+        <v>0.6333</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.76916</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5306095625564361</v>
+        <v>-0.1655</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.5051</v>
+        <v>0.6333</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.50513909922454</v>
+        <v>-0.3548</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.9881</v>
       </c>
       <c r="H24" t="n">
-        <v>-16.44453497346034</v>
+        <v>-0.3548</v>
       </c>
       <c r="I24" t="n">
-        <v>-21.09864864519439</v>
+        <v>-0.2876</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.9881</v>
       </c>
       <c r="K24" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M24" t="n">
-        <v>-21.0986</v>
+        <v>0.7004999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>170</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>r3salt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2.4376</v>
+        <v>0.2916</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.85316</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5958587111689874</v>
+        <v>-0.3036</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.5348</v>
+        <v>0.2916</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.69460024367398</v>
+        <v>0.2916</v>
       </c>
       <c r="G25" t="n">
-        <v>4.159821367948826</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-24.00069833026998</v>
+        <v>0.2916</v>
       </c>
       <c r="I25" t="n">
-        <v>-30.7933488011011</v>
+        <v>0.2916</v>
       </c>
       <c r="J25" t="n">
-        <v>4.159821367948826</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-26.6335</v>
+        <v>0.2916</v>
       </c>
       <c r="N25" t="n">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Norwi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.4426</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8549099999999999</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5972413273259028</v>
+        <v>-0.4604</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.5778</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.22217359668699</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>2.644387067875485</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-21.93619914028469</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-27.31677628790169</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>2.644387067875485</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-24.6724</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>208</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.503</v>
+        <v>-0.1052</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.87605</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6141121980752821</v>
+        <v>-0.4639</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.1026</v>
+        <v>-0.1052</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.10257177222469</v>
+        <v>-0.1052</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-19.27213172917313</v>
+        <v>-0.1052</v>
       </c>
       <c r="I27" t="n">
-        <v>-24.72650863365609</v>
+        <v>-0.1052</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-24.7265</v>
+        <v>-0.1052</v>
       </c>
       <c r="N27" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.5316</v>
+        <v>-0.2179</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.88606</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6221650474317314</v>
+        <v>-0.5094</v>
       </c>
       <c r="E28" t="n">
-        <v>-19.3531</v>
+        <v>-0.2179</v>
       </c>
       <c r="F28" t="n">
-        <v>-19.35306367465654</v>
+        <v>-0.2179</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-19.56929313883329</v>
+        <v>-0.2179</v>
       </c>
       <c r="I28" t="n">
-        <v>-16.68928395991065</v>
+        <v>-0.2179</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-16.6893</v>
+        <v>-0.2179</v>
       </c>
       <c r="N28" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Norwi</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.8985</v>
+        <v>-0.2447</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.014475</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7290306610840414</v>
+        <v>-0.5202</v>
       </c>
       <c r="E29" t="n">
-        <v>-22.6772</v>
+        <v>-0.2447</v>
       </c>
       <c r="F29" t="n">
-        <v>-22.67722505945586</v>
+        <v>-0.2447</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-23.97523795062961</v>
+        <v>-0.2447</v>
       </c>
       <c r="I29" t="n">
-        <v>-14.83750575057832</v>
+        <v>-0.2447</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-14.8375</v>
+        <v>-0.2447</v>
       </c>
       <c r="N29" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.9424</v>
+        <v>-0.2778</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.02984</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7422748178573002</v>
+        <v>-0.5336</v>
       </c>
       <c r="E30" t="n">
-        <v>-23.0892</v>
+        <v>-0.2778</v>
       </c>
       <c r="F30" t="n">
-        <v>-23.08919775128108</v>
+        <v>0.7222</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>-24.58624965677559</v>
+        <v>0.7222</v>
       </c>
       <c r="I30" t="n">
-        <v>-20.96789593370296</v>
+        <v>0.5854</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K30" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M30" t="n">
-        <v>-20.9679</v>
+        <v>-0.4146</v>
       </c>
       <c r="N30" t="n">
-        <v>113</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.956</v>
+        <v>-0.5783</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.0346</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7464281423684519</v>
+        <v>-0.655</v>
       </c>
       <c r="E31" t="n">
-        <v>-23.2184</v>
+        <v>-0.5783</v>
       </c>
       <c r="F31" t="n">
-        <v>-23.2183910482328</v>
+        <v>-0.5783</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-24.78104973926483</v>
+        <v>-0.5783</v>
       </c>
       <c r="I31" t="n">
-        <v>-30.11131326808783</v>
+        <v>-0.5783</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-30.1113</v>
+        <v>-0.5783</v>
       </c>
       <c r="N31" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.1928</v>
+        <v>-0.616</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.11748</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8198491089889879</v>
+        <v>-0.6702</v>
       </c>
       <c r="E32" t="n">
-        <v>-25.5022</v>
+        <v>-0.616</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.818316781712859</v>
+        <v>-0.616</v>
       </c>
       <c r="G32" t="n">
-        <v>-18.68390658388904</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.818316781712859</v>
+        <v>-0.616</v>
       </c>
       <c r="I32" t="n">
-        <v>-8.490734105529221</v>
+        <v>-0.616</v>
       </c>
       <c r="J32" t="n">
-        <v>-18.68390658388904</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L32" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-27.1746</v>
+        <v>-0.616</v>
       </c>
       <c r="N32" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.359</v>
+        <v>-0.6765</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.17565</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8732117450409944</v>
+        <v>-0.6947</v>
       </c>
       <c r="E33" t="n">
-        <v>-27.1621</v>
+        <v>-0.6765</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.360285428125088</v>
+        <v>-0.6765</v>
       </c>
       <c r="G33" t="n">
-        <v>-22.80183589803417</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.360285428125088</v>
+        <v>-0.6765</v>
       </c>
       <c r="I33" t="n">
-        <v>-5.594328473820867</v>
+        <v>-0.6765</v>
       </c>
       <c r="J33" t="n">
-        <v>-22.80183589803417</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L33" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-28.3962</v>
+        <v>-0.6765</v>
       </c>
       <c r="N33" t="n">
-        <v>205</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.4476</v>
+        <v>-0.7518</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.20666</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9023044632876692</v>
+        <v>-0.7251</v>
       </c>
       <c r="E34" t="n">
-        <v>-28.0671</v>
+        <v>-0.7518</v>
       </c>
       <c r="F34" t="n">
-        <v>-28.06707931282359</v>
+        <v>-1.2709</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.5191</v>
       </c>
       <c r="H34" t="n">
-        <v>-33.32361969057161</v>
+        <v>-1.2709</v>
       </c>
       <c r="I34" t="n">
-        <v>-40.49134166175116</v>
+        <v>-1.0301</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.5191</v>
       </c>
       <c r="K34" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M34" t="n">
-        <v>-40.4913</v>
+        <v>-0.511</v>
       </c>
       <c r="N34" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35">
@@ -2026,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.5888</v>
+        <v>-0.9214</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.25608</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9495856054105067</v>
+        <v>-0.7936</v>
       </c>
       <c r="E35" t="n">
-        <v>-29.5378</v>
+        <v>-0.9214</v>
       </c>
       <c r="F35" t="n">
-        <v>-29.53780634561173</v>
+        <v>-0.9214</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-36.45604720660053</v>
+        <v>-0.9214</v>
       </c>
       <c r="I35" t="n">
-        <v>-31.09081761770461</v>
+        <v>-0.9214</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2059,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-31.0908</v>
+        <v>-0.9214</v>
       </c>
       <c r="N35" t="n">
         <v>113</v>
@@ -2072,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.8239</v>
+        <v>-0.9563</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.338365</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.030941103764559</v>
+        <v>-0.8077</v>
       </c>
       <c r="E36" t="n">
-        <v>-32.0685</v>
+        <v>-0.9563</v>
       </c>
       <c r="F36" t="n">
-        <v>-32.06845017786935</v>
+        <v>-0.9563</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-42.55061810473796</v>
+        <v>-0.9563</v>
       </c>
       <c r="I36" t="n">
-        <v>-26.33321271387557</v>
+        <v>-0.9563</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-26.3332</v>
+        <v>-0.9563</v>
       </c>
       <c r="N36" t="n">
         <v>82</v>
@@ -2114,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.9405</v>
+        <v>-1.1654</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.379175</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.072541824905233</v>
+        <v>-0.8922</v>
       </c>
       <c r="E37" t="n">
-        <v>-33.3625</v>
+        <v>-1.1654</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.633303131685514</v>
+        <v>-1.1654</v>
       </c>
       <c r="G37" t="n">
-        <v>-23.7291789248156</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-9.633303131685514</v>
+        <v>-1.1654</v>
       </c>
       <c r="I37" t="n">
-        <v>-12.35970967838896</v>
+        <v>-1.1654</v>
       </c>
       <c r="J37" t="n">
-        <v>-23.7291789248156</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-36.0889</v>
+        <v>-1.1654</v>
       </c>
       <c r="N37" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38">
@@ -2164,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.1677</v>
+        <v>-1.3087</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.458695</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.156072894689938</v>
+        <v>-0.95</v>
       </c>
       <c r="E38" t="n">
-        <v>-35.9608</v>
+        <v>-1.3087</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.96079920567037</v>
+        <v>-1.3087</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-53.97184944652476</v>
+        <v>-1.3087</v>
       </c>
       <c r="I38" t="n">
-        <v>-33.40144644992476</v>
+        <v>-1.3087</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-33.4014</v>
+        <v>-1.3087</v>
       </c>
       <c r="N38" t="n">
         <v>82</v>
@@ -2206,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.3245</v>
+        <v>-1.8858</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.513575</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.215687162609682</v>
+        <v>-1.1832</v>
       </c>
       <c r="E39" t="n">
-        <v>-37.8152</v>
+        <v>-1.8858</v>
       </c>
       <c r="F39" t="n">
-        <v>-21.79278248906799</v>
+        <v>-1.8858</v>
       </c>
       <c r="G39" t="n">
-        <v>-16.02237791501966</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-22.71429458410916</v>
+        <v>-1.8858</v>
       </c>
       <c r="I39" t="n">
-        <v>-29.14286852300798</v>
+        <v>-1.8858</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.02237791501966</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-45.1652</v>
+        <v>-1.8858</v>
       </c>
       <c r="N39" t="n">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.4285</v>
+        <v>-2.7055</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.549975</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.256147236520399</v>
+        <v>-1.5143</v>
       </c>
       <c r="E40" t="n">
-        <v>-39.0737</v>
+        <v>-2.7055</v>
       </c>
       <c r="F40" t="n">
-        <v>-39.07371131418411</v>
+        <v>-1.907</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.7985</v>
       </c>
       <c r="H40" t="n">
-        <v>-65.27558685428856</v>
+        <v>-1.907</v>
       </c>
       <c r="I40" t="n">
-        <v>-40.39696695888047</v>
+        <v>-1.5457</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.7985</v>
       </c>
       <c r="K40" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-40.397</v>
+        <v>-2.3442</v>
       </c>
       <c r="N40" t="n">
-        <v>82</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.7936</v>
+        <v>-2.921</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.67776</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.404017869057817</v>
+        <v>-1.6014</v>
       </c>
       <c r="E41" t="n">
-        <v>-43.6734</v>
+        <v>-2.921</v>
       </c>
       <c r="F41" t="n">
-        <v>-33.36753892642992</v>
+        <v>-3.4458</v>
       </c>
       <c r="G41" t="n">
-        <v>-10.30583573901694</v>
+        <v>0.5248</v>
       </c>
       <c r="H41" t="n">
-        <v>-46.0648681429503</v>
+        <v>-3.4458</v>
       </c>
       <c r="I41" t="n">
-        <v>-29.89870687014132</v>
+        <v>-2.7929</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.30583573901694</v>
+        <v>0.5248</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2335,7 +2323,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-40.2045</v>
+        <v>-2.2681</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.140447827314907</v>
+        <v>0.9466</v>
       </c>
       <c r="J2" t="n">
-        <v>27.37074785555777</v>
+        <v>22.7184</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1970387553788742</v>
+        <v>0.3301</v>
       </c>
       <c r="J3" t="n">
-        <v>4.72893012909298</v>
+        <v>7.9224</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1861992554610854</v>
+        <v>-0.205</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.46878213106605</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.71</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4633338441992305</v>
+        <v>-0.5041</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.12001226078153</v>
+        <v>-12.0984</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7632645307037182</v>
+        <v>-0.7849</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.31834873688924</v>
+        <v>-18.8376</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4628225062978794</v>
+        <v>0.7912</v>
       </c>
       <c r="J7" t="n">
-        <v>11.10774015114911</v>
+        <v>18.9888</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3891526777703145</v>
+        <v>0.6952</v>
       </c>
       <c r="J8" t="n">
-        <v>9.339664266487549</v>
+        <v>16.6848</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1237947205225536</v>
+        <v>0.2674</v>
       </c>
       <c r="J9" t="n">
-        <v>2.971073292541287</v>
+        <v>6.4176</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.93</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1096995495939776</v>
+        <v>-0.3445</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.632789190255461</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1876101087108749</v>
+        <v>-0.4896</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.502642609060998</v>
+        <v>-11.7504</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03502699431788074</v>
+        <v>0.2238</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7705938749933763</v>
+        <v>4.9236</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1042336750082082</v>
+        <v>0.1296</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.29314085018058</v>
+        <v>2.8512</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1314144377336644</v>
+        <v>0.0849</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.891117630140617</v>
+        <v>1.8678</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3090890414389547</v>
+        <v>-0.2505</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.799958911657003</v>
+        <v>-5.511</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4194013698969342</v>
+        <v>-0.3753</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.226830137732552</v>
+        <v>-8.256600000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8812996177727039</v>
+        <v>1.2917</v>
       </c>
       <c r="J17" t="n">
-        <v>19.38859159099949</v>
+        <v>28.4174</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8812996177727039</v>
+        <v>1.2917</v>
       </c>
       <c r="J18" t="n">
-        <v>19.38859159099949</v>
+        <v>28.4174</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2925780737491619</v>
+        <v>0.5507</v>
       </c>
       <c r="J19" t="n">
-        <v>6.436717622481561</v>
+        <v>12.1154</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.196009693879614</v>
+        <v>-0.4701</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.312213265351508</v>
+        <v>-10.3422</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4384605910123134</v>
+        <v>-0.8632</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.646133002270895</v>
+        <v>-18.9904</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1298142723501458</v>
+        <v>0.5108</v>
       </c>
       <c r="J22" t="n">
-        <v>2.206842629952479</v>
+        <v>8.6836</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09736201671486804</v>
+        <v>0.2983</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.655154284152757</v>
+        <v>5.0711</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4613778031739723</v>
+        <v>-0.248</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.843422653957529</v>
+        <v>-4.216</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.61</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7223726374013238</v>
+        <v>-0.5884</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.28033483582251</v>
+        <v>-10.0028</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.294528476620353</v>
+        <v>-1.1404</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.006984102546</v>
+        <v>-19.3868</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>1.278864842184941</v>
+        <v>1.6625</v>
       </c>
       <c r="J27" t="n">
-        <v>21.740702317144</v>
+        <v>28.2625</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.145893872848332</v>
+        <v>1.5184</v>
       </c>
       <c r="J28" t="n">
-        <v>19.48019583842165</v>
+        <v>25.8128</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>0.870791896840321</v>
+        <v>1.2118</v>
       </c>
       <c r="J29" t="n">
-        <v>14.80346224628546</v>
+        <v>20.6006</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09645401249519375</v>
+        <v>0.1553</v>
       </c>
       <c r="J30" t="n">
-        <v>1.639718212418294</v>
+        <v>2.6401</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.06828956717978882</v>
+        <v>-0.1885</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.16092264205641</v>
+        <v>-3.2045</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.482311027524476</v>
+        <v>0.8992</v>
       </c>
       <c r="J32" t="n">
-        <v>10.61084260553847</v>
+        <v>19.7824</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2753381651891449</v>
+        <v>0.534</v>
       </c>
       <c r="J33" t="n">
-        <v>6.057439634161188</v>
+        <v>11.748</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1501562027418871</v>
+        <v>0.212</v>
       </c>
       <c r="J34" t="n">
-        <v>3.303436460321516</v>
+        <v>4.664</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1113219950800704</v>
+        <v>0.1063</v>
       </c>
       <c r="J35" t="n">
-        <v>2.449083891761549</v>
+        <v>2.3386</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1472133434029569</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.238693554865051</v>
+        <v>-12.6302</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1672651239419825</v>
+        <v>0.3625</v>
       </c>
       <c r="J37" t="n">
-        <v>3.679832726723614</v>
+        <v>7.975</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03454624222055377</v>
+        <v>0.2353</v>
       </c>
       <c r="J38" t="n">
-        <v>0.760017328852183</v>
+        <v>5.1766</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1146302917745163</v>
+        <v>-0.0707</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.521866419039358</v>
+        <v>-1.5554</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2239396056340673</v>
+        <v>-0.2895</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.926671323949481</v>
+        <v>-6.369</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4829341580647761</v>
+        <v>-0.6234</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.62455147742507</v>
+        <v>-13.7148</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4641025453497862</v>
+        <v>0.88</v>
       </c>
       <c r="J42" t="n">
-        <v>9.74615345234551</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3819689920670004</v>
+        <v>0.7405</v>
       </c>
       <c r="J43" t="n">
-        <v>8.021348833407009</v>
+        <v>15.5505</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3819689920670004</v>
+        <v>0.7405</v>
       </c>
       <c r="J44" t="n">
-        <v>8.021348833407009</v>
+        <v>15.5505</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01224659231707181</v>
+        <v>-0.1689</v>
       </c>
       <c r="J45" t="n">
-        <v>0.257178438658508</v>
+        <v>-3.5469</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.01583196573270169</v>
+        <v>-0.2487</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3324712803867355</v>
+        <v>-5.2227</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1092813497144984</v>
+        <v>0.3457</v>
       </c>
       <c r="J47" t="n">
-        <v>2.294908344004467</v>
+        <v>7.2597</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.04930693613562518</v>
+        <v>0.1566</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.035445658848129</v>
+        <v>3.2886</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09329109124713122</v>
+        <v>0.0529</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.959112916189756</v>
+        <v>1.1109</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3837788145935222</v>
+        <v>-0.4718</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.059355106463967</v>
+        <v>-9.9078</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.59</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.521502950142234</v>
+        <v>-0.642</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.95156195298691</v>
+        <v>-13.482</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7163295939071981</v>
+        <v>1.3045</v>
       </c>
       <c r="J52" t="n">
-        <v>14.32659187814396</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.31</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4150839040671985</v>
+        <v>0.7954</v>
       </c>
       <c r="J53" t="n">
-        <v>8.301678081343971</v>
+        <v>15.908</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3316374455326868</v>
+        <v>0.6149</v>
       </c>
       <c r="J54" t="n">
-        <v>6.632748910653735</v>
+        <v>12.298</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2638320300968113</v>
+        <v>0.4392</v>
       </c>
       <c r="J55" t="n">
-        <v>5.276640601936227</v>
+        <v>8.784000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1294151171923021</v>
+        <v>-0.513</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.588302343846043</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.009013777748612733</v>
+        <v>0.2367</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1802755549722547</v>
+        <v>4.734</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1698224952333924</v>
+        <v>-0.0843</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.396449904667847</v>
+        <v>-1.686</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3898591882088163</v>
+        <v>-0.4241</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.797183764176326</v>
+        <v>-8.481999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4506414453525993</v>
+        <v>-0.4978</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.012828907051986</v>
+        <v>-9.956</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5483980585854775</v>
+        <v>-0.6071</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.96796117170955</v>
+        <v>-12.142</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.83</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9480728810121953</v>
+        <v>1.6851</v>
       </c>
       <c r="J62" t="n">
-        <v>14.22109321518293</v>
+        <v>25.2765</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.78</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8887247886041982</v>
+        <v>1.6013</v>
       </c>
       <c r="J63" t="n">
-        <v>13.33087182906297</v>
+        <v>24.0195</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6041384874164879</v>
+        <v>1.127</v>
       </c>
       <c r="J64" t="n">
-        <v>9.062077311247318</v>
+        <v>16.905</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.35</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3782732949310981</v>
+        <v>0.7081</v>
       </c>
       <c r="J65" t="n">
-        <v>5.674099423966471</v>
+        <v>10.6215</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1652606409648127</v>
+        <v>0.33</v>
       </c>
       <c r="J66" t="n">
-        <v>2.47890961447219</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2653030541984381</v>
+        <v>0.7305</v>
       </c>
       <c r="J67" t="n">
-        <v>3.979545812976571</v>
+        <v>10.9575</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5483462767228887</v>
+        <v>-0.3744</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.225194150843331</v>
+        <v>-5.616</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.51</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7694196786521198</v>
+        <v>-0.6932</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.5412951797818</v>
+        <v>-10.398</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.44</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8507478502070701</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.76121775310605</v>
+        <v>-11.757</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9192671327321458</v>
+        <v>-0.8582</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.78900699098219</v>
+        <v>-12.873</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09358762092198519</v>
+        <v>0.6087</v>
       </c>
       <c r="J72" t="n">
-        <v>1.403814313829778</v>
+        <v>9.1305</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>0.82</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4092586527374092</v>
+        <v>-0.1877</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.138879791061139</v>
+        <v>-2.8155</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6670374244862504</v>
+        <v>-0.5596</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.00556136729375</v>
+        <v>-8.394</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.38</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9347537988715446</v>
+        <v>-0.8547</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.02130698307317</v>
+        <v>-12.8205</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.25</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.086363035200653</v>
+        <v>-1.0097</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.2954455280098</v>
+        <v>-15.1455</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>2.29</v>
       </c>
       <c r="I77" t="n">
-        <v>1.06200909973966</v>
+        <v>1.4116</v>
       </c>
       <c r="J77" t="n">
-        <v>15.9301364960949</v>
+        <v>21.174</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.61</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5207127523432292</v>
+        <v>0.747</v>
       </c>
       <c r="J78" t="n">
-        <v>7.810691285148438</v>
+        <v>11.205</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3475243347248501</v>
+        <v>0.4771</v>
       </c>
       <c r="J79" t="n">
-        <v>5.21286502087275</v>
+        <v>7.1565</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1219954474282764</v>
+        <v>0.1536</v>
       </c>
       <c r="J80" t="n">
-        <v>1.829931711424146</v>
+        <v>2.304</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01553720576044153</v>
+        <v>-0.0395</v>
       </c>
       <c r="J81" t="n">
-        <v>0.2330580864066229</v>
+        <v>-0.5925</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>0.515332359899917</v>
+        <v>1.4058</v>
       </c>
       <c r="J82" t="n">
-        <v>9.791314838098423</v>
+        <v>26.7102</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3539850150314359</v>
+        <v>1.0253</v>
       </c>
       <c r="J83" t="n">
-        <v>6.725715285597282</v>
+        <v>19.4807</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1551746007295371</v>
+        <v>0.4227</v>
       </c>
       <c r="J84" t="n">
-        <v>2.948317413861206</v>
+        <v>8.0313</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.04797263876345617</v>
+        <v>0.0905</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9114801365056673</v>
+        <v>1.7195</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.03900980265878332</v>
+        <v>0.059</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7411862505168831</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2245217253135424</v>
+        <v>0.6851</v>
       </c>
       <c r="J87" t="n">
-        <v>4.265912780957306</v>
+        <v>13.0169</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2137528395210675</v>
+        <v>-0.0031</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.061303950900283</v>
+        <v>-0.0589</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.386396559249254</v>
+        <v>-0.3046</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.341534625735825</v>
+        <v>-5.7874</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4973401741621555</v>
+        <v>-0.4411</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.449463309080954</v>
+        <v>-8.3809</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.5</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7860452963400216</v>
+        <v>-0.7496</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.93486063046041</v>
+        <v>-14.2424</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4689785471317724</v>
+        <v>1.3144</v>
       </c>
       <c r="J92" t="n">
-        <v>9.379570942635448</v>
+        <v>26.288</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2805137245601345</v>
+        <v>0.8537</v>
       </c>
       <c r="J93" t="n">
-        <v>5.610274491202691</v>
+        <v>17.074</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1687744133666152</v>
+        <v>0.4803</v>
       </c>
       <c r="J94" t="n">
-        <v>3.375488267332303</v>
+        <v>9.606</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.09852374707148301</v>
+        <v>0.2678</v>
       </c>
       <c r="J95" t="n">
-        <v>1.97047494142966</v>
+        <v>5.356</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.03579037479782345</v>
+        <v>0.0625</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7158074959564689</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07279471821504953</v>
+        <v>0.4066</v>
       </c>
       <c r="J97" t="n">
-        <v>1.455894364300991</v>
+        <v>8.132</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>0.84</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3193385457296146</v>
+        <v>-0.2715</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.386770914592292</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>0.8</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.365945605213001</v>
+        <v>-0.3398</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.318912104260019</v>
+        <v>-6.796</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3902147668343782</v>
+        <v>-0.3714</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.804295336687563</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5012470388869175</v>
+        <v>-0.5021</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.02494077773835</v>
+        <v>-10.042</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3590245251871198</v>
+        <v>1.0611</v>
       </c>
       <c r="J102" t="n">
-        <v>8.257564079303755</v>
+        <v>24.4053</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2990826103495153</v>
+        <v>0.9318</v>
       </c>
       <c r="J103" t="n">
-        <v>6.878900038038853</v>
+        <v>21.4314</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.19</v>
       </c>
       <c r="I104" t="n">
-        <v>0.135297350639858</v>
+        <v>0.4993</v>
       </c>
       <c r="J104" t="n">
-        <v>3.111839064716734</v>
+        <v>11.4839</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.03849944581311991</v>
+        <v>-0.0204</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.885487253701758</v>
+        <v>-0.4692</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.98</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.08604125810736392</v>
+        <v>-0.2215</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.97894893646937</v>
+        <v>-5.0945</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1197904425534181</v>
+        <v>0.4346</v>
       </c>
       <c r="J107" t="n">
-        <v>2.755180178728616</v>
+        <v>9.995799999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1045404806614506</v>
+        <v>0.0373</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.404431055213363</v>
+        <v>0.8579</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1176079817796938</v>
+        <v>0.002</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.704983580932958</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3948929648626396</v>
+        <v>-0.4108</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.08253819184071</v>
+        <v>-9.448399999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.7</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4871177357689714</v>
+        <v>-0.5075</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.20370792268634</v>
+        <v>-11.6725</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3397787630283896</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>6.116017734511013</v>
+        <v>15.1974</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4659389534816271</v>
+        <v>-0.4417</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.386901162669288</v>
+        <v>-7.9506</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.61</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5786864519229461</v>
+        <v>-0.5855</v>
       </c>
       <c r="J114" t="n">
-        <v>-10.41635613461303</v>
+        <v>-10.539</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.53</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.668772262162988</v>
+        <v>-0.6904</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.03790071893378</v>
+        <v>-12.4272</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7020924863050513</v>
+        <v>-0.7282</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.63766475349092</v>
+        <v>-13.1076</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.9</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6940504367450566</v>
+        <v>1.0738</v>
       </c>
       <c r="J117" t="n">
-        <v>12.49290786141102</v>
+        <v>19.3284</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4522561674845416</v>
+        <v>0.7517</v>
       </c>
       <c r="J118" t="n">
-        <v>8.140611014721749</v>
+        <v>13.5306</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.28</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2058156123595454</v>
+        <v>0.3486</v>
       </c>
       <c r="J119" t="n">
-        <v>3.704681022471818</v>
+        <v>6.2748</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>1.26</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1888414598713255</v>
+        <v>0.3219</v>
       </c>
       <c r="J120" t="n">
-        <v>3.399146277683859</v>
+        <v>5.7942</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1274242003337777</v>
+        <v>-0.236</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.293635606007999</v>
+        <v>-4.248</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3478434859820476</v>
+        <v>0.8811</v>
       </c>
       <c r="J122" t="n">
-        <v>7.304713205622999</v>
+        <v>18.5031</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3077169656513523</v>
+        <v>0.7892</v>
       </c>
       <c r="J123" t="n">
-        <v>6.462056278678398</v>
+        <v>16.5732</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2188676282774792</v>
+        <v>0.5636</v>
       </c>
       <c r="J124" t="n">
-        <v>4.596220193827063</v>
+        <v>11.8356</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1671082083273659</v>
+        <v>0.3743</v>
       </c>
       <c r="J125" t="n">
-        <v>3.509272374874683</v>
+        <v>7.8603</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1306280268660898</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-2.743188564187886</v>
+        <v>-12.0141</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1501437368117205</v>
+        <v>0.4967</v>
       </c>
       <c r="J127" t="n">
-        <v>3.15301847304613</v>
+        <v>10.4307</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0999602267889578</v>
+        <v>0.4126</v>
       </c>
       <c r="J128" t="n">
-        <v>2.099164762568114</v>
+        <v>8.6646</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4115937532378267</v>
+        <v>-0.4237</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.643468817994361</v>
+        <v>-8.8977</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4777697449211668</v>
+        <v>-0.4942</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.0331646433445</v>
+        <v>-10.3782</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7218547630420986</v>
+        <v>-0.7362</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.15895002388407</v>
+        <v>-15.4602</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>0.87</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2959428469894184</v>
+        <v>-0.1466</v>
       </c>
       <c r="J132" t="n">
-        <v>-5.326971245809531</v>
+        <v>-2.6388</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>0.85</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3216886175119137</v>
+        <v>-0.18</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.790395115214446</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3847943117832223</v>
+        <v>-0.2628</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.926297612098001</v>
+        <v>-4.7304</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3847943117832223</v>
+        <v>-0.2628</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.926297612098001</v>
+        <v>-4.7304</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8669237692302145</v>
+        <v>-0.8455</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.60462784614386</v>
+        <v>-15.219</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.75</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5518338990781062</v>
+        <v>1.6182</v>
       </c>
       <c r="J137" t="n">
-        <v>9.933010183405912</v>
+        <v>29.1276</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3220717852244532</v>
+        <v>1.0142</v>
       </c>
       <c r="J138" t="n">
-        <v>5.797292134040158</v>
+        <v>18.2556</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.33</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2469278426469055</v>
+        <v>0.7382</v>
       </c>
       <c r="J139" t="n">
-        <v>4.4447011676443</v>
+        <v>13.2876</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1786381012183426</v>
+        <v>0.5246</v>
       </c>
       <c r="J140" t="n">
-        <v>3.215485821930166</v>
+        <v>9.4428</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>1.07</v>
       </c>
       <c r="I141" t="n">
-        <v>0.04521514531327272</v>
+        <v>0.0883</v>
       </c>
       <c r="J141" t="n">
-        <v>0.8138726156389089</v>
+        <v>1.5894</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.38</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2729037566236571</v>
+        <v>0.6509</v>
       </c>
       <c r="J142" t="n">
-        <v>6.276786402344112</v>
+        <v>14.9707</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.01547637082953307</v>
+        <v>0.2255</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3559565290792606</v>
+        <v>5.1865</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.006504151338659277</v>
+        <v>0.2077</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1495954807891633</v>
+        <v>4.7771</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.54</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6608946991316003</v>
+        <v>-0.7058</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.20057808002681</v>
+        <v>-16.2334</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6973210363124088</v>
+        <v>-0.7415</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.0383838351854</v>
+        <v>-17.0545</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.51</v>
       </c>
       <c r="I147" t="n">
-        <v>0.357189030670001</v>
+        <v>1.2471</v>
       </c>
       <c r="J147" t="n">
-        <v>8.215347705410023</v>
+        <v>28.6833</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1784331323210545</v>
+        <v>0.7502</v>
       </c>
       <c r="J148" t="n">
-        <v>4.103962043384253</v>
+        <v>17.2546</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1122385799771229</v>
+        <v>0.5067</v>
       </c>
       <c r="J149" t="n">
-        <v>2.581487339473827</v>
+        <v>11.6541</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.02952929816814376</v>
+        <v>0.1819</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6791738578673066</v>
+        <v>4.1837</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2104061632862996</v>
+        <v>-0.5006</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.83934175558489</v>
+        <v>-11.5138</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6420355094289493</v>
+        <v>1.7293</v>
       </c>
       <c r="J152" t="n">
-        <v>15.40885222629478</v>
+        <v>41.5032</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.09263547907525901</v>
+        <v>0.386</v>
       </c>
       <c r="J153" t="n">
-        <v>2.223251497806216</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.09263547907525901</v>
+        <v>0.386</v>
       </c>
       <c r="J154" t="n">
-        <v>2.223251497806216</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.07332037160216243</v>
+        <v>-0.2887</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.759688918451898</v>
+        <v>-6.9288</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5638106908393995</v>
+        <v>-1.2469</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.53145658014559</v>
+        <v>-29.9256</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.18</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1410101455687252</v>
+        <v>0.3679</v>
       </c>
       <c r="J157" t="n">
-        <v>3.384243493649405</v>
+        <v>8.829599999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.98</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.070800678699452</v>
+        <v>-0.0379</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.699216288786848</v>
+        <v>-0.9096</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.08040092224501147</v>
+        <v>-0.0634</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.929622133880275</v>
+        <v>-1.5216</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.09773126959907312</v>
+        <v>-0.1166</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.345550470377755</v>
+        <v>-2.7984</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3388230305099406</v>
+        <v>-0.4728</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.131752732238574</v>
+        <v>-11.3472</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4333548169864453</v>
+        <v>1.2001</v>
       </c>
       <c r="J162" t="n">
-        <v>9.100451156715351</v>
+        <v>25.2021</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3604878743043192</v>
+        <v>1.0348</v>
       </c>
       <c r="J163" t="n">
-        <v>7.570245360390702</v>
+        <v>21.7308</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2584704114370184</v>
+        <v>0.7896</v>
       </c>
       <c r="J164" t="n">
-        <v>5.427878640177387</v>
+        <v>16.5816</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1384702337720176</v>
+        <v>0.4033</v>
       </c>
       <c r="J165" t="n">
-        <v>2.907874909212369</v>
+        <v>8.4693</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4271488004281256</v>
+        <v>-1.0413</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.970124808990638</v>
+        <v>-21.8673</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.09</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.01944564410010229</v>
+        <v>0.2429</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.4083585261021481</v>
+        <v>5.1009</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.06444540686709549</v>
+        <v>0.1701</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.353353544209005</v>
+        <v>3.5721</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2840214935871493</v>
+        <v>-0.2985</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.964451365330135</v>
+        <v>-6.2685</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.294905041176023</v>
+        <v>-0.3145</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.193005864696482</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3607871630635321</v>
+        <v>-0.4054</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.576530424334174</v>
+        <v>-8.513400000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.94</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8475002113656027</v>
+        <v>1.9106</v>
       </c>
       <c r="J172" t="n">
-        <v>14.40750359321525</v>
+        <v>32.4802</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8044185716510563</v>
+        <v>1.8357</v>
       </c>
       <c r="J173" t="n">
-        <v>13.67511571806796</v>
+        <v>31.2069</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.26</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2211658610310916</v>
+        <v>0.5464</v>
       </c>
       <c r="J174" t="n">
-        <v>3.759819637528557</v>
+        <v>9.2888</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I175" t="n">
-        <v>0.08207183627348058</v>
+        <v>0.2084</v>
       </c>
       <c r="J175" t="n">
-        <v>1.39522121664917</v>
+        <v>3.5428</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1095751459936128</v>
+        <v>-0.4181</v>
       </c>
       <c r="J176" t="n">
-        <v>-1.862777481891418</v>
+        <v>-7.1077</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>0.91</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2132304652409912</v>
+        <v>-0.0795</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.62491790909685</v>
+        <v>-1.3515</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2132304652409912</v>
+        <v>-0.0795</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.62491790909685</v>
+        <v>-1.3515</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.78</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3302050150564769</v>
+        <v>-0.2989</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.613485255960108</v>
+        <v>-5.0813</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.346352878142295</v>
+        <v>-0.3346</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.887998928419016</v>
+        <v>-5.6882</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6727335449789191</v>
+        <v>-0.8699</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.43647026464163</v>
+        <v>-14.7883</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2974777147377116</v>
+        <v>0.654</v>
       </c>
       <c r="J182" t="n">
-        <v>8.626853727393636</v>
+        <v>18.966</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.98</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1360444510340267</v>
+        <v>-0.0477</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.945289079986775</v>
+        <v>-1.3833</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.199563315443827</v>
+        <v>-0.1838</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.787336147870985</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.82</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3179113196105792</v>
+        <v>-0.3483</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.219428268706798</v>
+        <v>-10.1007</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3890335606016025</v>
+        <v>-0.4347</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.28197325744647</v>
+        <v>-12.6063</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.92</v>
       </c>
       <c r="I187" t="n">
-        <v>1.015647662444437</v>
+        <v>1.1525</v>
       </c>
       <c r="J187" t="n">
-        <v>29.45378221088868</v>
+        <v>33.4225</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.12</v>
       </c>
       <c r="I188" t="n">
-        <v>0.091259957538188</v>
+        <v>0.1788</v>
       </c>
       <c r="J188" t="n">
-        <v>2.646538768607452</v>
+        <v>5.1852</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.05411498374186972</v>
+        <v>0.1277</v>
       </c>
       <c r="J189" t="n">
-        <v>1.569334528514222</v>
+        <v>3.7033</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.08815375160522367</v>
+        <v>-0.1829</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.556458796551486</v>
+        <v>-5.3041</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2550442546735595</v>
+        <v>-0.4556</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.396283385533226</v>
+        <v>-13.2124</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.8</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7852018780224912</v>
+        <v>1.681</v>
       </c>
       <c r="J192" t="n">
-        <v>11.77802817033737</v>
+        <v>25.215</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.67</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6661483503352661</v>
+        <v>1.4453</v>
       </c>
       <c r="J193" t="n">
-        <v>9.992225255028991</v>
+        <v>21.6795</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.54</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5430408643055775</v>
+        <v>1.1925</v>
       </c>
       <c r="J194" t="n">
-        <v>8.145612964583663</v>
+        <v>17.8875</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1777977139694203</v>
+        <v>0.2855</v>
       </c>
       <c r="J195" t="n">
-        <v>2.666965709541305</v>
+        <v>4.2825</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.98</v>
       </c>
       <c r="I196" t="n">
-        <v>0.01266744201775885</v>
+        <v>-0.2859</v>
       </c>
       <c r="J196" t="n">
-        <v>0.1900116302663828</v>
+        <v>-4.2885</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2149468165545324</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.224202248317986</v>
+        <v>-1.122</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.233305823887498</v>
+        <v>-0.1085</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.499587358312471</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3426144728726044</v>
+        <v>-0.3008</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.139217093089067</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5796768012240617</v>
+        <v>-0.7418</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.695152018360925</v>
+        <v>-11.127</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.35</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6836411031059271</v>
+        <v>-0.8921</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.25461654658891</v>
+        <v>-13.3815</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3796027167297882</v>
+        <v>0.7136</v>
       </c>
       <c r="J202" t="n">
-        <v>8.351259768055339</v>
+        <v>15.6992</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.36</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2440154015241413</v>
+        <v>0.5206</v>
       </c>
       <c r="J203" t="n">
-        <v>5.36833883353111</v>
+        <v>11.4532</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.25</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1534647342423359</v>
+        <v>0.3656</v>
       </c>
       <c r="J204" t="n">
-        <v>3.376224153331389</v>
+        <v>8.043200000000001</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.03905434029467417</v>
+        <v>0.141</v>
       </c>
       <c r="J205" t="n">
-        <v>0.8591954864828318</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1274196596657599</v>
+        <v>-0.1579</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.803232512646719</v>
+        <v>-3.4738</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1472917440967324</v>
+        <v>0.5294</v>
       </c>
       <c r="J207" t="n">
-        <v>3.240418370128113</v>
+        <v>11.6468</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.07497889882099046</v>
+        <v>0.4063</v>
       </c>
       <c r="J208" t="n">
-        <v>1.64953577406179</v>
+        <v>8.938599999999999</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4166053877699206</v>
+        <v>-0.3818</v>
       </c>
       <c r="J209" t="n">
-        <v>-9.165318530938254</v>
+        <v>-8.3996</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5355439596972343</v>
+        <v>-0.5075</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.78196711333915</v>
+        <v>-11.165</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.7</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5355439596972343</v>
+        <v>-0.5075</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.78196711333915</v>
+        <v>-11.165</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2538729551330575</v>
+        <v>0.604</v>
       </c>
       <c r="J212" t="n">
-        <v>5.839077968060323</v>
+        <v>13.892</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.07308818805142893</v>
+        <v>0.2886</v>
       </c>
       <c r="J213" t="n">
-        <v>1.681028325182865</v>
+        <v>6.6378</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.73</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3639162181990842</v>
+        <v>-0.4406</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.370073018578937</v>
+        <v>-10.1338</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5847399142746754</v>
+        <v>-0.6684</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.44901802831754</v>
+        <v>-15.3732</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.5</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6602038550007621</v>
+        <v>-0.7421</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.18468866501753</v>
+        <v>-17.0683</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.34</v>
       </c>
       <c r="I217" t="n">
-        <v>0.250004624255323</v>
+        <v>0.8796</v>
       </c>
       <c r="J217" t="n">
-        <v>5.750106357872429</v>
+        <v>20.2308</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.24</v>
       </c>
       <c r="I218" t="n">
-        <v>0.167338944159621</v>
+        <v>0.638</v>
       </c>
       <c r="J218" t="n">
-        <v>3.848795715671283</v>
+        <v>14.674</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.23</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1595857493783113</v>
+        <v>0.611</v>
       </c>
       <c r="J219" t="n">
-        <v>3.670472235701159</v>
+        <v>14.053</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1160909573171233</v>
+        <v>0.4285</v>
       </c>
       <c r="J220" t="n">
-        <v>2.670092018293836</v>
+        <v>9.855499999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.02285529691407765</v>
+        <v>0.1122</v>
       </c>
       <c r="J221" t="n">
-        <v>0.5256718290237861</v>
+        <v>2.5806</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.175053915061389</v>
+        <v>0.2058</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.800862640982225</v>
+        <v>3.2928</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.347011424893914</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.552182798302624</v>
+        <v>-1.5072</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4121060642957959</v>
+        <v>-0.1809</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.593697028732734</v>
+        <v>-2.8944</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.59</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.7413891248089037</v>
+        <v>-0.6156</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.86222599694246</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.5</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8543375608760402</v>
+        <v>-0.7306</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.66940097401664</v>
+        <v>-11.6896</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.93</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7411178194124763</v>
+        <v>1.909</v>
       </c>
       <c r="J227" t="n">
-        <v>11.85788511059962</v>
+        <v>30.544</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.76</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6146651240775497</v>
+        <v>1.6242</v>
       </c>
       <c r="J228" t="n">
-        <v>9.834641985240795</v>
+        <v>25.9872</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.65</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5283260392830756</v>
+        <v>1.4226</v>
       </c>
       <c r="J229" t="n">
-        <v>8.45321662852921</v>
+        <v>22.7616</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2044043106695151</v>
+        <v>-0.6751</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.270468970712241</v>
+        <v>-10.8016</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.79</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2641379317349637</v>
+        <v>-0.792</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.226206907759419</v>
+        <v>-12.672</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6397769843922002</v>
+        <v>1.7079</v>
       </c>
       <c r="J232" t="n">
-        <v>12.795539687844</v>
+        <v>34.158</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2851688681406742</v>
+        <v>0.859</v>
       </c>
       <c r="J233" t="n">
-        <v>5.703377362813484</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.27</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2239170681713882</v>
+        <v>0.6445</v>
       </c>
       <c r="J234" t="n">
-        <v>4.478341363427765</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.24</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1999915776350865</v>
+        <v>0.5656</v>
       </c>
       <c r="J235" t="n">
-        <v>3.999831552701729</v>
+        <v>11.312</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2916201096713728</v>
+        <v>-0.7948</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.832402193427455</v>
+        <v>-15.896</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.44</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3259919430338509</v>
+        <v>0.7712</v>
       </c>
       <c r="J237" t="n">
-        <v>6.519838860677018</v>
+        <v>15.424</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.4575740842028931</v>
+        <v>-0.4835</v>
       </c>
       <c r="J238" t="n">
-        <v>-9.151481684057863</v>
+        <v>-9.67</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4942745208621875</v>
+        <v>-0.526</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.88549041724375</v>
+        <v>-10.52</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5187483725431431</v>
+        <v>-0.5536</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.37496745086286</v>
+        <v>-11.072</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6158829381437444</v>
+        <v>-0.659</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.31765876287489</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.23</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1318758777495583</v>
+        <v>0.4379</v>
       </c>
       <c r="J242" t="n">
-        <v>3.824400454737192</v>
+        <v>12.6991</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I243" t="n">
-        <v>0.07001597543158349</v>
+        <v>0.3366</v>
       </c>
       <c r="J243" t="n">
-        <v>2.030463287515921</v>
+        <v>9.7614</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.06</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.02258739387138537</v>
+        <v>0.1694</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.6550344222701757</v>
+        <v>4.9126</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4020339743364768</v>
+        <v>-0.4324</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.65898525575783</v>
+        <v>-12.5396</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5819022741506394</v>
+        <v>-0.6161</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.87516595036854</v>
+        <v>-17.8669</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4714479547026311</v>
+        <v>0.7599</v>
       </c>
       <c r="J247" t="n">
-        <v>13.6719906863763</v>
+        <v>22.0371</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.35</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3090655362440123</v>
+        <v>0.5457</v>
       </c>
       <c r="J248" t="n">
-        <v>8.962900551076357</v>
+        <v>15.8253</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.01067566027459601</v>
+        <v>-0.0516</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.3095941479632843</v>
+        <v>-1.4964</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1577185846659582</v>
+        <v>-0.2903</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.573838955312788</v>
+        <v>-8.418699999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2082486696486813</v>
+        <v>-0.3504</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.039211419811757</v>
+        <v>-10.1616</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.84</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7092459334790153</v>
+        <v>1.79</v>
       </c>
       <c r="J252" t="n">
-        <v>12.05718086914326</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.46</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3994811222489959</v>
+        <v>1.0731</v>
       </c>
       <c r="J253" t="n">
-        <v>6.79117907823293</v>
+        <v>18.2427</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2300631536193185</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>3.911073611528414</v>
+        <v>9.554</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>1.22</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2039446336204291</v>
+        <v>0.4893</v>
       </c>
       <c r="J255" t="n">
-        <v>3.467058771547294</v>
+        <v>8.318099999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.100809481613828</v>
+        <v>-0.4838</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.713761187435077</v>
+        <v>-8.224600000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.01393925533996399</v>
+        <v>0.3682</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.2369673407793877</v>
+        <v>6.2594</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2783044623471441</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.73117585990145</v>
+        <v>-1.1645</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3881392868310254</v>
+        <v>-0.228</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.598367876127432</v>
+        <v>-3.876</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.58</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.6909058027131054</v>
+        <v>-0.6347</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.74539864612279</v>
+        <v>-10.7899</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7505365765179191</v>
+        <v>-0.6982</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.75912180080462</v>
+        <v>-11.8694</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3754399098601928</v>
+        <v>1.2706</v>
       </c>
       <c r="J262" t="n">
-        <v>7.884238107064048</v>
+        <v>26.6826</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2830519610338044</v>
+        <v>1.0253</v>
       </c>
       <c r="J263" t="n">
-        <v>5.944091181709893</v>
+        <v>21.5313</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2285481851620601</v>
+        <v>0.8709</v>
       </c>
       <c r="J264" t="n">
-        <v>4.799511888403262</v>
+        <v>18.2889</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1.25</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1573967716996379</v>
+        <v>0.6067</v>
       </c>
       <c r="J265" t="n">
-        <v>3.305332205692397</v>
+        <v>12.7407</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3898965925228365</v>
+        <v>-0.8361</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.187828442979566</v>
+        <v>-17.5581</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.04100262424514298</v>
+        <v>0.3464</v>
       </c>
       <c r="J267" t="n">
-        <v>0.8610551091480025</v>
+        <v>7.2744</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.04800881977707952</v>
+        <v>0.2147</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.00818521531867</v>
+        <v>4.5087</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1811089103091097</v>
+        <v>-0.0725</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.803287116491304</v>
+        <v>-1.5225</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.365126395669366</v>
+        <v>-0.4001</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.667654309056686</v>
+        <v>-8.402100000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6000183955546163</v>
+        <v>-0.6909</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.60038630664694</v>
+        <v>-14.5089</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2.49</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9368238804549051</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>18.7364776090981</v>
+        <v>41.186</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2381070093270835</v>
+        <v>0.9301</v>
       </c>
       <c r="J273" t="n">
-        <v>4.762140186541669</v>
+        <v>18.602</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.03953514809872329</v>
+        <v>0.3314</v>
       </c>
       <c r="J274" t="n">
-        <v>0.7907029619744657</v>
+        <v>6.628</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.01612405075400058</v>
+        <v>0.257</v>
       </c>
       <c r="J275" t="n">
-        <v>0.3224810150800116</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.97</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2029563426884751</v>
+        <v>-0.3246</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.059126853769502</v>
+        <v>-6.492</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1470128160544494</v>
+        <v>0.5331</v>
       </c>
       <c r="J277" t="n">
-        <v>2.940256321088988</v>
+        <v>10.662</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.95</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1757261995852336</v>
+        <v>-0.024</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.514523991704672</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.66</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.471428989366134</v>
+        <v>-0.5234</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.428579787322679</v>
+        <v>-10.468</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.55</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5869169727291264</v>
+        <v>-0.67</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.73833945458253</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5972798252979485</v>
+        <v>-0.6827</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.94559650595897</v>
+        <v>-13.654</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4315618586404972</v>
+        <v>1.3223</v>
       </c>
       <c r="J282" t="n">
-        <v>12.51529390057442</v>
+        <v>38.3467</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1367734506159964</v>
+        <v>0.5406</v>
       </c>
       <c r="J283" t="n">
-        <v>3.966430067863895</v>
+        <v>15.6774</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.18</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1288227280930392</v>
+        <v>0.5122</v>
       </c>
       <c r="J284" t="n">
-        <v>3.735859114698135</v>
+        <v>14.8538</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.05645660675651752</v>
+        <v>-0.2079</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.637241595939008</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1586514814640139</v>
+        <v>-0.4631</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.600892962456403</v>
+        <v>-13.4299</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.12</v>
       </c>
       <c r="I287" t="n">
-        <v>0.06486244465997874</v>
+        <v>0.2912</v>
       </c>
       <c r="J287" t="n">
-        <v>1.881010895139384</v>
+        <v>8.444800000000001</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.004085120112540487</v>
+        <v>0.1877</v>
       </c>
       <c r="J288" t="n">
-        <v>0.1184684832636741</v>
+        <v>5.4433</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2314080022665914</v>
+        <v>-0.2837</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.710832065731152</v>
+        <v>-8.2273</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2903131142495205</v>
+        <v>-0.3622</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.419080313236094</v>
+        <v>-10.5038</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3258902665140015</v>
+        <v>-0.4065</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.450817728906044</v>
+        <v>-11.7885</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>2.39</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9930399709357178</v>
+        <v>2.0593</v>
       </c>
       <c r="J292" t="n">
-        <v>17.87471947684292</v>
+        <v>37.0674</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4478278557811283</v>
+        <v>1.3399</v>
       </c>
       <c r="J293" t="n">
-        <v>8.060901404060308</v>
+        <v>24.1182</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3273546432611762</v>
+        <v>0.9856</v>
       </c>
       <c r="J294" t="n">
-        <v>5.892383578701173</v>
+        <v>17.7408</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>1.09</v>
       </c>
       <c r="I295" t="n">
-        <v>0.01518303104223232</v>
+        <v>0.1125</v>
       </c>
       <c r="J295" t="n">
-        <v>0.2732945587601818</v>
+        <v>2.025</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.89</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2247422699754809</v>
+        <v>-0.5678</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.045360859558656</v>
+        <v>-10.2204</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.09</v>
       </c>
       <c r="I297" t="n">
-        <v>0.02035720046924978</v>
+        <v>0.3614</v>
       </c>
       <c r="J297" t="n">
-        <v>0.366429608446496</v>
+        <v>6.5052</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.145479741101999</v>
+        <v>0.0247</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.618635339835982</v>
+        <v>0.4446</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>0.42</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.7150164767396601</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>-12.87029658131388</v>
+        <v>-14.4162</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.39</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.7477525599535191</v>
+        <v>-0.8388</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.45954607916334</v>
+        <v>-15.0984</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.39</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7477525599535191</v>
+        <v>-0.8388</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.45954607916334</v>
+        <v>-15.0984</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.59</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4436459387150875</v>
+        <v>1.4312</v>
       </c>
       <c r="J302" t="n">
-        <v>10.6475025291621</v>
+        <v>34.3488</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>1.19</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1095537391816535</v>
+        <v>0.5581</v>
       </c>
       <c r="J303" t="n">
-        <v>2.629289740359685</v>
+        <v>13.3944</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>1.17</v>
       </c>
       <c r="I304" t="n">
-        <v>0.09307938206879653</v>
+        <v>0.5031</v>
       </c>
       <c r="J304" t="n">
-        <v>2.233905169651117</v>
+        <v>12.0744</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.02470951251118169</v>
+        <v>0.2125</v>
       </c>
       <c r="J305" t="n">
-        <v>0.5930283002683605</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5375418361822017</v>
+        <v>-1.0697</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.90100406837284</v>
+        <v>-25.6728</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.66</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6867780929961185</v>
+        <v>0.9396</v>
       </c>
       <c r="J307" t="n">
-        <v>16.48267423190684</v>
+        <v>22.5504</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1113281452581358</v>
+        <v>0.353</v>
       </c>
       <c r="J308" t="n">
-        <v>2.67187548619526</v>
+        <v>8.472</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>0.76</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2976033641069526</v>
+        <v>-0.4408</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.142480738566862</v>
+        <v>-10.5792</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>0.76</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2976033641069526</v>
+        <v>-0.4408</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.142480738566862</v>
+        <v>-10.5792</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3893200093642004</v>
+        <v>-0.5722</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.343680224740808</v>
+        <v>-13.7328</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3611976718106912</v>
+        <v>1.169</v>
       </c>
       <c r="J312" t="n">
-        <v>10.11353481069935</v>
+        <v>32.732</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2437996883601432</v>
+        <v>0.8696</v>
       </c>
       <c r="J313" t="n">
-        <v>6.826391274084008</v>
+        <v>24.3488</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1417039713725504</v>
+        <v>0.527</v>
       </c>
       <c r="J314" t="n">
-        <v>3.96771119843141</v>
+        <v>14.756</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>1.09</v>
       </c>
       <c r="I315" t="n">
-        <v>0.04141506809297572</v>
+        <v>0.1952</v>
       </c>
       <c r="J315" t="n">
-        <v>1.15962190660332</v>
+        <v>5.4656</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>1.01</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.04396390852319855</v>
+        <v>-0.0743</v>
       </c>
       <c r="J316" t="n">
-        <v>-1.230989438649559</v>
+        <v>-2.0804</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.14</v>
       </c>
       <c r="I317" t="n">
-        <v>0.07659471670182638</v>
+        <v>0.3318</v>
       </c>
       <c r="J317" t="n">
-        <v>2.144652067651139</v>
+        <v>9.2904</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.01315417043050507</v>
+        <v>0.2506</v>
       </c>
       <c r="J318" t="n">
-        <v>0.368316772054142</v>
+        <v>7.0168</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1133910096936509</v>
+        <v>-0.0506</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.174948271422225</v>
+        <v>-1.4168</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2422748770610073</v>
+        <v>-0.3389</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.783696557708205</v>
+        <v>-9.4892</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5402536992021831</v>
+        <v>-0.774</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.12710357766113</v>
+        <v>-21.672</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.4476</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.9452</v>
       </c>
       <c r="D2" t="n">
         <v>2.9913</v>
@@ -545,7 +545,7 @@
         <v>7.9685</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.8349</v>
       </c>
       <c r="D3" t="n">
         <v>2.7977</v>
@@ -591,7 +591,7 @@
         <v>5.9462</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.3692</v>
       </c>
       <c r="D4" t="n">
         <v>1.9808</v>
@@ -637,7 +637,7 @@
         <v>5.2624</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.2117</v>
       </c>
       <c r="D5" t="n">
         <v>1.7045</v>
@@ -683,7 +683,7 @@
         <v>5.1224</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.1795</v>
       </c>
       <c r="D6" t="n">
         <v>1.648</v>
@@ -729,7 +729,7 @@
         <v>3.5063</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8074</v>
       </c>
       <c r="D7" t="n">
         <v>0.9951</v>
@@ -775,7 +775,7 @@
         <v>3.2809</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0.904</v>
@@ -821,7 +821,7 @@
         <v>3.2514</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.7487</v>
       </c>
       <c r="D9" t="n">
         <v>0.8921</v>
@@ -867,7 +867,7 @@
         <v>3.1165</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.7176</v>
       </c>
       <c r="D10" t="n">
         <v>0.8376</v>
@@ -913,7 +913,7 @@
         <v>2.9205</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.6725</v>
       </c>
       <c r="D11" t="n">
         <v>0.7585</v>
@@ -959,7 +959,7 @@
         <v>2.8023</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6453</v>
       </c>
       <c r="D12" t="n">
         <v>0.7107</v>
@@ -1005,7 +1005,7 @@
         <v>2.0848</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.4801</v>
       </c>
       <c r="D13" t="n">
         <v>0.4209</v>
@@ -1051,7 +1051,7 @@
         <v>2.0835</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.4798</v>
       </c>
       <c r="D14" t="n">
         <v>0.4203</v>
@@ -1097,7 +1097,7 @@
         <v>1.8016</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.4148</v>
       </c>
       <c r="D15" t="n">
         <v>0.3064</v>
@@ -1143,7 +1143,7 @@
         <v>1.7698</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="D16" t="n">
         <v>0.2936</v>
@@ -1189,7 +1189,7 @@
         <v>1.6265</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3745</v>
       </c>
       <c r="D17" t="n">
         <v>0.2357</v>
@@ -1235,7 +1235,7 @@
         <v>1.5564</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3584</v>
       </c>
       <c r="D18" t="n">
         <v>0.2074</v>
@@ -1281,7 +1281,7 @@
         <v>1.3463</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="D19" t="n">
         <v>0.1225</v>
@@ -1327,7 +1327,7 @@
         <v>0.8068</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1858</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0954</v>
@@ -1373,7 +1373,7 @@
         <v>0.7914</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1822</v>
       </c>
       <c r="D21" t="n">
         <v>-0.1017</v>
@@ -1419,7 +1419,7 @@
         <v>0.7606000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1751</v>
       </c>
       <c r="D22" t="n">
         <v>-0.1141</v>
@@ -1465,7 +1465,7 @@
         <v>0.6334</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1458</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1655</v>
@@ -1511,7 +1511,7 @@
         <v>0.6333</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1458</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1655</v>
@@ -1557,7 +1557,7 @@
         <v>0.2916</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3036</v>
@@ -1603,7 +1603,7 @@
         <v>-0.09669999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>-0.0223</v>
       </c>
       <c r="D26" t="n">
         <v>-0.4604</v>
@@ -1649,7 +1649,7 @@
         <v>-0.1052</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0242</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4639</v>
@@ -1695,7 +1695,7 @@
         <v>-0.2179</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0502</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5094</v>
@@ -1741,7 +1741,7 @@
         <v>-0.2447</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0563</v>
       </c>
       <c r="D29" t="n">
         <v>-0.5202</v>
@@ -1787,7 +1787,7 @@
         <v>-0.2778</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.064</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5336</v>
@@ -1833,7 +1833,7 @@
         <v>-0.5783</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1332</v>
       </c>
       <c r="D31" t="n">
         <v>-0.655</v>
@@ -1879,7 +1879,7 @@
         <v>-0.616</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1418</v>
       </c>
       <c r="D32" t="n">
         <v>-0.6702</v>
@@ -1925,7 +1925,7 @@
         <v>-0.6765</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.1558</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6947</v>
@@ -1971,7 +1971,7 @@
         <v>-0.7518</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1731</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7251</v>
@@ -2017,7 +2017,7 @@
         <v>-0.9214</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.2122</v>
       </c>
       <c r="D35" t="n">
         <v>-0.7936</v>
@@ -2063,7 +2063,7 @@
         <v>-0.9563</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.2202</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8077</v>
@@ -2109,7 +2109,7 @@
         <v>-1.1654</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.2684</v>
       </c>
       <c r="D37" t="n">
         <v>-0.8922</v>
@@ -2155,7 +2155,7 @@
         <v>-1.3087</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.3013</v>
       </c>
       <c r="D38" t="n">
         <v>-0.95</v>
@@ -2201,7 +2201,7 @@
         <v>-1.8858</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.4342</v>
       </c>
       <c r="D39" t="n">
         <v>-1.1832</v>
@@ -2247,7 +2247,7 @@
         <v>-2.7055</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.623</v>
       </c>
       <c r="D40" t="n">
         <v>-1.5143</v>
@@ -2293,7 +2293,7 @@
         <v>-2.921</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.6726</v>
       </c>
       <c r="D41" t="n">
         <v>-1.6014</v>

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.9452</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9913</v>
+        <v>2.9216</v>
       </c>
       <c r="E2" t="n">
         <v>8.4476</v>
@@ -548,7 +548,7 @@
         <v>1.8349</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7977</v>
+        <v>2.7307</v>
       </c>
       <c r="E3" t="n">
         <v>7.9685</v>
@@ -594,7 +594,7 @@
         <v>1.3692</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9808</v>
+        <v>1.9251</v>
       </c>
       <c r="E4" t="n">
         <v>5.9462</v>
@@ -640,7 +640,7 @@
         <v>1.2117</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7045</v>
+        <v>1.6526</v>
       </c>
       <c r="E5" t="n">
         <v>5.2624</v>
@@ -686,7 +686,7 @@
         <v>1.1795</v>
       </c>
       <c r="D6" t="n">
-        <v>1.648</v>
+        <v>1.5969</v>
       </c>
       <c r="E6" t="n">
         <v>5.1224</v>
@@ -732,7 +732,7 @@
         <v>0.8074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9951</v>
+        <v>0.953</v>
       </c>
       <c r="E7" t="n">
         <v>3.5063</v>
@@ -778,7 +778,7 @@
         <v>0.7554999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.904</v>
+        <v>0.8632</v>
       </c>
       <c r="E8" t="n">
         <v>3.2809</v>
@@ -824,7 +824,7 @@
         <v>0.7487</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8921</v>
+        <v>0.8514</v>
       </c>
       <c r="E9" t="n">
         <v>3.2514</v>
@@ -870,7 +870,7 @@
         <v>0.7176</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8376</v>
+        <v>0.7977</v>
       </c>
       <c r="E10" t="n">
         <v>3.1165</v>
@@ -916,7 +916,7 @@
         <v>0.6725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7585</v>
+        <v>0.7196</v>
       </c>
       <c r="E11" t="n">
         <v>2.9205</v>
@@ -962,7 +962,7 @@
         <v>0.6453</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7107</v>
+        <v>0.6725</v>
       </c>
       <c r="E12" t="n">
         <v>2.8023</v>
@@ -1008,7 +1008,7 @@
         <v>0.4801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4209</v>
+        <v>0.3867</v>
       </c>
       <c r="E13" t="n">
         <v>2.0848</v>
@@ -1054,7 +1054,7 @@
         <v>0.4798</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4203</v>
+        <v>0.3862</v>
       </c>
       <c r="E14" t="n">
         <v>2.0835</v>
@@ -1100,7 +1100,7 @@
         <v>0.4148</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3064</v>
+        <v>0.2738</v>
       </c>
       <c r="E15" t="n">
         <v>1.8016</v>
@@ -1146,7 +1146,7 @@
         <v>0.4075</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2936</v>
+        <v>0.2612</v>
       </c>
       <c r="E16" t="n">
         <v>1.7698</v>
@@ -1192,7 +1192,7 @@
         <v>0.3745</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2357</v>
+        <v>0.2041</v>
       </c>
       <c r="E17" t="n">
         <v>1.6265</v>
@@ -1238,7 +1238,7 @@
         <v>0.3584</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2074</v>
+        <v>0.1762</v>
       </c>
       <c r="E18" t="n">
         <v>1.5564</v>
@@ -1284,7 +1284,7 @@
         <v>0.31</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1225</v>
+        <v>0.0925</v>
       </c>
       <c r="E19" t="n">
         <v>1.3463</v>
@@ -1330,7 +1330,7 @@
         <v>0.1858</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0954</v>
+        <v>-0.1225</v>
       </c>
       <c r="E20" t="n">
         <v>0.8068</v>
@@ -1376,7 +1376,7 @@
         <v>0.1822</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1017</v>
+        <v>-0.1286</v>
       </c>
       <c r="E21" t="n">
         <v>0.7914</v>
@@ -1422,7 +1422,7 @@
         <v>0.1751</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1141</v>
+        <v>-0.1409</v>
       </c>
       <c r="E22" t="n">
         <v>0.7606000000000001</v>
@@ -1468,7 +1468,7 @@
         <v>0.1458</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1655</v>
+        <v>-0.1916</v>
       </c>
       <c r="E23" t="n">
         <v>0.6334</v>
@@ -1514,7 +1514,7 @@
         <v>0.1458</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1655</v>
+        <v>-0.1916</v>
       </c>
       <c r="E24" t="n">
         <v>0.6333</v>
@@ -1560,7 +1560,7 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3036</v>
+        <v>-0.3277</v>
       </c>
       <c r="E25" t="n">
         <v>0.2916</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0223</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4604</v>
+        <v>-0.4824</v>
       </c>
       <c r="E26" t="n">
         <v>-0.09669999999999999</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0242</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4639</v>
+        <v>-0.4858</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1052</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0502</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5094</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2179</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0563</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5202</v>
+        <v>-0.5414</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2447</v>
@@ -1790,7 +1790,7 @@
         <v>-0.064</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5336</v>
+        <v>-0.5546</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2778</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1332</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.655</v>
+        <v>-0.6743</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5783</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1418</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6702</v>
+        <v>-0.6893</v>
       </c>
       <c r="E32" t="n">
         <v>-0.616</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1558</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6947</v>
+        <v>-0.7134</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6765</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1731</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7251</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7518</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2122</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7936</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9214</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2202</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8077</v>
+        <v>-0.8249</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9563</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2684</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8922</v>
+        <v>-0.9082</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1654</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3013</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.95</v>
+        <v>-0.9653</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3087</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4342</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1832</v>
+        <v>-1.1952</v>
       </c>
       <c r="E39" t="n">
         <v>-1.8858</v>
@@ -2250,7 +2250,7 @@
         <v>-0.623</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5143</v>
+        <v>-1.5218</v>
       </c>
       <c r="E40" t="n">
         <v>-2.7055</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6726</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6014</v>
+        <v>-1.6076</v>
       </c>
       <c r="E41" t="n">
         <v>-2.921</v>

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.4476</v>
+        <v>7.6282</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9452</v>
+        <v>1.7565</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9216</v>
+        <v>2.8057</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4476</v>
+        <v>7.6282</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2542</v>
+        <v>4.3458</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1934</v>
+        <v>3.2824</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5552</v>
+        <v>9.825699999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6921</v>
+        <v>5.1089</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1934</v>
+        <v>3.2824</v>
       </c>
       <c r="K2" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L2" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8855</v>
+        <v>8.391300000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.9685</v>
+        <v>7.4662</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8349</v>
+        <v>1.7192</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7307</v>
+        <v>2.7326</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9685</v>
+        <v>7.4662</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5038</v>
+        <v>3.7555</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4647</v>
+        <v>3.7107</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5593</v>
+        <v>7.7457</v>
       </c>
       <c r="I3" t="n">
-        <v>4.506</v>
+        <v>4.0274</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4647</v>
+        <v>3.7107</v>
       </c>
       <c r="K3" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="L3" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M3" t="n">
-        <v>7.970700000000001</v>
+        <v>7.7381</v>
       </c>
       <c r="N3" t="n">
-        <v>184</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9462</v>
+        <v>5.2377</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3692</v>
+        <v>1.2061</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9251</v>
+        <v>1.7265</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9462</v>
+        <v>5.2377</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4836</v>
+        <v>2.9913</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4626</v>
+        <v>2.2464</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4836</v>
+        <v>5.0533</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8235</v>
+        <v>2.6275</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4626</v>
+        <v>2.2464</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -621,7 +621,7 @@
         <v>106</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2861</v>
+        <v>4.8739</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2624</v>
+        <v>5.14</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2117</v>
+        <v>1.1836</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6526</v>
+        <v>1.6824</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2624</v>
+        <v>5.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3149</v>
+        <v>2.6245</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9475</v>
+        <v>2.5155</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3149</v>
+        <v>3.7609</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8763</v>
+        <v>1.9555</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9475</v>
+        <v>2.5155</v>
       </c>
       <c r="K5" t="n">
         <v>86</v>
@@ -667,7 +667,7 @@
         <v>98</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8238</v>
+        <v>4.471</v>
       </c>
       <c r="N5" t="n">
         <v>184</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1224</v>
+        <v>4.9218</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1795</v>
+        <v>1.1333</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5969</v>
+        <v>1.5839</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1224</v>
+        <v>4.9218</v>
       </c>
       <c r="F6" t="n">
-        <v>4.515</v>
+        <v>4.3396</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6043</v>
+        <v>9.803800000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5424</v>
+        <v>5.0975</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1498</v>
+        <v>5.6797</v>
       </c>
       <c r="N6" t="n">
         <v>219</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5063</v>
+        <v>3.4123</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8074</v>
+        <v>0.7857</v>
       </c>
       <c r="D7" t="n">
-        <v>0.953</v>
+        <v>0.9025</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5063</v>
+        <v>3.4123</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2838</v>
+        <v>3.9697</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7775</v>
+        <v>-0.5574</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6741</v>
+        <v>8.500400000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7885</v>
+        <v>4.4198</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7775</v>
+        <v>-0.5574</v>
       </c>
       <c r="K7" t="n">
         <v>170</v>
@@ -759,7 +759,7 @@
         <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.011</v>
+        <v>3.8624</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2809</v>
+        <v>3.3278</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7663</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8632</v>
+        <v>0.8643</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2809</v>
+        <v>3.3278</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2124</v>
+        <v>3.0633</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9315</v>
+        <v>0.2645</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3871</v>
+        <v>5.307</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5559</v>
+        <v>2.7594</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9315</v>
+        <v>0.2645</v>
       </c>
       <c r="K8" t="n">
         <v>165</v>
@@ -805,7 +805,7 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6244</v>
+        <v>3.0239</v>
       </c>
       <c r="N8" t="n">
         <v>208</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2514</v>
+        <v>3.0984</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7487</v>
+        <v>0.7135</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8514</v>
+        <v>0.7608</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2514</v>
+        <v>3.0984</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9632</v>
+        <v>3.7061</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2882</v>
+        <v>-0.6077</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9632</v>
+        <v>7.5716</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4017</v>
+        <v>3.9369</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2882</v>
+        <v>-0.6077</v>
       </c>
       <c r="K9" t="n">
         <v>165</v>
@@ -851,7 +851,7 @@
         <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6899</v>
+        <v>3.3292</v>
       </c>
       <c r="N9" t="n">
         <v>208</v>
@@ -860,173 +860,173 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1165</v>
+        <v>3.0867</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7176</v>
+        <v>0.7108</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7977</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1165</v>
+        <v>3.0867</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0282</v>
+        <v>3.0867</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0883</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0282</v>
+        <v>3.418</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4544</v>
+        <v>3.418</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0883</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5427</v>
+        <v>3.418</v>
       </c>
       <c r="N10" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9205</v>
+        <v>3.0821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6725</v>
+        <v>0.7097</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7196</v>
+        <v>0.7534</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9205</v>
+        <v>3.0821</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9205</v>
+        <v>2.8531</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9205</v>
+        <v>4.5662</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9205</v>
+        <v>2.3742</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="K11" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9205</v>
+        <v>2.6032</v>
       </c>
       <c r="N11" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8023</v>
+        <v>3.033</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6453</v>
+        <v>0.6984</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6725</v>
+        <v>0.7312</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8023</v>
+        <v>3.033</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8574</v>
+        <v>3.033</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0551</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8574</v>
+        <v>3.3001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.316</v>
+        <v>3.3001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0551</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="L12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2609</v>
+        <v>3.3001</v>
       </c>
       <c r="N12" t="n">
-        <v>184</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0848</v>
+        <v>2.7672</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4801</v>
+        <v>0.6372</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3867</v>
+        <v>0.6112</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0848</v>
+        <v>2.7672</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0848</v>
+        <v>2.4645</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>0.3027</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0848</v>
+        <v>3.197</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5003</v>
+        <v>1.6623</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>0.3027</v>
       </c>
       <c r="K13" t="n">
         <v>165</v>
@@ -1035,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5003</v>
+        <v>1.965</v>
       </c>
       <c r="N13" t="n">
         <v>208</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0835</v>
+        <v>2.7259</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4798</v>
+        <v>0.6277</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3862</v>
+        <v>0.5926</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0835</v>
+        <v>2.7259</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0835</v>
+        <v>3.0298</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.3039</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0835</v>
+        <v>5.1887</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0835</v>
+        <v>2.6979</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3039</v>
       </c>
       <c r="K14" t="n">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0835</v>
+        <v>2.394</v>
       </c>
       <c r="N14" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4148</v>
+        <v>0.5864</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2738</v>
+        <v>0.5117</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8016</v>
+        <v>2.5468</v>
       </c>
       <c r="N15" t="n">
         <v>161</v>
@@ -1136,369 +1136,369 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7698</v>
+        <v>2.4695</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4075</v>
+        <v>0.5686</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2612</v>
+        <v>0.4768</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7698</v>
+        <v>2.4695</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1795</v>
+        <v>3.1875</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9493</v>
+        <v>-0.718</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1795</v>
+        <v>5.7444</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1455</v>
+        <v>2.9868</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9493</v>
+        <v>-0.718</v>
       </c>
       <c r="K16" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="L16" t="n">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8038</v>
+        <v>2.2688</v>
       </c>
       <c r="N16" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6265</v>
+        <v>2.4575</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3745</v>
+        <v>0.5659</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2041</v>
+        <v>0.4714</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6265</v>
+        <v>2.4575</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3515</v>
+        <v>1.5298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.275</v>
+        <v>0.9277</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3515</v>
+        <v>1.5298</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0954</v>
+        <v>0.7954</v>
       </c>
       <c r="J17" t="n">
-        <v>0.275</v>
+        <v>0.9277</v>
       </c>
       <c r="K17" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3704</v>
+        <v>1.7231</v>
       </c>
       <c r="N17" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5564</v>
+        <v>2.438</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3584</v>
+        <v>0.5614</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1762</v>
+        <v>0.4626</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5564</v>
+        <v>2.438</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5564</v>
+        <v>0.5689</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.8691</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5564</v>
+        <v>0.5689</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5564</v>
+        <v>0.2958</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.8691</v>
       </c>
       <c r="K18" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5564</v>
+        <v>2.1649</v>
       </c>
       <c r="N18" t="n">
-        <v>161</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3463</v>
+        <v>2.3482</v>
       </c>
       <c r="C19" t="n">
-        <v>0.31</v>
+        <v>0.5407</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0925</v>
+        <v>0.4221</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3463</v>
+        <v>2.3482</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3791</v>
+        <v>2.3482</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9671999999999999</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3791</v>
+        <v>2.3482</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3073</v>
+        <v>2.3482</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9671999999999999</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2745</v>
+        <v>2.3482</v>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8068</v>
+        <v>1.8127</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1858</v>
+        <v>0.4174</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1225</v>
+        <v>0.1803</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8068</v>
+        <v>1.8127</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8068</v>
+        <v>2.7339</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.9212</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8068</v>
+        <v>4.1463</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8068</v>
+        <v>2.1559</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.9212</v>
       </c>
       <c r="K20" t="n">
         <v>170</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8068</v>
+        <v>1.2347</v>
       </c>
       <c r="N20" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7914</v>
+        <v>1.4515</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1822</v>
+        <v>0.3342</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1286</v>
+        <v>0.0173</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7914</v>
+        <v>1.4515</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7914</v>
+        <v>2.3916</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.9401</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7914</v>
+        <v>2.9403</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7914</v>
+        <v>1.5288</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.9401</v>
       </c>
       <c r="K21" t="n">
         <v>170</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7914</v>
+        <v>0.5886999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1751</v>
+        <v>0.3192</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1409</v>
+        <v>-0.0122</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.3863</v>
       </c>
       <c r="N22" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6334</v>
+        <v>1.295</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1458</v>
+        <v>0.2982</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1916</v>
+        <v>-0.0534</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6334</v>
+        <v>1.295</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6334</v>
+        <v>1.295</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6334</v>
+        <v>1.295</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3239</v>
+        <v>1.295</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>170</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3239000000000001</v>
+        <v>1.295</v>
       </c>
       <c r="N23" t="n">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6333</v>
+        <v>1.1739</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1458</v>
+        <v>0.2703</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1916</v>
+        <v>-0.1081</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6333</v>
+        <v>1.1739</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3548</v>
+        <v>0.2952</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9881</v>
+        <v>0.8787</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3548</v>
+        <v>0.2952</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2876</v>
+        <v>0.1535</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9881</v>
+        <v>0.8787</v>
       </c>
       <c r="K24" t="n">
         <v>113</v>
@@ -1541,7 +1541,7 @@
         <v>106</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7004999999999999</v>
+        <v>1.0322</v>
       </c>
       <c r="N24" t="n">
         <v>219</v>
@@ -1550,78 +1550,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>r3salt</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.2447</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3277</v>
+        <v>-0.1582</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2916</v>
+        <v>1.0629</v>
       </c>
       <c r="N25" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Norwi</t>
+          <t>r3salt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0223</v>
+        <v>0.1087</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4824</v>
+        <v>-0.425</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.4719</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0242</v>
+        <v>0.0914</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4858</v>
+        <v>-0.4589</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1052</v>
+        <v>0.3968</v>
       </c>
       <c r="N27" t="n">
         <v>113</v>
@@ -1688,216 +1688,216 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Norwi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0502</v>
+        <v>0.0561</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5281</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2179</v>
+        <v>0.2435</v>
       </c>
       <c r="N28" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0563</v>
+        <v>0.0446</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5414</v>
+        <v>-0.5505</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2447</v>
+        <v>0.1938</v>
       </c>
       <c r="N29" t="n">
-        <v>113</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2778</v>
+        <v>0.1419</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.064</v>
+        <v>0.0327</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5546</v>
+        <v>-0.574</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2778</v>
+        <v>0.1419</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7222</v>
+        <v>-0.3754</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>0.5173</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7222</v>
+        <v>-0.3754</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5854</v>
+        <v>-0.1952</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>0.5173</v>
       </c>
       <c r="K30" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L30" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4146</v>
+        <v>0.3220999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1332</v>
+        <v>0.0275</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6743</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5783</v>
+        <v>0.1193</v>
       </c>
       <c r="N31" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1418</v>
+        <v>0.0267</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6893</v>
+        <v>-0.5856</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.616</v>
+        <v>0.116</v>
       </c>
       <c r="N32" t="n">
         <v>170</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1558</v>
+        <v>-0.041</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7134</v>
+        <v>-0.7184</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6765</v>
+        <v>-0.178</v>
       </c>
       <c r="N33" t="n">
         <v>113</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7518</v>
+        <v>-0.3237</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1731</v>
+        <v>-0.0745</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.7841</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7518</v>
+        <v>-0.3237</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2709</v>
+        <v>-0.3237</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2709</v>
+        <v>-0.3237</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0301</v>
+        <v>-0.3237</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.511</v>
+        <v>-0.3237</v>
       </c>
       <c r="N34" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>deko</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2122</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8331</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9214</v>
+        <v>-0.4321</v>
       </c>
       <c r="N35" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>deko</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2202</v>
+        <v>-0.1458</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8249</v>
+        <v>-0.924</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9563</v>
+        <v>-0.6334</v>
       </c>
       <c r="N36" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2684</v>
+        <v>-0.1511</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9082</v>
+        <v>-0.9342</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1654</v>
+        <v>-0.6561</v>
       </c>
       <c r="N37" t="n">
         <v>161</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3013</v>
+        <v>-0.1946</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9653</v>
+        <v>-1.0194</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3087</v>
+        <v>-0.8449</v>
       </c>
       <c r="N38" t="n">
         <v>82</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4342</v>
+        <v>-0.3079</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1952</v>
+        <v>-1.2416</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8858</v>
+        <v>-1.3371</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7055</v>
+        <v>-2.3443</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.623</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5218</v>
+        <v>-1.6963</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.7055</v>
+        <v>-2.3443</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.907</v>
+        <v>-1.7767</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7985</v>
+        <v>-0.5676</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.907</v>
+        <v>-1.7767</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5457</v>
+        <v>-0.9238</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7985</v>
+        <v>-0.5676</v>
       </c>
       <c r="K40" t="n">
         <v>170</v>
@@ -2277,7 +2277,7 @@
         <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3442</v>
+        <v>-1.4914</v>
       </c>
       <c r="N40" t="n">
         <v>205</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.921</v>
+        <v>-4.3894</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6726</v>
+        <v>-1.0107</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6076</v>
+        <v>-2.6196</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.921</v>
+        <v>-4.3894</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.4458</v>
+        <v>-5.0622</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5248</v>
+        <v>0.6728</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.4458</v>
+        <v>-5.0622</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.7929</v>
+        <v>-2.6321</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5248</v>
+        <v>0.6728</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2681</v>
+        <v>-1.9593</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -2429,10 +2429,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9466</v>
+        <v>1.1297</v>
       </c>
       <c r="J2" t="n">
-        <v>22.7184</v>
+        <v>27.1128</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3301</v>
+        <v>0.3689</v>
       </c>
       <c r="J3" t="n">
-        <v>7.9224</v>
+        <v>8.8536</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.205</v>
+        <v>-0.1213</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.92</v>
+        <v>-2.9112</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.71</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5041</v>
+        <v>-0.3249</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.0984</v>
+        <v>-7.7976</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7849</v>
+        <v>-0.5357</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.8376</v>
+        <v>-12.8568</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7912</v>
+        <v>0.7637</v>
       </c>
       <c r="J7" t="n">
-        <v>18.9888</v>
+        <v>18.3288</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6952</v>
+        <v>0.6654</v>
       </c>
       <c r="J8" t="n">
-        <v>16.6848</v>
+        <v>15.9696</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2674</v>
+        <v>0.2708</v>
       </c>
       <c r="J9" t="n">
-        <v>6.4176</v>
+        <v>6.4992</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.93</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3445</v>
+        <v>-0.2816</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.268000000000001</v>
+        <v>-6.7584</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4896</v>
+        <v>-0.4282</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.7504</v>
+        <v>-10.2768</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2238</v>
+        <v>0.2347</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9236</v>
+        <v>5.1634</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1296</v>
+        <v>0.1233</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8512</v>
+        <v>2.7126</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0849</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8678</v>
+        <v>1.5928</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2505</v>
+        <v>-0.1523</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.511</v>
+        <v>-3.3506</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3753</v>
+        <v>-0.235</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.256600000000001</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2917</v>
+        <v>1.1849</v>
       </c>
       <c r="J17" t="n">
-        <v>28.4174</v>
+        <v>26.0678</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2917</v>
+        <v>1.1849</v>
       </c>
       <c r="J18" t="n">
-        <v>28.4174</v>
+        <v>26.0678</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5507</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>12.1154</v>
+        <v>12.386</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4701</v>
+        <v>-0.3984</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.3422</v>
+        <v>-8.764799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8632</v>
+        <v>-0.822</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.9904</v>
+        <v>-18.084</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5108</v>
+        <v>0.6039</v>
       </c>
       <c r="J22" t="n">
-        <v>8.6836</v>
+        <v>10.2663</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2983</v>
+        <v>0.312</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0711</v>
+        <v>5.304</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.248</v>
+        <v>-0.1936</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.216</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.61</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5884</v>
+        <v>-0.3921</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.0028</v>
+        <v>-6.6657</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1404</v>
+        <v>-0.8216</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.3868</v>
+        <v>-13.9672</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6625</v>
+        <v>1.4409</v>
       </c>
       <c r="J27" t="n">
-        <v>28.2625</v>
+        <v>24.4953</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5184</v>
+        <v>1.3482</v>
       </c>
       <c r="J28" t="n">
-        <v>25.8128</v>
+        <v>22.9194</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2118</v>
+        <v>1.1599</v>
       </c>
       <c r="J29" t="n">
-        <v>20.6006</v>
+        <v>19.7183</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1553</v>
+        <v>0.2503</v>
       </c>
       <c r="J30" t="n">
-        <v>2.6401</v>
+        <v>4.2551</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1885</v>
+        <v>-0.1011</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.2045</v>
+        <v>-1.7187</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8992</v>
+        <v>0.6549</v>
       </c>
       <c r="J32" t="n">
-        <v>19.7824</v>
+        <v>14.4078</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.534</v>
+        <v>0.4377</v>
       </c>
       <c r="J33" t="n">
-        <v>11.748</v>
+        <v>9.6294</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.212</v>
+        <v>0.2402</v>
       </c>
       <c r="J34" t="n">
-        <v>4.664</v>
+        <v>5.2844</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1063</v>
+        <v>0.1463</v>
       </c>
       <c r="J35" t="n">
-        <v>2.3386</v>
+        <v>3.2186</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5145</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.6302</v>
+        <v>-11.319</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3625</v>
+        <v>0.3756</v>
       </c>
       <c r="J37" t="n">
-        <v>7.975</v>
+        <v>8.263199999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2353</v>
+        <v>0.2437</v>
       </c>
       <c r="J38" t="n">
-        <v>5.1766</v>
+        <v>5.3614</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0707</v>
+        <v>-0.0582</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5554</v>
+        <v>-1.2804</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2895</v>
+        <v>-0.1805</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.369</v>
+        <v>-3.971</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6234</v>
+        <v>-0.413</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.7148</v>
+        <v>-9.086</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.88</v>
+        <v>0.6516</v>
       </c>
       <c r="J42" t="n">
-        <v>18.48</v>
+        <v>13.6836</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7405</v>
+        <v>0.5692</v>
       </c>
       <c r="J43" t="n">
-        <v>15.5505</v>
+        <v>11.9532</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7405</v>
+        <v>0.5692</v>
       </c>
       <c r="J44" t="n">
-        <v>15.5505</v>
+        <v>11.9532</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.5469</v>
+        <v>-1.9929</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2487</v>
+        <v>-0.1733</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.2227</v>
+        <v>-3.6393</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3457</v>
+        <v>0.3609</v>
       </c>
       <c r="J47" t="n">
-        <v>7.2597</v>
+        <v>7.5789</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="J48" t="n">
-        <v>3.2886</v>
+        <v>2.9757</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0529</v>
+        <v>0.0208</v>
       </c>
       <c r="J49" t="n">
-        <v>1.1109</v>
+        <v>0.4368</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4718</v>
+        <v>-0.305</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.9078</v>
+        <v>-6.405</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.59</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.642</v>
+        <v>-0.4272</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.482</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3045</v>
+        <v>0.9228</v>
       </c>
       <c r="J52" t="n">
-        <v>26.09</v>
+        <v>18.456</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.31</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7954</v>
+        <v>0.6129</v>
       </c>
       <c r="J53" t="n">
-        <v>15.908</v>
+        <v>12.258</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6149</v>
+        <v>0.519</v>
       </c>
       <c r="J54" t="n">
-        <v>12.298</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4392</v>
+        <v>0.4354</v>
       </c>
       <c r="J55" t="n">
-        <v>8.784000000000001</v>
+        <v>8.708</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.513</v>
+        <v>-0.4405</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.26</v>
+        <v>-8.81</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2367</v>
+        <v>0.2318</v>
       </c>
       <c r="J57" t="n">
-        <v>4.734</v>
+        <v>4.636</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0843</v>
+        <v>-0.0873</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.686</v>
+        <v>-1.746</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4241</v>
+        <v>-0.2817</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.481999999999999</v>
+        <v>-5.634</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4978</v>
+        <v>-0.3292</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.956</v>
+        <v>-6.584</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6071</v>
+        <v>-0.4044</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.142</v>
+        <v>-8.087999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.83</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6851</v>
+        <v>1.1928</v>
       </c>
       <c r="J62" t="n">
-        <v>25.2765</v>
+        <v>17.892</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.78</v>
       </c>
       <c r="I63" t="n">
-        <v>1.6013</v>
+        <v>1.1366</v>
       </c>
       <c r="J63" t="n">
-        <v>24.0195</v>
+        <v>17.049</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>1.127</v>
+        <v>0.8635</v>
       </c>
       <c r="J64" t="n">
-        <v>16.905</v>
+        <v>12.9525</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.35</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7081</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>10.6215</v>
+        <v>9.489000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.33</v>
+        <v>0.3977</v>
       </c>
       <c r="J66" t="n">
-        <v>4.95</v>
+        <v>5.9655</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7305</v>
+        <v>0.6959</v>
       </c>
       <c r="J67" t="n">
-        <v>10.9575</v>
+        <v>10.4385</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3744</v>
+        <v>-0.2859</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.616</v>
+        <v>-4.2885</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.51</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6932</v>
+        <v>-0.4701</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.398</v>
+        <v>-7.0515</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.44</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.5357</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.757</v>
+        <v>-8.035500000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8582</v>
+        <v>-0.592</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.873</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6087</v>
+        <v>0.5869</v>
       </c>
       <c r="J72" t="n">
-        <v>9.1305</v>
+        <v>8.8035</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.82</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1877</v>
+        <v>-0.1691</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.8155</v>
+        <v>-2.5365</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5596</v>
+        <v>-0.3829</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.394</v>
+        <v>-5.7435</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.38</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8547</v>
+        <v>-0.5893</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.8205</v>
+        <v>-8.839499999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.25</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0097</v>
+        <v>-0.7117</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.1455</v>
+        <v>-10.6755</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.29</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4116</v>
+        <v>1.2008</v>
       </c>
       <c r="J77" t="n">
-        <v>21.174</v>
+        <v>18.012</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.61</v>
       </c>
       <c r="I78" t="n">
-        <v>0.747</v>
+        <v>0.6922</v>
       </c>
       <c r="J78" t="n">
-        <v>11.205</v>
+        <v>10.383</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4771</v>
+        <v>0.481</v>
       </c>
       <c r="J79" t="n">
-        <v>7.1565</v>
+        <v>7.215</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1536</v>
+        <v>0.1875</v>
       </c>
       <c r="J80" t="n">
-        <v>2.304</v>
+        <v>2.8125</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0395</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.5925</v>
+        <v>0.1395</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4058</v>
+        <v>1.2639</v>
       </c>
       <c r="J82" t="n">
-        <v>26.7102</v>
+        <v>24.0141</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0253</v>
+        <v>1.022</v>
       </c>
       <c r="J83" t="n">
-        <v>19.4807</v>
+        <v>19.418</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4227</v>
+        <v>0.4997</v>
       </c>
       <c r="J84" t="n">
-        <v>8.0313</v>
+        <v>9.494300000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J85" t="n">
-        <v>1.7195</v>
+        <v>3.2034</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.059</v>
+        <v>0.1368</v>
       </c>
       <c r="J86" t="n">
-        <v>1.121</v>
+        <v>2.5992</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6851</v>
+        <v>0.8451</v>
       </c>
       <c r="J87" t="n">
-        <v>13.0169</v>
+        <v>16.0569</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0031</v>
+        <v>-0.0246</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.0589</v>
+        <v>-0.4674</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3046</v>
+        <v>-0.1955</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.7874</v>
+        <v>-3.7145</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4411</v>
+        <v>-0.2845</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.3809</v>
+        <v>-5.4055</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7496</v>
+        <v>-0.5083</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.2424</v>
+        <v>-9.6577</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3144</v>
+        <v>1.2044</v>
       </c>
       <c r="J92" t="n">
-        <v>26.288</v>
+        <v>24.088</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8537</v>
+        <v>0.8699</v>
       </c>
       <c r="J93" t="n">
-        <v>17.074</v>
+        <v>17.398</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4803</v>
+        <v>0.5511</v>
       </c>
       <c r="J94" t="n">
-        <v>9.606</v>
+        <v>11.022</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2678</v>
+        <v>0.3454</v>
       </c>
       <c r="J95" t="n">
-        <v>5.356</v>
+        <v>6.908</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0625</v>
+        <v>0.1391</v>
       </c>
       <c r="J96" t="n">
-        <v>1.25</v>
+        <v>2.782</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4066</v>
+        <v>0.4579</v>
       </c>
       <c r="J97" t="n">
-        <v>8.132</v>
+        <v>9.157999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.84</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2715</v>
+        <v>-0.182</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.43</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3398</v>
+        <v>-0.2217</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.796</v>
+        <v>-4.434</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3714</v>
+        <v>-0.2413</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.428</v>
+        <v>-4.826</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5021</v>
+        <v>-0.3281</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.042</v>
+        <v>-6.562</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0611</v>
+        <v>1.0379</v>
       </c>
       <c r="J102" t="n">
-        <v>24.4053</v>
+        <v>23.8717</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9318</v>
+        <v>0.9308</v>
       </c>
       <c r="J103" t="n">
-        <v>21.4314</v>
+        <v>21.4084</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.19</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4993</v>
+        <v>0.5374</v>
       </c>
       <c r="J104" t="n">
-        <v>11.4839</v>
+        <v>12.3602</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0204</v>
+        <v>0.0489</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.4692</v>
+        <v>1.1247</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.98</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2215</v>
+        <v>-0.1432</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.0945</v>
+        <v>-3.2936</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4346</v>
+        <v>0.499</v>
       </c>
       <c r="J107" t="n">
-        <v>9.995799999999999</v>
+        <v>11.477</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0373</v>
+        <v>0.0114</v>
       </c>
       <c r="J108" t="n">
-        <v>0.8579</v>
+        <v>0.2622</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>0.002</v>
+        <v>-0.015</v>
       </c>
       <c r="J109" t="n">
-        <v>0.046</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4108</v>
+        <v>-0.2611</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.448399999999999</v>
+        <v>-6.0053</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.7</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5075</v>
+        <v>-0.3287</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.6725</v>
+        <v>-7.5601</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8417</v>
       </c>
       <c r="J112" t="n">
-        <v>15.1974</v>
+        <v>15.1506</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4417</v>
+        <v>-0.2965</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.9506</v>
+        <v>-5.337</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.61</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5855</v>
+        <v>-0.3906</v>
       </c>
       <c r="J114" t="n">
-        <v>-10.539</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.53</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6904</v>
+        <v>-0.4652</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.4272</v>
+        <v>-8.3736</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7282</v>
+        <v>-0.493</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.1076</v>
+        <v>-8.874000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.9</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0738</v>
+        <v>0.9853</v>
       </c>
       <c r="J117" t="n">
-        <v>19.3284</v>
+        <v>17.7354</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7517</v>
+        <v>0.6849</v>
       </c>
       <c r="J118" t="n">
-        <v>13.5306</v>
+        <v>12.3282</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.28</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3486</v>
+        <v>0.3579</v>
       </c>
       <c r="J119" t="n">
-        <v>6.2748</v>
+        <v>6.4422</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.26</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3219</v>
+        <v>0.3346</v>
       </c>
       <c r="J120" t="n">
-        <v>5.7942</v>
+        <v>6.0228</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.236</v>
+        <v>-0.1258</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.248</v>
+        <v>-2.2644</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8811</v>
+        <v>0.8738</v>
       </c>
       <c r="J122" t="n">
-        <v>18.5031</v>
+        <v>18.3498</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7892</v>
+        <v>0.7809</v>
       </c>
       <c r="J123" t="n">
-        <v>16.5732</v>
+        <v>16.3989</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5636</v>
+        <v>0.5662</v>
       </c>
       <c r="J124" t="n">
-        <v>11.8356</v>
+        <v>11.8902</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3743</v>
+        <v>0.4184</v>
       </c>
       <c r="J125" t="n">
-        <v>7.8603</v>
+        <v>8.7864</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.5069</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.0141</v>
+        <v>-10.6449</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4967</v>
+        <v>0.5806</v>
       </c>
       <c r="J127" t="n">
-        <v>10.4307</v>
+        <v>12.1926</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4126</v>
+        <v>0.4668</v>
       </c>
       <c r="J128" t="n">
-        <v>8.6646</v>
+        <v>9.8028</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4237</v>
+        <v>-0.2735</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.8977</v>
+        <v>-5.7435</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4942</v>
+        <v>-0.3216</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.3782</v>
+        <v>-6.7536</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7362</v>
+        <v>-0.4981</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.4602</v>
+        <v>-10.4601</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.87</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1466</v>
+        <v>-0.134</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.6388</v>
+        <v>-2.412</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.85</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.18</v>
+        <v>-0.1561</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.24</v>
+        <v>-2.8098</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2628</v>
+        <v>-0.2086</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.7304</v>
+        <v>-3.7548</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2628</v>
+        <v>-0.2086</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.7304</v>
+        <v>-3.7548</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8455</v>
+        <v>-0.5821</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.219</v>
+        <v>-10.4778</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.75</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6182</v>
+        <v>1.4083</v>
       </c>
       <c r="J137" t="n">
-        <v>29.1276</v>
+        <v>25.3494</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0142</v>
+        <v>1.0333</v>
       </c>
       <c r="J138" t="n">
-        <v>18.2556</v>
+        <v>18.5994</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.33</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7382</v>
+        <v>0.8288</v>
       </c>
       <c r="J139" t="n">
-        <v>13.2876</v>
+        <v>14.9184</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5246</v>
+        <v>0.6241</v>
       </c>
       <c r="J140" t="n">
-        <v>9.4428</v>
+        <v>11.2338</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.07</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0883</v>
+        <v>0.1761</v>
       </c>
       <c r="J141" t="n">
-        <v>1.5894</v>
+        <v>3.1698</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.38</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6509</v>
+        <v>0.7951</v>
       </c>
       <c r="J142" t="n">
-        <v>14.9707</v>
+        <v>18.2873</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2255</v>
+        <v>0.2287</v>
       </c>
       <c r="J143" t="n">
-        <v>5.1865</v>
+        <v>5.2601</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2077</v>
+        <v>0.2066</v>
       </c>
       <c r="J144" t="n">
-        <v>4.7771</v>
+        <v>4.7518</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.54</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7058</v>
+        <v>-0.4749</v>
       </c>
       <c r="J145" t="n">
-        <v>-16.2334</v>
+        <v>-10.9227</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7415</v>
+        <v>-0.5021</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.0545</v>
+        <v>-11.5483</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.51</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2471</v>
+        <v>1.1568</v>
       </c>
       <c r="J147" t="n">
-        <v>28.6833</v>
+        <v>26.6064</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7502</v>
+        <v>0.75</v>
       </c>
       <c r="J148" t="n">
-        <v>17.2546</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5067</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>11.6541</v>
+        <v>12.3694</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1819</v>
+        <v>0.2472</v>
       </c>
       <c r="J150" t="n">
-        <v>4.1837</v>
+        <v>5.6856</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5006</v>
+        <v>-0.4297</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.5138</v>
+        <v>-9.883100000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7293</v>
+        <v>1.4803</v>
       </c>
       <c r="J152" t="n">
-        <v>41.5032</v>
+        <v>35.5272</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.386</v>
+        <v>0.3773</v>
       </c>
       <c r="J153" t="n">
-        <v>9.263999999999999</v>
+        <v>9.055199999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.386</v>
+        <v>0.3773</v>
       </c>
       <c r="J154" t="n">
-        <v>9.263999999999999</v>
+        <v>9.055199999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2887</v>
+        <v>-0.2231</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.9288</v>
+        <v>-5.3544</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.2469</v>
+        <v>-1.2558</v>
       </c>
       <c r="J156" t="n">
-        <v>-29.9256</v>
+        <v>-30.1392</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.18</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3679</v>
+        <v>0.4142</v>
       </c>
       <c r="J157" t="n">
-        <v>8.829599999999999</v>
+        <v>9.940799999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.98</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0379</v>
+        <v>-0.0334</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.9096</v>
+        <v>-0.8016</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0634</v>
+        <v>-0.0473</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.5216</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1166</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.7984</v>
+        <v>-1.7376</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4728</v>
+        <v>-0.3032</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.3472</v>
+        <v>-7.2768</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2001</v>
+        <v>1.1277</v>
       </c>
       <c r="J162" t="n">
-        <v>25.2021</v>
+        <v>23.6817</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0348</v>
+        <v>1.0204</v>
       </c>
       <c r="J163" t="n">
-        <v>21.7308</v>
+        <v>21.4284</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7896</v>
+        <v>0.7924</v>
       </c>
       <c r="J164" t="n">
-        <v>16.5816</v>
+        <v>16.6404</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4033</v>
+        <v>0.4618</v>
       </c>
       <c r="J165" t="n">
-        <v>8.4693</v>
+        <v>9.697800000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0413</v>
+        <v>-1.0214</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.8673</v>
+        <v>-21.4494</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.09</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2429</v>
+        <v>0.2503</v>
       </c>
       <c r="J167" t="n">
-        <v>5.1009</v>
+        <v>5.2563</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1701</v>
+        <v>0.1608</v>
       </c>
       <c r="J168" t="n">
-        <v>3.5721</v>
+        <v>3.3768</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2985</v>
+        <v>-0.1884</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.2685</v>
+        <v>-3.9564</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3145</v>
+        <v>-0.1986</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.6045</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4054</v>
+        <v>-0.2586</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.513400000000001</v>
+        <v>-5.4306</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.94</v>
       </c>
       <c r="I172" t="n">
-        <v>1.9106</v>
+        <v>1.6122</v>
       </c>
       <c r="J172" t="n">
-        <v>32.4802</v>
+        <v>27.4074</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.8357</v>
+        <v>1.5555</v>
       </c>
       <c r="J173" t="n">
-        <v>31.2069</v>
+        <v>26.4435</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.26</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5464</v>
+        <v>0.658</v>
       </c>
       <c r="J174" t="n">
-        <v>9.2888</v>
+        <v>11.186</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2084</v>
+        <v>0.306</v>
       </c>
       <c r="J175" t="n">
-        <v>3.5428</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4181</v>
+        <v>-0.3343</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.1077</v>
+        <v>-5.6831</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.91</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0795</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.3515</v>
+        <v>-1.5028</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0795</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.3515</v>
+        <v>-1.5028</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.78</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2989</v>
+        <v>-0.2291</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.0813</v>
+        <v>-3.8947</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3346</v>
+        <v>-0.2481</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.6882</v>
+        <v>-4.2177</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8699</v>
+        <v>-0.601</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.7883</v>
+        <v>-10.217</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.654</v>
+        <v>0.6112</v>
       </c>
       <c r="J182" t="n">
-        <v>18.966</v>
+        <v>17.7248</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.98</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0477</v>
+        <v>-0.0344</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.3833</v>
+        <v>-0.9976</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1838</v>
+        <v>-0.1091</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.3302</v>
+        <v>-3.1639</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.82</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3483</v>
+        <v>-0.216</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.1007</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4347</v>
+        <v>-0.2757</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.6063</v>
+        <v>-7.9953</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.92</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1525</v>
+        <v>1.0442</v>
       </c>
       <c r="J187" t="n">
-        <v>33.4225</v>
+        <v>30.2818</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.12</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1788</v>
+        <v>0.1833</v>
       </c>
       <c r="J188" t="n">
-        <v>5.1852</v>
+        <v>5.3157</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1277</v>
+        <v>0.1413</v>
       </c>
       <c r="J189" t="n">
-        <v>3.7033</v>
+        <v>4.0977</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1829</v>
+        <v>-0.0934</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.3041</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4556</v>
+        <v>-0.2865</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.2124</v>
+        <v>-8.3085</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.8</v>
       </c>
       <c r="I192" t="n">
-        <v>1.681</v>
+        <v>1.4529</v>
       </c>
       <c r="J192" t="n">
-        <v>25.215</v>
+        <v>21.7935</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.67</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4453</v>
+        <v>1.302</v>
       </c>
       <c r="J193" t="n">
-        <v>21.6795</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.54</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1925</v>
+        <v>1.1484</v>
       </c>
       <c r="J194" t="n">
-        <v>17.8875</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2855</v>
+        <v>0.3868</v>
       </c>
       <c r="J195" t="n">
-        <v>4.2825</v>
+        <v>5.802</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.98</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2859</v>
+        <v>-0.1966</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.2885</v>
+        <v>-2.949</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.122</v>
+        <v>-1.341</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1085</v>
+        <v>-0.1133</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.6275</v>
+        <v>-1.6995</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3008</v>
+        <v>-0.2441</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.512</v>
+        <v>-3.6615</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7418</v>
+        <v>-0.5052</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.127</v>
+        <v>-7.578</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.35</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8921</v>
+        <v>-0.6181</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.3815</v>
+        <v>-9.2715</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7136</v>
+        <v>0.6369</v>
       </c>
       <c r="J202" t="n">
-        <v>15.6992</v>
+        <v>14.0118</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.36</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5206</v>
+        <v>0.4614</v>
       </c>
       <c r="J203" t="n">
-        <v>11.4532</v>
+        <v>10.1508</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.25</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3656</v>
+        <v>0.3368</v>
       </c>
       <c r="J204" t="n">
-        <v>8.043200000000001</v>
+        <v>7.4096</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.141</v>
+        <v>0.1613</v>
       </c>
       <c r="J205" t="n">
-        <v>3.102</v>
+        <v>3.5486</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1579</v>
+        <v>-0.074</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.4738</v>
+        <v>-1.628</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5294</v>
+        <v>0.4793</v>
       </c>
       <c r="J207" t="n">
-        <v>11.6468</v>
+        <v>10.5446</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4063</v>
+        <v>0.3532</v>
       </c>
       <c r="J208" t="n">
-        <v>8.938599999999999</v>
+        <v>7.7704</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3818</v>
+        <v>-0.2413</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.3996</v>
+        <v>-5.3086</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5075</v>
+        <v>-0.3287</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.165</v>
+        <v>-7.2314</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.7</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5075</v>
+        <v>-0.3287</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.165</v>
+        <v>-7.2314</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.604</v>
+        <v>0.7318</v>
       </c>
       <c r="J212" t="n">
-        <v>13.892</v>
+        <v>16.8314</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2886</v>
+        <v>0.3013</v>
       </c>
       <c r="J213" t="n">
-        <v>6.6378</v>
+        <v>6.9299</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.73</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4406</v>
+        <v>-0.2877</v>
       </c>
       <c r="J214" t="n">
-        <v>-10.1338</v>
+        <v>-6.6171</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6684</v>
+        <v>-0.4476</v>
       </c>
       <c r="J215" t="n">
-        <v>-15.3732</v>
+        <v>-10.2948</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7421</v>
+        <v>-0.5028</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.0683</v>
+        <v>-11.5644</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.34</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8796</v>
+        <v>0.8825</v>
       </c>
       <c r="J217" t="n">
-        <v>20.2308</v>
+        <v>20.2975</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.24</v>
       </c>
       <c r="I218" t="n">
-        <v>0.638</v>
+        <v>0.6524</v>
       </c>
       <c r="J218" t="n">
-        <v>14.674</v>
+        <v>15.0052</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.23</v>
       </c>
       <c r="I219" t="n">
-        <v>0.611</v>
+        <v>0.629</v>
       </c>
       <c r="J219" t="n">
-        <v>14.053</v>
+        <v>14.467</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4285</v>
+        <v>0.4862</v>
       </c>
       <c r="J220" t="n">
-        <v>9.855499999999999</v>
+        <v>11.1826</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1122</v>
+        <v>0.1822</v>
       </c>
       <c r="J221" t="n">
-        <v>2.5806</v>
+        <v>4.1906</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2058</v>
+        <v>0.1914</v>
       </c>
       <c r="J222" t="n">
-        <v>3.2928</v>
+        <v>3.0624</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0956</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.5072</v>
+        <v>-1.5296</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1809</v>
+        <v>-0.1522</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.8944</v>
+        <v>-2.4352</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.59</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6156</v>
+        <v>-0.4111</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.849600000000001</v>
+        <v>-6.5776</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.5</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7306</v>
+        <v>-0.4947</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.6896</v>
+        <v>-7.9152</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.93</v>
       </c>
       <c r="I227" t="n">
-        <v>1.909</v>
+        <v>1.6099</v>
       </c>
       <c r="J227" t="n">
-        <v>30.544</v>
+        <v>25.7584</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.76</v>
       </c>
       <c r="I228" t="n">
-        <v>1.6242</v>
+        <v>1.4138</v>
       </c>
       <c r="J228" t="n">
-        <v>25.9872</v>
+        <v>22.6208</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.65</v>
       </c>
       <c r="I229" t="n">
-        <v>1.4226</v>
+        <v>1.2846</v>
       </c>
       <c r="J229" t="n">
-        <v>22.7616</v>
+        <v>20.5536</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6751</v>
+        <v>-0.6122</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.8016</v>
+        <v>-9.795199999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.79</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.792</v>
+        <v>-0.7415</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.672</v>
+        <v>-11.864</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7079</v>
+        <v>1.4646</v>
       </c>
       <c r="J232" t="n">
-        <v>34.158</v>
+        <v>29.292</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.859</v>
+        <v>0.8849</v>
       </c>
       <c r="J233" t="n">
-        <v>17.18</v>
+        <v>17.698</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.27</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6445</v>
+        <v>0.7093</v>
       </c>
       <c r="J234" t="n">
-        <v>12.89</v>
+        <v>14.186</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.24</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5656</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>11.312</v>
+        <v>12.812</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7948</v>
+        <v>-0.745</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.896</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.44</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7712</v>
+        <v>0.9754</v>
       </c>
       <c r="J237" t="n">
-        <v>15.424</v>
+        <v>19.508</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.4835</v>
+        <v>-0.3197</v>
       </c>
       <c r="J238" t="n">
-        <v>-9.67</v>
+        <v>-6.394</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.526</v>
+        <v>-0.3481</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.52</v>
+        <v>-6.962</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5536</v>
+        <v>-0.3669</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.072</v>
+        <v>-7.338</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.659</v>
+        <v>-0.4417</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.18</v>
+        <v>-8.834</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.23</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4379</v>
+        <v>0.3868</v>
       </c>
       <c r="J242" t="n">
-        <v>12.6991</v>
+        <v>11.2172</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3366</v>
+        <v>0.2867</v>
       </c>
       <c r="J243" t="n">
-        <v>9.7614</v>
+        <v>8.314299999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.06</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1694</v>
+        <v>0.1299</v>
       </c>
       <c r="J244" t="n">
-        <v>4.9126</v>
+        <v>3.7671</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4324</v>
+        <v>-0.2745</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.5396</v>
+        <v>-7.9605</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6161</v>
+        <v>-0.4072</v>
       </c>
       <c r="J246" t="n">
-        <v>-17.8669</v>
+        <v>-11.8088</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7599</v>
+        <v>0.6757</v>
       </c>
       <c r="J247" t="n">
-        <v>22.0371</v>
+        <v>19.5953</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.35</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5457</v>
+        <v>0.471</v>
       </c>
       <c r="J248" t="n">
-        <v>15.8253</v>
+        <v>13.659</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0516</v>
+        <v>-0.0108</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.4964</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2903</v>
+        <v>-0.1692</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.418699999999999</v>
+        <v>-4.9068</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3504</v>
+        <v>-0.2115</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1616</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.84</v>
       </c>
       <c r="I252" t="n">
-        <v>1.79</v>
+        <v>1.5212</v>
       </c>
       <c r="J252" t="n">
-        <v>30.43</v>
+        <v>25.8604</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.46</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0731</v>
+        <v>1.0641</v>
       </c>
       <c r="J253" t="n">
-        <v>18.2427</v>
+        <v>18.0897</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6539</v>
       </c>
       <c r="J254" t="n">
-        <v>9.554</v>
+        <v>11.1163</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.22</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4893</v>
+        <v>0.5826</v>
       </c>
       <c r="J255" t="n">
-        <v>8.318099999999999</v>
+        <v>9.904199999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4838</v>
+        <v>-0.4059</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.224600000000001</v>
+        <v>-6.9003</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3682</v>
+        <v>0.4055</v>
       </c>
       <c r="J257" t="n">
-        <v>6.2594</v>
+        <v>6.8935</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.1645</v>
+        <v>-1.2971</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.876</v>
+        <v>-3.0073</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.58</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.6347</v>
+        <v>-0.4239</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.7899</v>
+        <v>-7.2063</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6982</v>
+        <v>-0.4703</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.8694</v>
+        <v>-7.9951</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2706</v>
+        <v>1.1772</v>
       </c>
       <c r="J262" t="n">
-        <v>26.6826</v>
+        <v>24.7212</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0253</v>
+        <v>1.022</v>
       </c>
       <c r="J263" t="n">
-        <v>21.5313</v>
+        <v>21.462</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8709</v>
+        <v>0.8895</v>
       </c>
       <c r="J264" t="n">
-        <v>18.2889</v>
+        <v>18.6795</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.25</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6067</v>
+        <v>0.6671</v>
       </c>
       <c r="J265" t="n">
-        <v>12.7407</v>
+        <v>14.0091</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8361</v>
+        <v>-0.791</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.5581</v>
+        <v>-16.611</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3464</v>
+        <v>0.3804</v>
       </c>
       <c r="J267" t="n">
-        <v>7.2744</v>
+        <v>7.9884</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2147</v>
+        <v>0.2127</v>
       </c>
       <c r="J268" t="n">
-        <v>4.5087</v>
+        <v>4.4667</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0725</v>
+        <v>-0.0667</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.5225</v>
+        <v>-1.4007</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4001</v>
+        <v>-0.2563</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.402100000000001</v>
+        <v>-5.3823</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6909</v>
+        <v>-0.4637</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.5089</v>
+        <v>-9.7377</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.49</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9301</v>
+        <v>1.0111</v>
       </c>
       <c r="J273" t="n">
-        <v>18.602</v>
+        <v>20.222</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3314</v>
+        <v>0.4361</v>
       </c>
       <c r="J274" t="n">
-        <v>6.628</v>
+        <v>8.722</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.257</v>
+        <v>0.3579</v>
       </c>
       <c r="J275" t="n">
-        <v>5.14</v>
+        <v>7.158</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.97</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3246</v>
+        <v>-0.2362</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.492</v>
+        <v>-4.724</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5331</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>10.662</v>
+        <v>12.692</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.95</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.024</v>
+        <v>-0.0479</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.48</v>
+        <v>-0.958</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.66</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5234</v>
+        <v>-0.3469</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.468</v>
+        <v>-6.938</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.55</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.67</v>
+        <v>-0.4498</v>
       </c>
       <c r="J280" t="n">
-        <v>-13.4</v>
+        <v>-8.996</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6827</v>
+        <v>-0.4591</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.654</v>
+        <v>-9.182</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3223</v>
+        <v>1.204</v>
       </c>
       <c r="J282" t="n">
-        <v>38.3467</v>
+        <v>34.916</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5406</v>
+        <v>0.543</v>
       </c>
       <c r="J283" t="n">
-        <v>15.6774</v>
+        <v>15.747</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.18</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5122</v>
+        <v>0.5185</v>
       </c>
       <c r="J284" t="n">
-        <v>14.8538</v>
+        <v>15.0365</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2079</v>
+        <v>-0.134</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.0291</v>
+        <v>-3.886</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4631</v>
+        <v>-0.3928</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.4299</v>
+        <v>-11.3912</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.12</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2912</v>
+        <v>0.3115</v>
       </c>
       <c r="J287" t="n">
-        <v>8.444800000000001</v>
+        <v>9.0335</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1877</v>
+        <v>0.1828</v>
       </c>
       <c r="J288" t="n">
-        <v>5.4433</v>
+        <v>5.3012</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2837</v>
+        <v>-0.1786</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.2273</v>
+        <v>-5.1794</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3622</v>
+        <v>-0.2294</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.5038</v>
+        <v>-6.6526</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4065</v>
+        <v>-0.2591</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.7885</v>
+        <v>-7.5139</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.39</v>
       </c>
       <c r="I292" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J292" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3399</v>
+        <v>1.2452</v>
       </c>
       <c r="J293" t="n">
-        <v>24.1182</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9856</v>
+        <v>1.0596</v>
       </c>
       <c r="J294" t="n">
-        <v>17.7408</v>
+        <v>19.0728</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.09</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1125</v>
+        <v>0.2085</v>
       </c>
       <c r="J295" t="n">
-        <v>2.025</v>
+        <v>3.753</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.89</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5678</v>
+        <v>-0.4945</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.2204</v>
+        <v>-8.901</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.09</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3614</v>
+        <v>0.4092</v>
       </c>
       <c r="J297" t="n">
-        <v>6.5052</v>
+        <v>7.3656</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0247</v>
+        <v>-0.0178</v>
       </c>
       <c r="J298" t="n">
-        <v>0.4446</v>
+        <v>-0.3204</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.42</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.549</v>
       </c>
       <c r="J299" t="n">
-        <v>-14.4162</v>
+        <v>-9.882</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.39</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.8388</v>
+        <v>-0.5774</v>
       </c>
       <c r="J300" t="n">
-        <v>-15.0984</v>
+        <v>-10.3932</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.39</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8388</v>
+        <v>-0.5774</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.0984</v>
+        <v>-10.3932</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.59</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4312</v>
+        <v>1.2755</v>
       </c>
       <c r="J302" t="n">
-        <v>34.3488</v>
+        <v>30.612</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.19</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5581</v>
+        <v>0.5486</v>
       </c>
       <c r="J303" t="n">
-        <v>13.3944</v>
+        <v>13.1664</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.17</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5031</v>
+        <v>0.4986</v>
       </c>
       <c r="J304" t="n">
-        <v>12.0744</v>
+        <v>11.9664</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2125</v>
+        <v>0.2603</v>
       </c>
       <c r="J305" t="n">
-        <v>5.1</v>
+        <v>6.2472</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0697</v>
+        <v>-1.0536</v>
       </c>
       <c r="J306" t="n">
-        <v>-25.6728</v>
+        <v>-25.2864</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.66</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9396</v>
+        <v>1.1227</v>
       </c>
       <c r="J307" t="n">
-        <v>22.5504</v>
+        <v>26.9448</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.353</v>
+        <v>0.4004</v>
       </c>
       <c r="J308" t="n">
-        <v>8.472</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.76</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J309" t="n">
-        <v>-10.5792</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.76</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.5792</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5722</v>
+        <v>-0.3743</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.7328</v>
+        <v>-8.9832</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.169</v>
+        <v>1.1098</v>
       </c>
       <c r="J312" t="n">
-        <v>32.732</v>
+        <v>31.0744</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8696</v>
+        <v>0.8773</v>
       </c>
       <c r="J313" t="n">
-        <v>24.3488</v>
+        <v>24.5644</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.527</v>
+        <v>0.5803</v>
       </c>
       <c r="J314" t="n">
-        <v>14.756</v>
+        <v>16.2484</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.09</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1952</v>
+        <v>0.2678</v>
       </c>
       <c r="J315" t="n">
-        <v>5.4656</v>
+        <v>7.4984</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.01</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0743</v>
+        <v>-0.0002</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.0804</v>
+        <v>-0.0056</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.14</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3318</v>
+        <v>0.3612</v>
       </c>
       <c r="J317" t="n">
-        <v>9.2904</v>
+        <v>10.1136</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2506</v>
+        <v>0.2574</v>
       </c>
       <c r="J318" t="n">
-        <v>7.0168</v>
+        <v>7.2072</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0506</v>
+        <v>-0.0535</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.4168</v>
+        <v>-1.498</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3389</v>
+        <v>-0.2164</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.4892</v>
+        <v>-6.0592</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.774</v>
+        <v>-0.5271</v>
       </c>
       <c r="J321" t="n">
-        <v>-21.672</v>
+        <v>-14.7588</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6282</v>
+        <v>7.782</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7565</v>
+        <v>1.7919</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8057</v>
+        <v>2.9183</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6282</v>
+        <v>7.782</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3458</v>
+        <v>4.3615</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2824</v>
+        <v>3.4205</v>
       </c>
       <c r="H2" t="n">
-        <v>9.825699999999999</v>
+        <v>9.495900000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1089</v>
+        <v>5.1277</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2824</v>
+        <v>3.4205</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>98</v>
       </c>
       <c r="M2" t="n">
-        <v>8.391300000000001</v>
+        <v>8.5482</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4662</v>
+        <v>7.4828</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7192</v>
+        <v>1.723</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7326</v>
+        <v>2.7821</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4662</v>
+        <v>7.4828</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7555</v>
+        <v>3.6867</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7107</v>
+        <v>3.7961</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7457</v>
+        <v>7.2696</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0274</v>
+        <v>3.9255</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7107</v>
+        <v>3.7961</v>
       </c>
       <c r="K3" t="n">
         <v>113</v>
@@ -575,7 +575,7 @@
         <v>106</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7381</v>
+        <v>7.7216</v>
       </c>
       <c r="N3" t="n">
         <v>219</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2377</v>
+        <v>5.3279</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2061</v>
+        <v>1.2268</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7265</v>
+        <v>1.8012</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2377</v>
+        <v>5.3279</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9913</v>
+        <v>2.9553</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2464</v>
+        <v>2.3726</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0533</v>
+        <v>4.8566</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6275</v>
+        <v>2.6225</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2464</v>
+        <v>2.3726</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -621,7 +621,7 @@
         <v>106</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8739</v>
+        <v>4.9951</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.14</v>
+        <v>5.2407</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1836</v>
+        <v>1.2067</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6824</v>
+        <v>1.7615</v>
       </c>
       <c r="E5" t="n">
-        <v>5.14</v>
+        <v>5.2407</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6245</v>
+        <v>2.543</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5155</v>
+        <v>2.6976</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7609</v>
+        <v>3.4962</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9555</v>
+        <v>1.8879</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5155</v>
+        <v>2.6976</v>
       </c>
       <c r="K5" t="n">
         <v>86</v>
@@ -667,7 +667,7 @@
         <v>98</v>
       </c>
       <c r="M5" t="n">
-        <v>4.471</v>
+        <v>4.5855</v>
       </c>
       <c r="N5" t="n">
         <v>184</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9218</v>
+        <v>5.0608</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1333</v>
+        <v>1.1653</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5839</v>
+        <v>1.6796</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9218</v>
+        <v>5.0608</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3396</v>
+        <v>4.3099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.7509</v>
       </c>
       <c r="H6" t="n">
-        <v>9.803800000000001</v>
+        <v>9.325900000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0975</v>
+        <v>5.0359</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.7509</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>5.6797</v>
+        <v>5.786799999999999</v>
       </c>
       <c r="N6" t="n">
         <v>219</v>
@@ -722,461 +722,461 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4123</v>
+        <v>3.2643</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7857</v>
+        <v>0.7517</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9025</v>
+        <v>0.8618</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4123</v>
+        <v>3.2643</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9697</v>
+        <v>3.0038</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5574</v>
+        <v>0.2605</v>
       </c>
       <c r="H7" t="n">
-        <v>8.500400000000001</v>
+        <v>5.0164</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4198</v>
+        <v>2.7088</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5574</v>
+        <v>0.2605</v>
       </c>
       <c r="K7" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L7" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8624</v>
+        <v>2.9693</v>
       </c>
       <c r="N7" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3278</v>
+        <v>3.2635</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7663</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8643</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3278</v>
+        <v>3.2635</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0633</v>
+        <v>3.851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2645</v>
+        <v>-0.5875</v>
       </c>
       <c r="H8" t="n">
-        <v>5.307</v>
+        <v>7.8118</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7594</v>
+        <v>4.2183</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2645</v>
+        <v>-0.5875</v>
       </c>
       <c r="K8" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0239</v>
+        <v>3.6308</v>
       </c>
       <c r="N8" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0984</v>
+        <v>3.1391</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7135</v>
+        <v>0.7228</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7608</v>
+        <v>0.8048</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0984</v>
+        <v>3.1391</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7061</v>
+        <v>2.8018</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6077</v>
+        <v>0.3373</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5716</v>
+        <v>4.3501</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9369</v>
+        <v>2.349</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6077</v>
+        <v>0.3373</v>
       </c>
       <c r="K9" t="n">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3292</v>
+        <v>2.6863</v>
       </c>
       <c r="N9" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0867</v>
+        <v>2.9906</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7108</v>
+        <v>0.6886</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7372</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0867</v>
+        <v>2.9906</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0867</v>
+        <v>3.6235</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.6329</v>
       </c>
       <c r="H10" t="n">
-        <v>3.418</v>
+        <v>7.061</v>
       </c>
       <c r="I10" t="n">
-        <v>3.418</v>
+        <v>3.8129</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.6329</v>
       </c>
       <c r="K10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.418</v>
+        <v>3.18</v>
       </c>
       <c r="N10" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0821</v>
+        <v>2.8181</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7097</v>
+        <v>0.6489</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7534</v>
+        <v>0.6587</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0821</v>
+        <v>2.8181</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8531</v>
+        <v>2.8181</v>
       </c>
       <c r="G11" t="n">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5662</v>
+        <v>3.4431</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3742</v>
+        <v>3.4431</v>
       </c>
       <c r="J11" t="n">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="L11" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6032</v>
+        <v>3.4431</v>
       </c>
       <c r="N11" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.033</v>
+        <v>2.7599</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6984</v>
+        <v>0.6355</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7312</v>
+        <v>0.6322</v>
       </c>
       <c r="E12" t="n">
-        <v>3.033</v>
+        <v>2.7599</v>
       </c>
       <c r="F12" t="n">
-        <v>3.033</v>
+        <v>2.9161</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.1562</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3001</v>
+        <v>4.7271</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3001</v>
+        <v>2.5526</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.1562</v>
       </c>
       <c r="K12" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3001</v>
+        <v>2.3964</v>
       </c>
       <c r="N12" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7672</v>
+        <v>2.713</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6372</v>
+        <v>0.6247</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6112</v>
+        <v>0.6108</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7672</v>
+        <v>2.713</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4645</v>
+        <v>2.713</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.197</v>
+        <v>3.213</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6623</v>
+        <v>3.213</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L13" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.965</v>
+        <v>3.213</v>
       </c>
       <c r="N13" t="n">
-        <v>208</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7259</v>
+        <v>2.7124</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6277</v>
+        <v>0.6246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5926</v>
+        <v>0.6105</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7259</v>
+        <v>2.7124</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0298</v>
+        <v>2.4096</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3039</v>
+        <v>0.3028</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1887</v>
+        <v>3.056</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6979</v>
+        <v>1.6502</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3039</v>
+        <v>0.3028</v>
       </c>
       <c r="K14" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="L14" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>2.394</v>
+        <v>1.953</v>
       </c>
       <c r="N14" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5468</v>
+        <v>2.6473</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5864</v>
+        <v>0.6096</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5117</v>
+        <v>0.5809</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5468</v>
+        <v>2.6473</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5468</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.9875</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5468</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5468</v>
+        <v>0.3563</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.9875</v>
       </c>
       <c r="K15" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5468</v>
+        <v>2.3438</v>
       </c>
       <c r="N15" t="n">
-        <v>161</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4695</v>
+        <v>2.3331</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5686</v>
+        <v>0.5372</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4768</v>
+        <v>0.4379</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4695</v>
+        <v>2.3331</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1875</v>
+        <v>2.3331</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.718</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7444</v>
+        <v>2.3814</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9868</v>
+        <v>2.3814</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.718</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2688</v>
+        <v>2.3814</v>
       </c>
       <c r="N16" t="n">
-        <v>208</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4575</v>
+        <v>2.3312</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5659</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4714</v>
+        <v>0.437</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4575</v>
+        <v>2.3312</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5298</v>
+        <v>1.3593</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9277</v>
+        <v>0.9719</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5298</v>
+        <v>1.3593</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7954</v>
+        <v>0.734</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9277</v>
+        <v>0.9719</v>
       </c>
       <c r="K17" t="n">
         <v>170</v>
@@ -1219,7 +1219,7 @@
         <v>35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7231</v>
+        <v>1.7059</v>
       </c>
       <c r="N17" t="n">
         <v>205</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.438</v>
+        <v>2.2975</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5614</v>
+        <v>0.529</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4626</v>
+        <v>0.4217</v>
       </c>
       <c r="E18" t="n">
-        <v>2.438</v>
+        <v>2.2975</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5689</v>
+        <v>3.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8691</v>
+        <v>-0.7425</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5689</v>
+        <v>5.1358</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2958</v>
+        <v>2.7733</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8691</v>
+        <v>-0.7425</v>
       </c>
       <c r="K18" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="L18" t="n">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1649</v>
+        <v>2.0308</v>
       </c>
       <c r="N18" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5407</v>
+        <v>0.5175</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4221</v>
+        <v>0.3988</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3482</v>
+        <v>2.2472</v>
       </c>
       <c r="N19" t="n">
         <v>161</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8127</v>
+        <v>1.7263</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4174</v>
+        <v>0.3975</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1803</v>
+        <v>0.1616</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8127</v>
+        <v>1.7263</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7339</v>
+        <v>2.6681</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9212</v>
+        <v>-0.9418</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1463</v>
+        <v>3.9089</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1559</v>
+        <v>2.1108</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9212</v>
+        <v>-0.9418</v>
       </c>
       <c r="K20" t="n">
         <v>170</v>
@@ -1357,7 +1357,7 @@
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2347</v>
+        <v>1.169</v>
       </c>
       <c r="N20" t="n">
         <v>205</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4515</v>
+        <v>1.4894</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3342</v>
+        <v>0.343</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0173</v>
+        <v>0.0538</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4515</v>
+        <v>1.4894</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3916</v>
+        <v>0.3939</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9401</v>
+        <v>1.0955</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9403</v>
+        <v>0.3939</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5288</v>
+        <v>0.2127</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9401</v>
+        <v>1.0955</v>
       </c>
       <c r="K21" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5886999999999999</v>
+        <v>1.3082</v>
       </c>
       <c r="N21" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3192</v>
+        <v>0.317</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0122</v>
+        <v>0.0025</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3863</v>
+        <v>1.3767</v>
       </c>
       <c r="N22" t="n">
         <v>170</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.295</v>
+        <v>1.294</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2982</v>
+        <v>0.298</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0534</v>
+        <v>-0.0351</v>
       </c>
       <c r="E23" t="n">
-        <v>1.295</v>
+        <v>1.294</v>
       </c>
       <c r="F23" t="n">
-        <v>1.295</v>
+        <v>2.2556</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.9616</v>
       </c>
       <c r="H23" t="n">
-        <v>1.295</v>
+        <v>2.548</v>
       </c>
       <c r="I23" t="n">
-        <v>1.295</v>
+        <v>1.3759</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.9616</v>
       </c>
       <c r="K23" t="n">
         <v>170</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>1.295</v>
+        <v>0.4142999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1739</v>
+        <v>1.2267</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2703</v>
+        <v>0.2825</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1081</v>
+        <v>-0.0658</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1739</v>
+        <v>1.2267</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2952</v>
+        <v>1.2267</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8787</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2952</v>
+        <v>1.2267</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1535</v>
+        <v>1.2267</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8787</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L24" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0322</v>
+        <v>1.2267</v>
       </c>
       <c r="N24" t="n">
-        <v>219</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2447</v>
+        <v>0.2331</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1582</v>
+        <v>-0.1635</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0629</v>
+        <v>1.0121</v>
       </c>
       <c r="N25" t="n">
         <v>113</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1087</v>
+        <v>0.0872</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.425</v>
+        <v>-0.4518</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4719</v>
+        <v>0.3788</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0914</v>
+        <v>0.0751</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4589</v>
+        <v>-0.4758</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3968</v>
+        <v>0.326</v>
       </c>
       <c r="N27" t="n">
         <v>113</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Norwi</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2435</v>
+        <v>0.2072</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0561</v>
+        <v>0.0477</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5281</v>
+        <v>-0.5299</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2435</v>
+        <v>0.2072</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2435</v>
+        <v>-0.3335</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.5407</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2435</v>
+        <v>-0.3335</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2435</v>
+        <v>-0.1801</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.5407</v>
       </c>
       <c r="K28" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2435</v>
+        <v>0.3605999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>82</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Norwi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0446</v>
+        <v>0.0406</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5505</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1938</v>
+        <v>0.1765</v>
       </c>
       <c r="N29" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1419</v>
+        <v>0.1149</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0327</v>
+        <v>0.0265</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.574</v>
+        <v>-0.5719</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1419</v>
+        <v>0.1149</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3754</v>
+        <v>0.1149</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5173</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3754</v>
+        <v>0.1149</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1952</v>
+        <v>0.1149</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5173</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3220999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="N30" t="n">
-        <v>208</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0275</v>
+        <v>0.0166</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5915</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1193</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>113</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0267</v>
+        <v>0.006</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5856</v>
+        <v>-0.6123</v>
       </c>
       <c r="E32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="F32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="I32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.116</v>
+        <v>0.0261</v>
       </c>
       <c r="N32" t="n">
         <v>170</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.041</v>
+        <v>-0.0482</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7184</v>
+        <v>-0.7194</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.178</v>
+        <v>-0.2092</v>
       </c>
       <c r="N33" t="n">
         <v>113</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0745</v>
+        <v>-0.0757</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7841</v>
+        <v>-0.7739</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3237</v>
+        <v>-0.3289</v>
       </c>
       <c r="N34" t="n">
         <v>170</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1045</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8331</v>
+        <v>-0.8307</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4321</v>
+        <v>-0.4537</v>
       </c>
       <c r="N35" t="n">
         <v>82</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1458</v>
+        <v>-0.1504</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.924</v>
+        <v>-0.9215</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6334</v>
+        <v>-0.653</v>
       </c>
       <c r="N36" t="n">
         <v>113</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1511</v>
+        <v>-0.151</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9342</v>
+        <v>-0.9227</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6561</v>
+        <v>-0.6558</v>
       </c>
       <c r="N37" t="n">
         <v>161</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1946</v>
+        <v>-0.2042</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0194</v>
+        <v>-1.028</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8449</v>
+        <v>-0.887</v>
       </c>
       <c r="N38" t="n">
         <v>82</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3079</v>
+        <v>-0.3206</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2416</v>
+        <v>-1.2579</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3371</v>
+        <v>-1.3921</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3443</v>
+        <v>-2.3368</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5381</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6963</v>
+        <v>-1.688</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3443</v>
+        <v>-2.3368</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7767</v>
+        <v>-1.7304</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5676</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7767</v>
+        <v>-1.7304</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9238</v>
+        <v>-0.9344</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5676</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>170</v>
@@ -2277,7 +2277,7 @@
         <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4914</v>
+        <v>-1.5408</v>
       </c>
       <c r="N40" t="n">
         <v>205</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.3894</v>
+        <v>-3.5689</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0107</v>
+        <v>-0.8218</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.6196</v>
+        <v>-2.2488</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.3894</v>
+        <v>-3.5689</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.0622</v>
+        <v>-4.3419</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6728</v>
+        <v>0.773</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.0622</v>
+        <v>-4.3419</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6321</v>
+        <v>-2.3446</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6728</v>
+        <v>0.773</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9593</v>
+        <v>-1.5716</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -2429,10 +2429,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1297</v>
+        <v>1.1319</v>
       </c>
       <c r="J2" t="n">
-        <v>27.1128</v>
+        <v>27.1656</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3689</v>
+        <v>0.3676</v>
       </c>
       <c r="J3" t="n">
-        <v>8.8536</v>
+        <v>8.8224</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1213</v>
+        <v>-0.1341</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.9112</v>
+        <v>-3.2184</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.71</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3249</v>
+        <v>-0.337</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.7976</v>
+        <v>-8.087999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5357</v>
+        <v>-0.5386</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.8568</v>
+        <v>-12.9264</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7637</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>18.3288</v>
+        <v>17.2632</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6654</v>
+        <v>0.6327</v>
       </c>
       <c r="J8" t="n">
-        <v>15.9696</v>
+        <v>15.1848</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2708</v>
+        <v>0.2745</v>
       </c>
       <c r="J9" t="n">
-        <v>6.4992</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.93</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2816</v>
+        <v>-0.2745</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.7584</v>
+        <v>-6.588</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4282</v>
+        <v>-0.4097</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2768</v>
+        <v>-9.832800000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2347</v>
+        <v>0.2391</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1634</v>
+        <v>5.2602</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1233</v>
+        <v>0.1298</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7126</v>
+        <v>2.8556</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5928</v>
+        <v>1.7138</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1523</v>
+        <v>-0.1663</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.3506</v>
+        <v>-3.6586</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.235</v>
+        <v>-0.2493</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.17</v>
+        <v>-5.4846</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1849</v>
+        <v>1.2012</v>
       </c>
       <c r="J17" t="n">
-        <v>26.0678</v>
+        <v>26.4264</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1849</v>
+        <v>1.2012</v>
       </c>
       <c r="J18" t="n">
-        <v>26.0678</v>
+        <v>26.4264</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5471</v>
       </c>
       <c r="J19" t="n">
-        <v>12.386</v>
+        <v>12.0362</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3984</v>
+        <v>-0.3766</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.764799999999999</v>
+        <v>-8.2852</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.822</v>
+        <v>-0.756</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.084</v>
+        <v>-16.632</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6039</v>
+        <v>0.5659</v>
       </c>
       <c r="J22" t="n">
-        <v>10.2663</v>
+        <v>9.6203</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.312</v>
+        <v>0.2959</v>
       </c>
       <c r="J23" t="n">
-        <v>5.304</v>
+        <v>5.0303</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1936</v>
+        <v>-0.213</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2912</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.61</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3921</v>
+        <v>-0.4065</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.6657</v>
+        <v>-6.9105</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8216</v>
+        <v>-0.8058</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.9672</v>
+        <v>-13.6986</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4409</v>
+        <v>1.5672</v>
       </c>
       <c r="J27" t="n">
-        <v>24.4953</v>
+        <v>26.6424</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3482</v>
+        <v>1.4487</v>
       </c>
       <c r="J28" t="n">
-        <v>22.9194</v>
+        <v>24.6279</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1599</v>
+        <v>1.1781</v>
       </c>
       <c r="J29" t="n">
-        <v>19.7183</v>
+        <v>20.0277</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2503</v>
+        <v>0.2738</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2551</v>
+        <v>4.6546</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1011</v>
+        <v>-0.0704</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.7187</v>
+        <v>-1.1968</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6549</v>
+        <v>0.7211</v>
       </c>
       <c r="J32" t="n">
-        <v>14.4078</v>
+        <v>15.8642</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4377</v>
+        <v>0.48</v>
       </c>
       <c r="J33" t="n">
-        <v>9.6294</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2402</v>
+        <v>0.2461</v>
       </c>
       <c r="J34" t="n">
-        <v>5.2844</v>
+        <v>5.4142</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1463</v>
+        <v>0.1565</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2186</v>
+        <v>3.443</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5145</v>
+        <v>-0.4871</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.319</v>
+        <v>-10.7162</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3756</v>
+        <v>0.3975</v>
       </c>
       <c r="J37" t="n">
-        <v>8.263199999999999</v>
+        <v>8.744999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2437</v>
+        <v>0.2456</v>
       </c>
       <c r="J38" t="n">
-        <v>5.3614</v>
+        <v>5.4032</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0582</v>
+        <v>-0.0687</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.2804</v>
+        <v>-1.5114</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1805</v>
+        <v>-0.1957</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.971</v>
+        <v>-4.3054</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.413</v>
+        <v>-0.4229</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.086</v>
+        <v>-9.303800000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6516</v>
+        <v>0.7212</v>
       </c>
       <c r="J42" t="n">
-        <v>13.6836</v>
+        <v>15.1452</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5692</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>11.9532</v>
+        <v>13.2405</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5692</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>11.9532</v>
+        <v>13.2405</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.9929</v>
+        <v>-1.8354</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1733</v>
+        <v>-0.1654</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.6393</v>
+        <v>-3.4734</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3609</v>
+        <v>0.3715</v>
       </c>
       <c r="J47" t="n">
-        <v>7.5789</v>
+        <v>7.8015</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1417</v>
+        <v>0.1432</v>
       </c>
       <c r="J48" t="n">
-        <v>2.9757</v>
+        <v>3.0072</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0208</v>
+        <v>0.0149</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4368</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.305</v>
+        <v>-0.3196</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.405</v>
+        <v>-6.7116</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.59</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4272</v>
+        <v>-0.4372</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.9712</v>
+        <v>-9.1812</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9228</v>
+        <v>1.0176</v>
       </c>
       <c r="J52" t="n">
-        <v>18.456</v>
+        <v>20.352</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.31</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6129</v>
+        <v>0.6814</v>
       </c>
       <c r="J53" t="n">
-        <v>12.258</v>
+        <v>13.628</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.519</v>
+        <v>0.5768</v>
       </c>
       <c r="J54" t="n">
-        <v>10.38</v>
+        <v>11.536</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4354</v>
+        <v>0.4822</v>
       </c>
       <c r="J55" t="n">
-        <v>8.708</v>
+        <v>9.644</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4405</v>
+        <v>-0.4123</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.81</v>
+        <v>-8.246</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2318</v>
+        <v>0.2213</v>
       </c>
       <c r="J57" t="n">
-        <v>4.636</v>
+        <v>4.426</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.92</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0873</v>
+        <v>-0.1049</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.746</v>
+        <v>-2.098</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2817</v>
+        <v>-0.2996</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.634</v>
+        <v>-5.992</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3292</v>
+        <v>-0.3457</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.584</v>
+        <v>-6.914</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4044</v>
+        <v>-0.4177</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.087999999999999</v>
+        <v>-8.353999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.83</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1928</v>
+        <v>1.3156</v>
       </c>
       <c r="J62" t="n">
-        <v>17.892</v>
+        <v>19.734</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.78</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1366</v>
+        <v>1.2561</v>
       </c>
       <c r="J63" t="n">
-        <v>17.049</v>
+        <v>18.8415</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8635</v>
+        <v>0.9634</v>
       </c>
       <c r="J64" t="n">
-        <v>12.9525</v>
+        <v>14.451</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.35</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="J65" t="n">
-        <v>9.489000000000001</v>
+        <v>10.665</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3977</v>
+        <v>0.448</v>
       </c>
       <c r="J66" t="n">
-        <v>5.9655</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6959</v>
+        <v>0.7506</v>
       </c>
       <c r="J67" t="n">
-        <v>10.4385</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2859</v>
+        <v>-0.3068</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.2885</v>
+        <v>-4.602</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.51</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4701</v>
+        <v>-0.4826</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.0515</v>
+        <v>-7.239</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.44</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5357</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.035500000000001</v>
+        <v>-8.1585</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.592</v>
+        <v>-0.5961</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.9415</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5869</v>
+        <v>0.5458</v>
       </c>
       <c r="J72" t="n">
-        <v>8.8035</v>
+        <v>8.186999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.82</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1691</v>
+        <v>-0.1939</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.5365</v>
+        <v>-2.9085</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3829</v>
+        <v>-0.4009</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.7435</v>
+        <v>-6.0135</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.38</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5893</v>
+        <v>-0.594</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.839499999999999</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.25</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7117</v>
+        <v>-0.7064</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.6755</v>
+        <v>-10.596</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.29</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2008</v>
+        <v>1.2145</v>
       </c>
       <c r="J77" t="n">
-        <v>18.012</v>
+        <v>18.2175</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.61</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6922</v>
+        <v>0.697</v>
       </c>
       <c r="J78" t="n">
-        <v>10.383</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.481</v>
+        <v>0.4974</v>
       </c>
       <c r="J79" t="n">
-        <v>7.215</v>
+        <v>7.461</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1875</v>
+        <v>0.2133</v>
       </c>
       <c r="J80" t="n">
-        <v>2.8125</v>
+        <v>3.1995</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0318</v>
       </c>
       <c r="J81" t="n">
-        <v>0.1395</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2639</v>
+        <v>1.238</v>
       </c>
       <c r="J82" t="n">
-        <v>24.0141</v>
+        <v>23.522</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>1.022</v>
+        <v>0.9708</v>
       </c>
       <c r="J83" t="n">
-        <v>19.418</v>
+        <v>18.4452</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4997</v>
+        <v>0.4933</v>
       </c>
       <c r="J84" t="n">
-        <v>9.494300000000001</v>
+        <v>9.3727</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J85" t="n">
-        <v>3.2034</v>
+        <v>3.5891</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1368</v>
+        <v>0.1586</v>
       </c>
       <c r="J86" t="n">
-        <v>2.5992</v>
+        <v>3.0134</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8451</v>
+        <v>0.7937</v>
       </c>
       <c r="J87" t="n">
-        <v>16.0569</v>
+        <v>15.0803</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0246</v>
+        <v>-0.034</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.4674</v>
+        <v>-0.646</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1955</v>
+        <v>-0.212</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.7145</v>
+        <v>-4.028</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2845</v>
+        <v>-0.2998</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.4055</v>
+        <v>-5.6962</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5083</v>
+        <v>-0.5142</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.6577</v>
+        <v>-9.7698</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2044</v>
+        <v>1.1741</v>
       </c>
       <c r="J92" t="n">
-        <v>24.088</v>
+        <v>23.482</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8699</v>
+        <v>0.8226</v>
       </c>
       <c r="J93" t="n">
-        <v>17.398</v>
+        <v>16.452</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5511</v>
+        <v>0.5391</v>
       </c>
       <c r="J94" t="n">
-        <v>11.022</v>
+        <v>10.782</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3454</v>
+        <v>0.3526</v>
       </c>
       <c r="J95" t="n">
-        <v>6.908</v>
+        <v>7.052</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1391</v>
+        <v>0.1603</v>
       </c>
       <c r="J96" t="n">
-        <v>2.782</v>
+        <v>3.206</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4579</v>
+        <v>0.4407</v>
       </c>
       <c r="J97" t="n">
-        <v>9.157999999999999</v>
+        <v>8.814</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.84</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.182</v>
+        <v>-0.1993</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.64</v>
+        <v>-3.986</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2217</v>
+        <v>-0.2389</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.434</v>
+        <v>-4.778</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2413</v>
+        <v>-0.2584</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.826</v>
+        <v>-5.168</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3281</v>
+        <v>-0.3431</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.562</v>
+        <v>-6.862</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0379</v>
+        <v>0.9856</v>
       </c>
       <c r="J102" t="n">
-        <v>23.8717</v>
+        <v>22.6688</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9308</v>
+        <v>0.8738</v>
       </c>
       <c r="J103" t="n">
-        <v>21.4084</v>
+        <v>20.0974</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.19</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5374</v>
+        <v>0.5244</v>
       </c>
       <c r="J104" t="n">
-        <v>12.3602</v>
+        <v>12.0612</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0489</v>
+        <v>0.0687</v>
       </c>
       <c r="J105" t="n">
-        <v>1.1247</v>
+        <v>1.5801</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.98</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1432</v>
+        <v>-0.1338</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.2936</v>
+        <v>-3.0774</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.499</v>
+        <v>0.485</v>
       </c>
       <c r="J107" t="n">
-        <v>11.477</v>
+        <v>11.155</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0114</v>
+        <v>0.0081</v>
       </c>
       <c r="J108" t="n">
-        <v>0.2622</v>
+        <v>0.1863</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.345</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2611</v>
+        <v>-0.2758</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.0053</v>
+        <v>-6.3434</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.7</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3287</v>
+        <v>-0.3418</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.5601</v>
+        <v>-7.8614</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8417</v>
+        <v>0.7876</v>
       </c>
       <c r="J112" t="n">
-        <v>15.1506</v>
+        <v>14.1768</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2965</v>
+        <v>-0.3149</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.337</v>
+        <v>-5.6682</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.61</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3906</v>
+        <v>-0.4053</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.0308</v>
+        <v>-7.2954</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.53</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4652</v>
+        <v>-0.476</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.3736</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.493</v>
+        <v>-0.5021</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.874000000000001</v>
+        <v>-9.037800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.9</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9853</v>
+        <v>0.9696</v>
       </c>
       <c r="J117" t="n">
-        <v>17.7354</v>
+        <v>17.4528</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6849</v>
+        <v>0.6879</v>
       </c>
       <c r="J118" t="n">
-        <v>12.3282</v>
+        <v>12.3822</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.28</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3579</v>
+        <v>0.3774</v>
       </c>
       <c r="J119" t="n">
-        <v>6.4422</v>
+        <v>6.7932</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.26</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3346</v>
+        <v>0.3549</v>
       </c>
       <c r="J120" t="n">
-        <v>6.0228</v>
+        <v>6.3882</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1258</v>
+        <v>-0.1285</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.2644</v>
+        <v>-2.313</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8738</v>
+        <v>0.8212</v>
       </c>
       <c r="J122" t="n">
-        <v>18.3498</v>
+        <v>17.2452</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7809</v>
+        <v>0.7399</v>
       </c>
       <c r="J123" t="n">
-        <v>16.3989</v>
+        <v>15.5379</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5662</v>
+        <v>0.5493</v>
       </c>
       <c r="J124" t="n">
-        <v>11.8902</v>
+        <v>11.5353</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.4184</v>
+        <v>0.4149</v>
       </c>
       <c r="J125" t="n">
-        <v>8.7864</v>
+        <v>8.712899999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5069</v>
+        <v>-0.4763</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.6449</v>
+        <v>-10.0023</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5806</v>
+        <v>0.5551</v>
       </c>
       <c r="J127" t="n">
-        <v>12.1926</v>
+        <v>11.6571</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4668</v>
+        <v>0.4508</v>
       </c>
       <c r="J128" t="n">
-        <v>9.8028</v>
+        <v>9.466799999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2735</v>
+        <v>-0.2893</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.7435</v>
+        <v>-6.0753</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3216</v>
+        <v>-0.3362</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.7536</v>
+        <v>-7.0602</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4981</v>
+        <v>-0.5047</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.4601</v>
+        <v>-10.5987</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.87</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.134</v>
+        <v>-0.1549</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.412</v>
+        <v>-2.7882</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.85</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1561</v>
+        <v>-0.177</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.8098</v>
+        <v>-3.186</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2086</v>
+        <v>-0.229</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.7548</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2086</v>
+        <v>-0.229</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.7548</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5821</v>
+        <v>-0.5858</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.4778</v>
+        <v>-10.5444</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.75</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4083</v>
+        <v>1.3955</v>
       </c>
       <c r="J137" t="n">
-        <v>25.3494</v>
+        <v>25.119</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0333</v>
+        <v>0.9878</v>
       </c>
       <c r="J138" t="n">
-        <v>18.5994</v>
+        <v>17.7804</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.33</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8288</v>
+        <v>0.7903</v>
       </c>
       <c r="J139" t="n">
-        <v>14.9184</v>
+        <v>14.2254</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6241</v>
+        <v>0.6091</v>
       </c>
       <c r="J140" t="n">
-        <v>11.2338</v>
+        <v>10.9638</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.07</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1761</v>
+        <v>0.2015</v>
       </c>
       <c r="J141" t="n">
-        <v>3.1698</v>
+        <v>3.627</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.38</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7951</v>
+        <v>0.7514</v>
       </c>
       <c r="J142" t="n">
-        <v>18.2873</v>
+        <v>17.2822</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2287</v>
+        <v>0.2297</v>
       </c>
       <c r="J143" t="n">
-        <v>5.2601</v>
+        <v>5.2831</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2066</v>
+        <v>0.2083</v>
       </c>
       <c r="J144" t="n">
-        <v>4.7518</v>
+        <v>4.7909</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.54</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4749</v>
+        <v>-0.4822</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.9227</v>
+        <v>-11.0906</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5021</v>
+        <v>-0.5079</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.5483</v>
+        <v>-11.6817</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.51</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1568</v>
+        <v>1.1202</v>
       </c>
       <c r="J147" t="n">
-        <v>26.6064</v>
+        <v>25.7646</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.75</v>
+        <v>0.7141</v>
       </c>
       <c r="J148" t="n">
-        <v>17.25</v>
+        <v>16.4243</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>12.3694</v>
+        <v>12.0681</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2472</v>
+        <v>0.2583</v>
       </c>
       <c r="J150" t="n">
-        <v>5.6856</v>
+        <v>5.9409</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4297</v>
+        <v>-0.4047</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.883100000000001</v>
+        <v>-9.3081</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4803</v>
+        <v>1.4575</v>
       </c>
       <c r="J152" t="n">
-        <v>35.5272</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3773</v>
+        <v>0.3744</v>
       </c>
       <c r="J153" t="n">
-        <v>9.055199999999999</v>
+        <v>8.9856</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3773</v>
+        <v>0.3744</v>
       </c>
       <c r="J154" t="n">
-        <v>9.055199999999999</v>
+        <v>8.9856</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2231</v>
+        <v>-0.2182</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.3544</v>
+        <v>-5.2368</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.2558</v>
+        <v>-1.134</v>
       </c>
       <c r="J156" t="n">
-        <v>-30.1392</v>
+        <v>-27.216</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.18</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4142</v>
+        <v>0.4084</v>
       </c>
       <c r="J157" t="n">
-        <v>9.940799999999999</v>
+        <v>9.801600000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.98</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0334</v>
+        <v>-0.0408</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.8016</v>
+        <v>-0.9792</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0473</v>
+        <v>-0.0562</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.1352</v>
+        <v>-1.3488</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.7376</v>
+        <v>-2.0016</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3032</v>
+        <v>-0.3163</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.2768</v>
+        <v>-7.5912</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1277</v>
+        <v>1.0896</v>
       </c>
       <c r="J162" t="n">
-        <v>23.6817</v>
+        <v>22.8816</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0204</v>
+        <v>0.9659</v>
       </c>
       <c r="J163" t="n">
-        <v>21.4284</v>
+        <v>20.2839</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7924</v>
+        <v>0.7522</v>
       </c>
       <c r="J164" t="n">
-        <v>16.6404</v>
+        <v>15.7962</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4618</v>
+        <v>0.4563</v>
       </c>
       <c r="J165" t="n">
-        <v>9.697800000000001</v>
+        <v>9.5823</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0214</v>
+        <v>-0.929</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.4494</v>
+        <v>-19.509</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.09</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2503</v>
+        <v>0.2505</v>
       </c>
       <c r="J167" t="n">
-        <v>5.2563</v>
+        <v>5.2605</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1608</v>
+        <v>0.1634</v>
       </c>
       <c r="J168" t="n">
-        <v>3.3768</v>
+        <v>3.4314</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1884</v>
+        <v>-0.2042</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.9564</v>
+        <v>-4.2882</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1986</v>
+        <v>-0.2144</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.1706</v>
+        <v>-4.5024</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2586</v>
+        <v>-0.2738</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.4306</v>
+        <v>-5.7498</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.94</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6122</v>
+        <v>1.6124</v>
       </c>
       <c r="J172" t="n">
-        <v>27.4074</v>
+        <v>27.4108</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5555</v>
+        <v>1.553</v>
       </c>
       <c r="J173" t="n">
-        <v>26.4435</v>
+        <v>26.401</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.26</v>
       </c>
       <c r="I174" t="n">
-        <v>0.658</v>
+        <v>0.6418</v>
       </c>
       <c r="J174" t="n">
-        <v>11.186</v>
+        <v>10.9106</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I175" t="n">
-        <v>0.306</v>
+        <v>0.3251</v>
       </c>
       <c r="J175" t="n">
-        <v>5.202</v>
+        <v>5.5267</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3343</v>
+        <v>-0.3041</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.6831</v>
+        <v>-5.1697</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.91</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.5028</v>
+        <v>-1.8479</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.5028</v>
+        <v>-1.8479</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.78</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2291</v>
+        <v>-0.249</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.8947</v>
+        <v>-4.233</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2481</v>
+        <v>-0.2678</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.2177</v>
+        <v>-4.5526</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.601</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.217</v>
+        <v>-10.2561</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6112</v>
+        <v>0.5948</v>
       </c>
       <c r="J182" t="n">
-        <v>17.7248</v>
+        <v>17.2492</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.98</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0344</v>
+        <v>-0.0416</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.9976</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1091</v>
+        <v>-0.1217</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.1639</v>
+        <v>-3.5293</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.82</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.216</v>
+        <v>-0.2302</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.264</v>
+        <v>-6.6758</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2757</v>
+        <v>-0.2892</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.9953</v>
+        <v>-8.386799999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.92</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0442</v>
+        <v>1.0271</v>
       </c>
       <c r="J187" t="n">
-        <v>30.2818</v>
+        <v>29.7859</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.12</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1833</v>
+        <v>0.2006</v>
       </c>
       <c r="J188" t="n">
-        <v>5.3157</v>
+        <v>5.8174</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1413</v>
+        <v>0.1584</v>
       </c>
       <c r="J189" t="n">
-        <v>4.0977</v>
+        <v>4.5936</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0934</v>
+        <v>-0.0997</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.7086</v>
+        <v>-2.8913</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2865</v>
+        <v>-0.2957</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.3085</v>
+        <v>-8.5753</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.8</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4529</v>
+        <v>1.4449</v>
       </c>
       <c r="J192" t="n">
-        <v>21.7935</v>
+        <v>21.6735</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.67</v>
       </c>
       <c r="I193" t="n">
-        <v>1.302</v>
+        <v>1.2849</v>
       </c>
       <c r="J193" t="n">
-        <v>19.53</v>
+        <v>19.2735</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.54</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1484</v>
+        <v>1.1202</v>
       </c>
       <c r="J194" t="n">
-        <v>17.226</v>
+        <v>16.803</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3868</v>
+        <v>0.3987</v>
       </c>
       <c r="J195" t="n">
-        <v>5.802</v>
+        <v>5.9805</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.98</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1966</v>
+        <v>-0.1713</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.949</v>
+        <v>-2.5695</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1148</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.341</v>
+        <v>-1.722</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1133</v>
+        <v>-0.1387</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.6995</v>
+        <v>-2.0805</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2441</v>
+        <v>-0.2668</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.6615</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5052</v>
+        <v>-0.5159</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.578</v>
+        <v>-7.7385</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.35</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6181</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.2715</v>
+        <v>-9.307499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6369</v>
+        <v>0.6389</v>
       </c>
       <c r="J202" t="n">
-        <v>14.0118</v>
+        <v>14.0558</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.36</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4614</v>
+        <v>0.4738</v>
       </c>
       <c r="J203" t="n">
-        <v>10.1508</v>
+        <v>10.4236</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.25</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3368</v>
+        <v>0.3539</v>
       </c>
       <c r="J204" t="n">
-        <v>7.4096</v>
+        <v>7.7858</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1613</v>
+        <v>0.1806</v>
       </c>
       <c r="J205" t="n">
-        <v>3.5486</v>
+        <v>3.9732</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.074</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.628</v>
+        <v>-1.6896</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4793</v>
+        <v>0.4709</v>
       </c>
       <c r="J207" t="n">
-        <v>10.5446</v>
+        <v>10.3598</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3532</v>
+        <v>0.3529</v>
       </c>
       <c r="J208" t="n">
-        <v>7.7704</v>
+        <v>7.7638</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2413</v>
+        <v>-0.2563</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.3086</v>
+        <v>-5.6386</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3287</v>
+        <v>-0.3418</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.2314</v>
+        <v>-7.5196</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.7</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3287</v>
+        <v>-0.3418</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.2314</v>
+        <v>-7.5196</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7318</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>16.8314</v>
+        <v>15.824</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3013</v>
+        <v>0.2927</v>
       </c>
       <c r="J213" t="n">
-        <v>6.9299</v>
+        <v>6.7321</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.73</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2877</v>
+        <v>-0.3043</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.6171</v>
+        <v>-6.9989</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4476</v>
+        <v>-0.4577</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.2948</v>
+        <v>-10.5271</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5028</v>
+        <v>-0.5098</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.5644</v>
+        <v>-11.7254</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.34</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8825</v>
+        <v>0.8313</v>
       </c>
       <c r="J217" t="n">
-        <v>20.2975</v>
+        <v>19.1199</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.24</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6524</v>
+        <v>0.6284</v>
       </c>
       <c r="J218" t="n">
-        <v>15.0052</v>
+        <v>14.4532</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.23</v>
       </c>
       <c r="I219" t="n">
-        <v>0.629</v>
+        <v>0.6075</v>
       </c>
       <c r="J219" t="n">
-        <v>14.467</v>
+        <v>13.9725</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4862</v>
+        <v>0.4786</v>
       </c>
       <c r="J220" t="n">
-        <v>11.1826</v>
+        <v>11.0078</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1822</v>
+        <v>0.1983</v>
       </c>
       <c r="J221" t="n">
-        <v>4.1906</v>
+        <v>4.5609</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1914</v>
+        <v>0.1796</v>
       </c>
       <c r="J222" t="n">
-        <v>3.0624</v>
+        <v>2.8736</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0956</v>
+        <v>-0.1143</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.5296</v>
+        <v>-1.8288</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1522</v>
+        <v>-0.1715</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.4352</v>
+        <v>-2.744</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.59</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4111</v>
+        <v>-0.4245</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.5776</v>
+        <v>-6.792</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.5</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4947</v>
+        <v>-0.5034</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.9152</v>
+        <v>-8.054399999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.93</v>
       </c>
       <c r="I227" t="n">
-        <v>1.6099</v>
+        <v>1.6086</v>
       </c>
       <c r="J227" t="n">
-        <v>25.7584</v>
+        <v>25.7376</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.76</v>
       </c>
       <c r="I228" t="n">
-        <v>1.4138</v>
+        <v>1.4024</v>
       </c>
       <c r="J228" t="n">
-        <v>22.6208</v>
+        <v>22.4384</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.65</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2846</v>
+        <v>1.2652</v>
       </c>
       <c r="J229" t="n">
-        <v>20.5536</v>
+        <v>20.2432</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6122</v>
+        <v>-0.5612</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.795199999999999</v>
+        <v>-8.979200000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.79</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7415</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.864</v>
+        <v>-10.8304</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4646</v>
+        <v>1.4513</v>
       </c>
       <c r="J232" t="n">
-        <v>29.292</v>
+        <v>29.026</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8849</v>
+        <v>0.8371</v>
       </c>
       <c r="J233" t="n">
-        <v>17.698</v>
+        <v>16.742</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.27</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7093</v>
+        <v>0.6817</v>
       </c>
       <c r="J234" t="n">
-        <v>14.186</v>
+        <v>13.634</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.24</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>12.812</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.745</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.9</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.44</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9754</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J237" t="n">
-        <v>19.508</v>
+        <v>18.114</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3197</v>
+        <v>-0.3365</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.394</v>
+        <v>-6.73</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3481</v>
+        <v>-0.3638</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.962</v>
+        <v>-7.276</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3669</v>
+        <v>-0.3819</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.338</v>
+        <v>-7.638</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4417</v>
+        <v>-0.453</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.834</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.23</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3868</v>
+        <v>0.3863</v>
       </c>
       <c r="J242" t="n">
-        <v>11.2172</v>
+        <v>11.2027</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2867</v>
+        <v>0.2913</v>
       </c>
       <c r="J243" t="n">
-        <v>8.314299999999999</v>
+        <v>8.447699999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.06</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1299</v>
+        <v>0.1378</v>
       </c>
       <c r="J244" t="n">
-        <v>3.7671</v>
+        <v>3.9962</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2745</v>
+        <v>-0.2883</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.9605</v>
+        <v>-8.3607</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4072</v>
+        <v>-0.4167</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.8088</v>
+        <v>-12.0843</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6757</v>
+        <v>0.6705</v>
       </c>
       <c r="J247" t="n">
-        <v>19.5953</v>
+        <v>19.4445</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.35</v>
       </c>
       <c r="I248" t="n">
-        <v>0.471</v>
+        <v>0.479</v>
       </c>
       <c r="J248" t="n">
-        <v>13.659</v>
+        <v>13.891</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0108</v>
+        <v>-0.0083</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.3132</v>
+        <v>-0.2407</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1692</v>
+        <v>-0.1795</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.9068</v>
+        <v>-5.2055</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2115</v>
+        <v>-0.2222</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.1335</v>
+        <v>-6.4438</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.84</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5212</v>
+        <v>1.5131</v>
       </c>
       <c r="J252" t="n">
-        <v>25.8604</v>
+        <v>25.7227</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.46</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0641</v>
+        <v>1.0232</v>
       </c>
       <c r="J253" t="n">
-        <v>18.0897</v>
+        <v>17.3944</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6539</v>
+        <v>0.6343</v>
       </c>
       <c r="J254" t="n">
-        <v>11.1163</v>
+        <v>10.7831</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.22</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5826</v>
+        <v>0.5708</v>
       </c>
       <c r="J255" t="n">
-        <v>9.904199999999999</v>
+        <v>9.7036</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4059</v>
+        <v>-0.3754</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.9003</v>
+        <v>-6.3818</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4055</v>
+        <v>0.3867</v>
       </c>
       <c r="J257" t="n">
-        <v>6.8935</v>
+        <v>6.5739</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.2971</v>
+        <v>-1.5861</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1769</v>
+        <v>-0.1954</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.0073</v>
+        <v>-3.3218</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.58</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4239</v>
+        <v>-0.4361</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.2063</v>
+        <v>-7.4137</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4703</v>
+        <v>-0.4799</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.9951</v>
+        <v>-8.158300000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1772</v>
+        <v>1.1454</v>
       </c>
       <c r="J262" t="n">
-        <v>24.7212</v>
+        <v>24.0534</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.022</v>
+        <v>0.9708</v>
       </c>
       <c r="J263" t="n">
-        <v>21.462</v>
+        <v>20.3868</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8895</v>
+        <v>0.8403</v>
       </c>
       <c r="J264" t="n">
-        <v>18.6795</v>
+        <v>17.6463</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.25</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6671</v>
+        <v>0.6434</v>
       </c>
       <c r="J265" t="n">
-        <v>14.0091</v>
+        <v>13.5114</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.791</v>
+        <v>-0.7254</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.611</v>
+        <v>-15.2334</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3804</v>
+        <v>0.3721</v>
       </c>
       <c r="J267" t="n">
-        <v>7.9884</v>
+        <v>7.8141</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2127</v>
+        <v>0.2128</v>
       </c>
       <c r="J268" t="n">
-        <v>4.4667</v>
+        <v>4.4688</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0667</v>
+        <v>-0.0791</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.4007</v>
+        <v>-1.6611</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2563</v>
+        <v>-0.272</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.3823</v>
+        <v>-5.712</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4637</v>
+        <v>-0.4719</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.7377</v>
+        <v>-9.9099</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.49</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J272" t="n">
-        <v>36.676</v>
+        <v>38.744</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0111</v>
+        <v>0.9646</v>
       </c>
       <c r="J273" t="n">
-        <v>20.222</v>
+        <v>19.292</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4361</v>
+        <v>0.4438</v>
       </c>
       <c r="J274" t="n">
-        <v>8.722</v>
+        <v>8.875999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3579</v>
+        <v>0.3729</v>
       </c>
       <c r="J275" t="n">
-        <v>7.158</v>
+        <v>7.458</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.97</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2362</v>
+        <v>-0.2095</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.724</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="J277" t="n">
-        <v>12.692</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.95</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0479</v>
+        <v>-0.0645</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.958</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.66</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3469</v>
+        <v>-0.3629</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.938</v>
+        <v>-7.258</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.55</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4498</v>
+        <v>-0.4609</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.996</v>
+        <v>-9.218</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4591</v>
+        <v>-0.4697</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.182</v>
+        <v>-9.394</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.204</v>
+        <v>1.169</v>
       </c>
       <c r="J282" t="n">
-        <v>34.916</v>
+        <v>33.901</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.543</v>
+        <v>0.5282</v>
       </c>
       <c r="J283" t="n">
-        <v>15.747</v>
+        <v>15.3178</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.18</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5185</v>
+        <v>0.506</v>
       </c>
       <c r="J284" t="n">
-        <v>15.0365</v>
+        <v>14.674</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.134</v>
+        <v>-0.1274</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.886</v>
+        <v>-3.6946</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3928</v>
+        <v>-0.3726</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.3912</v>
+        <v>-10.8054</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.12</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3115</v>
+        <v>0.3091</v>
       </c>
       <c r="J287" t="n">
-        <v>9.0335</v>
+        <v>8.963900000000001</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1828</v>
+        <v>0.1854</v>
       </c>
       <c r="J288" t="n">
-        <v>5.3012</v>
+        <v>5.3766</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1786</v>
+        <v>-0.1942</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.1794</v>
+        <v>-5.6318</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2294</v>
+        <v>-0.2449</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.6526</v>
+        <v>-7.1021</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2591</v>
+        <v>-0.2742</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.5139</v>
+        <v>-7.9518</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.39</v>
       </c>
       <c r="I292" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J292" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2452</v>
+        <v>1.2262</v>
       </c>
       <c r="J293" t="n">
-        <v>22.4136</v>
+        <v>22.0716</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0596</v>
+        <v>1.0221</v>
       </c>
       <c r="J294" t="n">
-        <v>19.0728</v>
+        <v>18.3978</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.09</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2085</v>
+        <v>0.238</v>
       </c>
       <c r="J295" t="n">
-        <v>3.753</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.89</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4945</v>
+        <v>-0.4504</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.901</v>
+        <v>-8.107200000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.09</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4092</v>
+        <v>0.368</v>
       </c>
       <c r="J297" t="n">
-        <v>7.3656</v>
+        <v>6.624</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0178</v>
+        <v>-0.0441</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.3204</v>
+        <v>-0.7938</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.42</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.549</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J299" t="n">
-        <v>-9.882</v>
+        <v>-10.026</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.39</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5774</v>
+        <v>-0.5833</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.3932</v>
+        <v>-10.4994</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.39</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5774</v>
+        <v>-0.5833</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.3932</v>
+        <v>-10.4994</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.59</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2755</v>
+        <v>1.2438</v>
       </c>
       <c r="J302" t="n">
-        <v>30.612</v>
+        <v>29.8512</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.19</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5486</v>
+        <v>0.532</v>
       </c>
       <c r="J303" t="n">
-        <v>13.1664</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.17</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4986</v>
+        <v>0.4869</v>
       </c>
       <c r="J304" t="n">
-        <v>11.9664</v>
+        <v>11.6856</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2603</v>
+        <v>0.2674</v>
       </c>
       <c r="J305" t="n">
-        <v>6.2472</v>
+        <v>6.4176</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0536</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J306" t="n">
-        <v>-25.2864</v>
+        <v>-23.0208</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.66</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1227</v>
+        <v>1.092</v>
       </c>
       <c r="J307" t="n">
-        <v>26.9448</v>
+        <v>26.208</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4004</v>
+        <v>0.3984</v>
       </c>
       <c r="J308" t="n">
-        <v>9.6096</v>
+        <v>9.5616</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.76</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.696</v>
+        <v>-7.0032</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.76</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.696</v>
+        <v>-7.0032</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3743</v>
+        <v>-0.3844</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.9832</v>
+        <v>-9.2256</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1098</v>
+        <v>1.0712</v>
       </c>
       <c r="J312" t="n">
-        <v>31.0744</v>
+        <v>29.9936</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8773</v>
+        <v>0.8277</v>
       </c>
       <c r="J313" t="n">
-        <v>24.5644</v>
+        <v>23.1756</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5803</v>
+        <v>0.5642</v>
       </c>
       <c r="J314" t="n">
-        <v>16.2484</v>
+        <v>15.7976</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.09</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2678</v>
+        <v>0.2795</v>
       </c>
       <c r="J315" t="n">
-        <v>7.4984</v>
+        <v>7.826</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.01</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0002</v>
+        <v>0.0217</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.0056</v>
+        <v>0.6076</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.14</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3612</v>
+        <v>0.354</v>
       </c>
       <c r="J317" t="n">
-        <v>10.1136</v>
+        <v>9.912000000000001</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2574</v>
+        <v>0.2557</v>
       </c>
       <c r="J318" t="n">
-        <v>7.2072</v>
+        <v>7.1596</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0535</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.498</v>
+        <v>-1.8228</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2164</v>
+        <v>-0.2327</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.0592</v>
+        <v>-6.5156</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5271</v>
+        <v>-0.5317</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.7588</v>
+        <v>-14.8876</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.782</v>
+        <v>8.3886</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7919</v>
+        <v>1.9316</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9183</v>
+        <v>3.1332</v>
       </c>
       <c r="E2" t="n">
-        <v>7.782</v>
+        <v>8.3886</v>
       </c>
       <c r="F2" t="n">
         <v>4.3615</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4205</v>
+        <v>3.4062</v>
       </c>
       <c r="H2" t="n">
         <v>9.495900000000001</v>
@@ -520,7 +520,7 @@
         <v>5.1277</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4205</v>
+        <v>3.4062</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>98</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5482</v>
+        <v>8.533899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4828</v>
+        <v>7.6653</v>
       </c>
       <c r="C3" t="n">
-        <v>1.723</v>
+        <v>1.765</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7821</v>
+        <v>2.8101</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4828</v>
+        <v>7.6653</v>
       </c>
       <c r="F3" t="n">
         <v>3.6867</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3279</v>
+        <v>5.422</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2268</v>
+        <v>1.2485</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8012</v>
+        <v>1.8081</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3279</v>
+        <v>5.422</v>
       </c>
       <c r="F4" t="n">
         <v>2.9553</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2407</v>
+        <v>5.3627</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2067</v>
+        <v>1.2348</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7615</v>
+        <v>1.7816</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2407</v>
+        <v>5.3627</v>
       </c>
       <c r="F5" t="n">
         <v>2.543</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6976</v>
+        <v>2.6983</v>
       </c>
       <c r="H5" t="n">
         <v>3.4962</v>
@@ -658,7 +658,7 @@
         <v>1.8879</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6976</v>
+        <v>2.6983</v>
       </c>
       <c r="K5" t="n">
         <v>86</v>
@@ -667,7 +667,7 @@
         <v>98</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5855</v>
+        <v>4.5862</v>
       </c>
       <c r="N5" t="n">
         <v>184</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0608</v>
+        <v>5.136</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1653</v>
+        <v>1.1826</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6796</v>
+        <v>1.6803</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0608</v>
+        <v>5.136</v>
       </c>
       <c r="F6" t="n">
         <v>4.3099</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2643</v>
+        <v>3.5159</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7517</v>
+        <v>0.8096</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8618</v>
+        <v>0.9567</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2643</v>
+        <v>3.5159</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0038</v>
+        <v>3.851</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2605</v>
+        <v>-0.5768</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0164</v>
+        <v>7.8118</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7088</v>
+        <v>4.2183</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2605</v>
+        <v>-0.5768</v>
       </c>
       <c r="K7" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9693</v>
+        <v>3.6415</v>
       </c>
       <c r="N7" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2635</v>
+        <v>3.4086</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7849</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.9087</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2635</v>
+        <v>3.4086</v>
       </c>
       <c r="F8" t="n">
-        <v>3.851</v>
+        <v>3.0038</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5875</v>
+        <v>0.2605</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8118</v>
+        <v>5.0164</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2183</v>
+        <v>2.7088</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5875</v>
+        <v>0.2605</v>
       </c>
       <c r="K8" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6308</v>
+        <v>2.9693</v>
       </c>
       <c r="N8" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1391</v>
+        <v>3.1799</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7228</v>
+        <v>0.7322</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8048</v>
+        <v>0.8066</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1391</v>
+        <v>3.1799</v>
       </c>
       <c r="F9" t="n">
         <v>2.8018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3373</v>
+        <v>0.3225</v>
       </c>
       <c r="H9" t="n">
         <v>4.3501</v>
@@ -842,7 +842,7 @@
         <v>2.349</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3373</v>
+        <v>0.3225</v>
       </c>
       <c r="K9" t="n">
         <v>86</v>
@@ -851,7 +851,7 @@
         <v>98</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6863</v>
+        <v>2.6715</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9906</v>
+        <v>3.0743</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6886</v>
+        <v>0.7079</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7372</v>
+        <v>0.7594</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9906</v>
+        <v>3.0743</v>
       </c>
       <c r="F10" t="n">
         <v>3.6235</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8181</v>
+        <v>2.9973</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6489</v>
+        <v>0.6902</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6587</v>
+        <v>0.725</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8181</v>
+        <v>2.9973</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8181</v>
+        <v>2.713</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4431</v>
+        <v>3.213</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4431</v>
+        <v>3.213</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4431</v>
+        <v>3.213</v>
       </c>
       <c r="N11" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7599</v>
+        <v>2.9835</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6355</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6322</v>
+        <v>0.7188</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7599</v>
+        <v>2.9835</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9161</v>
+        <v>2.8181</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1562</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7271</v>
+        <v>3.4431</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5526</v>
+        <v>3.4431</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1562</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="L12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3964</v>
+        <v>3.4431</v>
       </c>
       <c r="N12" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.713</v>
+        <v>2.8128</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6247</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6108</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.713</v>
+        <v>2.8128</v>
       </c>
       <c r="F13" t="n">
-        <v>2.713</v>
+        <v>2.4096</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.3028</v>
       </c>
       <c r="H13" t="n">
-        <v>3.213</v>
+        <v>3.056</v>
       </c>
       <c r="I13" t="n">
-        <v>3.213</v>
+        <v>1.6502</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.3028</v>
       </c>
       <c r="K13" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>3.213</v>
+        <v>1.953</v>
       </c>
       <c r="N13" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7124</v>
+        <v>2.6473</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6246</v>
+        <v>0.6096</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6105</v>
+        <v>0.5687</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7124</v>
+        <v>2.6473</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4096</v>
+        <v>2.9161</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3028</v>
+        <v>-0.1555</v>
       </c>
       <c r="H14" t="n">
-        <v>3.056</v>
+        <v>4.7271</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6502</v>
+        <v>2.5526</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3028</v>
+        <v>-0.1555</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="L14" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>1.953</v>
+        <v>2.3971</v>
       </c>
       <c r="N14" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6473</v>
+        <v>2.5416</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6096</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5809</v>
+        <v>0.5215</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6473</v>
+        <v>2.5416</v>
       </c>
       <c r="F15" t="n">
         <v>0.6598000000000001</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3331</v>
+        <v>2.4083</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5372</v>
+        <v>0.5545</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4379</v>
+        <v>0.4619</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3331</v>
+        <v>2.4083</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3331</v>
+        <v>2.2472</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3814</v>
+        <v>2.2472</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3814</v>
+        <v>2.2472</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3814</v>
+        <v>2.2472</v>
       </c>
       <c r="N16" t="n">
         <v>161</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3312</v>
+        <v>2.4059</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="D17" t="n">
-        <v>0.437</v>
+        <v>0.4608</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3312</v>
+        <v>2.4059</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3593</v>
+        <v>2.3331</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9719</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3593</v>
+        <v>2.3814</v>
       </c>
       <c r="I17" t="n">
-        <v>0.734</v>
+        <v>2.3814</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9719</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L17" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7059</v>
+        <v>2.3814</v>
       </c>
       <c r="N17" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2975</v>
+        <v>2.2549</v>
       </c>
       <c r="C18" t="n">
-        <v>0.529</v>
+        <v>0.5192</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4217</v>
+        <v>0.3934</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2975</v>
+        <v>2.2549</v>
       </c>
       <c r="F18" t="n">
-        <v>3.04</v>
+        <v>1.3593</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7425</v>
+        <v>0.9676</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1358</v>
+        <v>1.3593</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7733</v>
+        <v>0.734</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7425</v>
+        <v>0.9676</v>
       </c>
       <c r="K18" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0308</v>
+        <v>1.7016</v>
       </c>
       <c r="N18" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2472</v>
+        <v>2.2528</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5175</v>
+        <v>0.5187</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3988</v>
+        <v>0.3925</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2472</v>
+        <v>2.2528</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2472</v>
+        <v>3.04</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7425</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2472</v>
+        <v>5.1358</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2472</v>
+        <v>2.7733</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7425</v>
       </c>
       <c r="K19" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2472</v>
+        <v>2.0308</v>
       </c>
       <c r="N19" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7263</v>
+        <v>1.6241</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3975</v>
+        <v>0.374</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1616</v>
+        <v>0.1116</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7263</v>
+        <v>1.6241</v>
       </c>
       <c r="F20" t="n">
         <v>2.6681</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9418</v>
+        <v>-0.9248</v>
       </c>
       <c r="H20" t="n">
         <v>3.9089</v>
@@ -1348,7 +1348,7 @@
         <v>2.1108</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9418</v>
+        <v>-0.9248</v>
       </c>
       <c r="K20" t="n">
         <v>170</v>
@@ -1357,7 +1357,7 @@
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.169</v>
+        <v>1.186</v>
       </c>
       <c r="N20" t="n">
         <v>205</v>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4894</v>
+        <v>1.5192</v>
       </c>
       <c r="C21" t="n">
-        <v>0.343</v>
+        <v>0.3498</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0538</v>
+        <v>0.0648</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4894</v>
+        <v>1.5192</v>
       </c>
       <c r="F21" t="n">
         <v>0.3939</v>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3767</v>
+        <v>1.4462</v>
       </c>
       <c r="C22" t="n">
-        <v>0.317</v>
+        <v>0.333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0025</v>
+        <v>0.0322</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3767</v>
+        <v>1.4462</v>
       </c>
       <c r="F22" t="n">
         <v>1.3767</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.294</v>
+        <v>1.2408</v>
       </c>
       <c r="C23" t="n">
-        <v>0.298</v>
+        <v>0.2857</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0351</v>
+        <v>-0.0596</v>
       </c>
       <c r="E23" t="n">
-        <v>1.294</v>
+        <v>1.2408</v>
       </c>
       <c r="F23" t="n">
         <v>2.2556</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9616</v>
+        <v>-0.954</v>
       </c>
       <c r="H23" t="n">
         <v>2.548</v>
@@ -1486,7 +1486,7 @@
         <v>1.3759</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9616</v>
+        <v>-0.954</v>
       </c>
       <c r="K23" t="n">
         <v>170</v>
@@ -1495,7 +1495,7 @@
         <v>35</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4142999999999999</v>
+        <v>0.4218999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>205</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2267</v>
+        <v>1.2214</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2825</v>
+        <v>0.2812</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0658</v>
+        <v>-0.0682</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2267</v>
+        <v>1.2214</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2267</v>
+        <v>1.0121</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2267</v>
+        <v>1.0121</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2267</v>
+        <v>1.0121</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2267</v>
+        <v>1.0121</v>
       </c>
       <c r="N24" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0121</v>
+        <v>1.1855</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2331</v>
+        <v>0.273</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1635</v>
+        <v>-0.0843</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0121</v>
+        <v>1.1855</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0121</v>
+        <v>1.2267</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0121</v>
+        <v>1.2267</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0121</v>
+        <v>1.2267</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0121</v>
+        <v>1.2267</v>
       </c>
       <c r="N25" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3788</v>
+        <v>0.6948</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0872</v>
+        <v>0.16</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4518</v>
+        <v>-0.3035</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3788</v>
+        <v>0.6948</v>
       </c>
       <c r="F26" t="n">
         <v>0.3788</v>
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.326</v>
+        <v>0.2623</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0751</v>
+        <v>0.0604</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4758</v>
+        <v>-0.4967</v>
       </c>
       <c r="E27" t="n">
-        <v>0.326</v>
+        <v>0.2623</v>
       </c>
       <c r="F27" t="n">
         <v>0.326</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2072</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0477</v>
+        <v>0.0021</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5299</v>
+        <v>-0.6098</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2072</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3335</v>
+        <v>0.1149</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5407</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3335</v>
+        <v>0.1149</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1801</v>
+        <v>0.1149</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5407</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3605999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="N28" t="n">
-        <v>208</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1765</v>
+        <v>-0.0509</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0406</v>
+        <v>-0.0117</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1765</v>
+        <v>-0.0509</v>
       </c>
       <c r="F29" t="n">
         <v>0.1765</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1149</v>
+        <v>-0.0709</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0265</v>
+        <v>-0.0163</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5719</v>
+        <v>-0.6455</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1149</v>
+        <v>-0.0709</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1149</v>
+        <v>-0.3335</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5407</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1149</v>
+        <v>-0.3335</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1149</v>
+        <v>-0.1801</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5407</v>
       </c>
       <c r="K30" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1149</v>
+        <v>0.3605999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0166</v>
+        <v>-0.0227</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5915</v>
+        <v>-0.6579</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>0.07190000000000001</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0261</v>
+        <v>-0.1798</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006</v>
+        <v>-0.0414</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6123</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0261</v>
+        <v>-0.1798</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0261</v>
+        <v>-0.2092</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0261</v>
+        <v>-0.2092</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0261</v>
+        <v>-0.2092</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0261</v>
+        <v>-0.2092</v>
       </c>
       <c r="N32" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2092</v>
+        <v>-0.3083</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0482</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7194</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2092</v>
+        <v>-0.3083</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2092</v>
+        <v>0.0261</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2092</v>
+        <v>0.0261</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2092</v>
+        <v>0.0261</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2092</v>
+        <v>0.0261</v>
       </c>
       <c r="N33" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3289</v>
+        <v>-0.4856</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0757</v>
+        <v>-0.1118</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7739</v>
+        <v>-0.8307</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3289</v>
+        <v>-0.4856</v>
       </c>
       <c r="F34" t="n">
         <v>-0.3289</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>deko</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4537</v>
+        <v>-0.7066</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1045</v>
+        <v>-0.1627</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8307</v>
+        <v>-0.9294</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4537</v>
+        <v>-0.7066</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4537</v>
+        <v>-0.6558</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4537</v>
+        <v>-0.6558</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4537</v>
+        <v>-0.6558</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4537</v>
+        <v>-0.6558</v>
       </c>
       <c r="N35" t="n">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>deko</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.653</v>
+        <v>-0.7348</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1504</v>
+        <v>-0.1692</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9215</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.653</v>
+        <v>-0.7348</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.653</v>
+        <v>-0.4537</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.653</v>
+        <v>-0.4537</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.653</v>
+        <v>-0.4537</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.653</v>
+        <v>-0.4537</v>
       </c>
       <c r="N36" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6558</v>
+        <v>-0.8354</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.151</v>
+        <v>-0.1924</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9227</v>
+        <v>-0.987</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6558</v>
+        <v>-0.8354</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6558</v>
+        <v>-0.653</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6558</v>
+        <v>-0.653</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6558</v>
+        <v>-0.653</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6558</v>
+        <v>-0.653</v>
       </c>
       <c r="N37" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.887</v>
+        <v>-1.0551</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2042</v>
+        <v>-0.243</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.028</v>
+        <v>-1.0851</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.887</v>
+        <v>-1.0551</v>
       </c>
       <c r="F38" t="n">
         <v>-0.887</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3921</v>
+        <v>-1.5218</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3206</v>
+        <v>-0.3504</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2579</v>
+        <v>-1.2936</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3921</v>
+        <v>-1.5218</v>
       </c>
       <c r="F39" t="n">
         <v>-1.3921</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3368</v>
+        <v>-2.3252</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5381</v>
+        <v>-0.5354</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.688</v>
+        <v>-1.6524</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3368</v>
+        <v>-2.3252</v>
       </c>
       <c r="F40" t="n">
         <v>-1.7304</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.589</v>
       </c>
       <c r="H40" t="n">
         <v>-1.7304</v>
@@ -2268,7 +2268,7 @@
         <v>-0.9344</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.589</v>
       </c>
       <c r="K40" t="n">
         <v>170</v>
@@ -2277,7 +2277,7 @@
         <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5408</v>
+        <v>-1.5234</v>
       </c>
       <c r="N40" t="n">
         <v>205</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5689</v>
+        <v>-3.9143</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8218</v>
+        <v>-0.9013</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.2488</v>
+        <v>-2.3623</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5689</v>
+        <v>-3.9143</v>
       </c>
       <c r="F41" t="n">
         <v>-4.3419</v>
       </c>
       <c r="G41" t="n">
-        <v>0.773</v>
+        <v>0.7734</v>
       </c>
       <c r="H41" t="n">
         <v>-4.3419</v>
@@ -2314,7 +2314,7 @@
         <v>-2.3446</v>
       </c>
       <c r="J41" t="n">
-        <v>0.773</v>
+        <v>0.7734</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5716</v>
+        <v>-1.5712</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0176</v>
+        <v>1.0184</v>
       </c>
       <c r="J52" t="n">
-        <v>20.352</v>
+        <v>20.368</v>
       </c>
     </row>
     <row r="53">
@@ -4466,13 +4466,13 @@
         <v>20</v>
       </c>
       <c r="H53" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6814</v>
+        <v>0.6671</v>
       </c>
       <c r="J53" t="n">
-        <v>13.628</v>
+        <v>13.342</v>
       </c>
     </row>
     <row r="54">
@@ -4506,13 +4506,13 @@
         <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5768</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>11.536</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4822</v>
+        <v>0.4826</v>
       </c>
       <c r="J55" t="n">
-        <v>9.644</v>
+        <v>9.651999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4123</v>
+        <v>-0.4116</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.246</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2213</v>
+        <v>0.217</v>
       </c>
       <c r="J57" t="n">
-        <v>4.426</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="58">
@@ -4666,13 +4666,13 @@
         <v>20</v>
       </c>
       <c r="H58" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1049</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.098</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="59">
@@ -4706,13 +4706,13 @@
         <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2996</v>
+        <v>-0.2822</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.992</v>
+        <v>-5.644</v>
       </c>
     </row>
     <row r="60">
@@ -4746,13 +4746,13 @@
         <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3457</v>
+        <v>-0.3287</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.914</v>
+        <v>-6.574</v>
       </c>
     </row>
     <row r="61">
@@ -4786,13 +4786,13 @@
         <v>20</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4177</v>
+        <v>-0.4101</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.353999999999999</v>
+        <v>-8.202</v>
       </c>
     </row>
     <row r="62">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D314" t="n">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">

--- a/database/event/7755/event_7755_evp_summary.xlsx
+++ b/database/event/7755/event_7755_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3886</v>
+        <v>8.103</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9316</v>
+        <v>1.8658</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1332</v>
+        <v>3.0855</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3886</v>
+        <v>8.103</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3615</v>
+        <v>4.1791</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4062</v>
+        <v>3.303</v>
       </c>
       <c r="H2" t="n">
-        <v>9.495900000000001</v>
+        <v>9.247400000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1277</v>
+        <v>5.1921</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4062</v>
+        <v>3.303</v>
       </c>
       <c r="K2" t="n">
         <v>86</v>
@@ -529,7 +529,7 @@
         <v>98</v>
       </c>
       <c r="M2" t="n">
-        <v>8.533899999999999</v>
+        <v>8.495100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>184</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6653</v>
+        <v>7.4851</v>
       </c>
       <c r="C3" t="n">
-        <v>1.765</v>
+        <v>1.7236</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8101</v>
+        <v>2.804</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6653</v>
+        <v>7.4851</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6867</v>
+        <v>3.585</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7961</v>
+        <v>3.7176</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2696</v>
+        <v>7.017</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9255</v>
+        <v>3.9398</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7961</v>
+        <v>3.7176</v>
       </c>
       <c r="K3" t="n">
         <v>113</v>
@@ -575,7 +575,7 @@
         <v>106</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7216</v>
+        <v>7.6574</v>
       </c>
       <c r="N3" t="n">
         <v>219</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.422</v>
+        <v>5.3865</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2485</v>
+        <v>1.2403</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8081</v>
+        <v>1.848</v>
       </c>
       <c r="E4" t="n">
-        <v>5.422</v>
+        <v>5.3865</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9553</v>
+        <v>2.9872</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3726</v>
+        <v>2.3052</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8566</v>
+        <v>4.7727</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6225</v>
+        <v>2.6797</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3726</v>
+        <v>2.3052</v>
       </c>
       <c r="K4" t="n">
         <v>113</v>
@@ -621,7 +621,7 @@
         <v>106</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9951</v>
+        <v>4.9849</v>
       </c>
       <c r="N4" t="n">
         <v>219</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3627</v>
+        <v>5.3468</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2348</v>
+        <v>1.2312</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7816</v>
+        <v>1.8299</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3627</v>
+        <v>5.3468</v>
       </c>
       <c r="F5" t="n">
-        <v>2.543</v>
+        <v>2.5897</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6983</v>
+        <v>2.6358</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4962</v>
+        <v>3.2801</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8879</v>
+        <v>1.8417</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6983</v>
+        <v>2.6358</v>
       </c>
       <c r="K5" t="n">
         <v>86</v>
@@ -667,7 +667,7 @@
         <v>98</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5862</v>
+        <v>4.4775</v>
       </c>
       <c r="N5" t="n">
         <v>184</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.136</v>
+        <v>5.0427</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1826</v>
+        <v>1.1612</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6803</v>
+        <v>1.6914</v>
       </c>
       <c r="E6" t="n">
-        <v>5.136</v>
+        <v>5.0427</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3099</v>
+        <v>4.1298</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7509</v>
+        <v>0.8377</v>
       </c>
       <c r="H6" t="n">
-        <v>9.325900000000001</v>
+        <v>9.0625</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0359</v>
+        <v>5.0883</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7509</v>
+        <v>0.8377</v>
       </c>
       <c r="K6" t="n">
         <v>113</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>5.786799999999999</v>
+        <v>5.926</v>
       </c>
       <c r="N6" t="n">
         <v>219</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5159</v>
+        <v>3.3483</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8096</v>
+        <v>0.771</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9567</v>
+        <v>0.9195</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5159</v>
+        <v>3.3483</v>
       </c>
       <c r="F7" t="n">
-        <v>3.851</v>
+        <v>3.6662</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5768</v>
+        <v>-0.5596</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8118</v>
+        <v>7.3219</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2183</v>
+        <v>4.111</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5768</v>
+        <v>-0.5596</v>
       </c>
       <c r="K7" t="n">
         <v>170</v>
@@ -759,7 +759,7 @@
         <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6415</v>
+        <v>3.5514</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4086</v>
+        <v>3.2588</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7849</v>
+        <v>0.7504</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9087</v>
+        <v>0.8788</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4086</v>
+        <v>3.2588</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0038</v>
+        <v>2.9047</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2605</v>
+        <v>0.2098</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0164</v>
+        <v>4.4628</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7088</v>
+        <v>2.5057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2605</v>
+        <v>0.2098</v>
       </c>
       <c r="K8" t="n">
         <v>165</v>
@@ -805,7 +805,7 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9693</v>
+        <v>2.7155</v>
       </c>
       <c r="N8" t="n">
         <v>208</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1799</v>
+        <v>3.0742</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7322</v>
+        <v>0.7079</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8066</v>
+        <v>0.7947</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1799</v>
+        <v>3.0742</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8018</v>
+        <v>3.5958</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3225</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3501</v>
+        <v>7.0574</v>
       </c>
       <c r="I9" t="n">
-        <v>2.349</v>
+        <v>3.9625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3225</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="L9" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6715</v>
+        <v>3.3572</v>
       </c>
       <c r="N9" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0743</v>
+        <v>3.0392</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7079</v>
+        <v>0.6998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7594</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0743</v>
+        <v>3.0392</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6235</v>
+        <v>2.7864</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6329</v>
+        <v>0.1972</v>
       </c>
       <c r="H10" t="n">
-        <v>7.061</v>
+        <v>4.0186</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8129</v>
+        <v>2.2563</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6329</v>
+        <v>0.1972</v>
       </c>
       <c r="K10" t="n">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.18</v>
+        <v>2.4535</v>
       </c>
       <c r="N10" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9973</v>
+        <v>2.9509</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6902</v>
+        <v>0.6795</v>
       </c>
       <c r="D11" t="n">
-        <v>0.725</v>
+        <v>0.7385</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9973</v>
+        <v>2.9509</v>
       </c>
       <c r="F11" t="n">
-        <v>2.713</v>
+        <v>2.7855</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.213</v>
+        <v>3.4333</v>
       </c>
       <c r="I11" t="n">
-        <v>3.213</v>
+        <v>3.4333</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.213</v>
+        <v>3.4333</v>
       </c>
       <c r="N11" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9835</v>
+        <v>2.8805</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6633</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7188</v>
+        <v>0.7064</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9835</v>
+        <v>2.8805</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8181</v>
+        <v>2.5962</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4431</v>
+        <v>2.9996</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4431</v>
+        <v>2.9996</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4431</v>
+        <v>2.9996</v>
       </c>
       <c r="N12" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8128</v>
+        <v>2.8319</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6521</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6843</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8128</v>
+        <v>2.8319</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4096</v>
+        <v>2.4697</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3028</v>
+        <v>0.2618</v>
       </c>
       <c r="H13" t="n">
-        <v>3.056</v>
+        <v>2.8295</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6502</v>
+        <v>1.5887</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3028</v>
+        <v>0.2618</v>
       </c>
       <c r="K13" t="n">
         <v>165</v>
@@ -1035,7 +1035,7 @@
         <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.953</v>
+        <v>1.8505</v>
       </c>
       <c r="N13" t="n">
         <v>208</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6473</v>
+        <v>2.7039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6096</v>
+        <v>0.6226</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5687</v>
+        <v>0.626</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6473</v>
+        <v>2.7039</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9161</v>
+        <v>2.9314</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1555</v>
+        <v>-0.1142</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7271</v>
+        <v>4.5632</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5526</v>
+        <v>2.5621</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1555</v>
+        <v>-0.1142</v>
       </c>
       <c r="K14" t="n">
         <v>86</v>
@@ -1081,7 +1081,7 @@
         <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3971</v>
+        <v>2.4479</v>
       </c>
       <c r="N14" t="n">
         <v>184</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5416</v>
+        <v>2.3877</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5498</v>
       </c>
       <c r="D15" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.3877</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.5215</v>
       </c>
-      <c r="E15" t="n">
-        <v>2.5416</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.6598000000000001</v>
-      </c>
       <c r="G15" t="n">
-        <v>1.9875</v>
+        <v>1.9719</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.5215</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3563</v>
+        <v>0.2928</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9875</v>
+        <v>1.9719</v>
       </c>
       <c r="K15" t="n">
         <v>113</v>
@@ -1127,7 +1127,7 @@
         <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3438</v>
+        <v>2.2647</v>
       </c>
       <c r="N15" t="n">
         <v>219</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4083</v>
+        <v>2.3641</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5545</v>
+        <v>0.5444</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4619</v>
+        <v>0.4712</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4083</v>
+        <v>2.3641</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2472</v>
+        <v>2.2913</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2472</v>
+        <v>2.3009</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2472</v>
+        <v>2.3009</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2472</v>
+        <v>2.3009</v>
       </c>
       <c r="N16" t="n">
         <v>161</v>
@@ -1182,32 +1182,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4059</v>
+        <v>2.3313</v>
       </c>
       <c r="C17" t="n">
-        <v>0.554</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4608</v>
+        <v>0.4562</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4059</v>
+        <v>2.3313</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3331</v>
+        <v>2.1702</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3814</v>
+        <v>2.1702</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3814</v>
+        <v>2.1702</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3814</v>
+        <v>2.1702</v>
       </c>
       <c r="N17" t="n">
         <v>161</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2549</v>
+        <v>2.2845</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5192</v>
+        <v>0.526</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3934</v>
+        <v>0.4349</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2549</v>
+        <v>2.2845</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3593</v>
+        <v>3.0461</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9676</v>
+        <v>-0.7169</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3593</v>
+        <v>4.9939</v>
       </c>
       <c r="I18" t="n">
-        <v>0.734</v>
+        <v>2.8039</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9676</v>
+        <v>-0.7169</v>
       </c>
       <c r="K18" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7016</v>
+        <v>2.087</v>
       </c>
       <c r="N18" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2528</v>
+        <v>2.1329</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5187</v>
+        <v>0.4911</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3925</v>
+        <v>0.3658</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2528</v>
+        <v>2.1329</v>
       </c>
       <c r="F19" t="n">
-        <v>3.04</v>
+        <v>1.274</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7425</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1358</v>
+        <v>1.274</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7733</v>
+        <v>0.7153</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7425</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L19" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0308</v>
+        <v>1.6462</v>
       </c>
       <c r="N19" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6241</v>
+        <v>1.6531</v>
       </c>
       <c r="C20" t="n">
-        <v>0.374</v>
+        <v>0.3807</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1116</v>
+        <v>0.1473</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6241</v>
+        <v>1.6531</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6681</v>
+        <v>2.6927</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9248</v>
+        <v>-0.9204</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9089</v>
+        <v>3.667</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1108</v>
+        <v>2.0589</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9248</v>
+        <v>-0.9204</v>
       </c>
       <c r="K20" t="n">
         <v>170</v>
@@ -1357,7 +1357,7 @@
         <v>35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.186</v>
+        <v>1.1385</v>
       </c>
       <c r="N20" t="n">
         <v>205</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5192</v>
+        <v>1.5652</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3498</v>
+        <v>0.3604</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0648</v>
+        <v>0.1072</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5192</v>
+        <v>1.5652</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3939</v>
+        <v>0.3211</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0955</v>
+        <v>1.2143</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3939</v>
+        <v>0.3211</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2127</v>
+        <v>0.1803</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0955</v>
+        <v>1.2143</v>
       </c>
       <c r="K21" t="n">
         <v>113</v>
@@ -1403,7 +1403,7 @@
         <v>106</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3082</v>
+        <v>1.3946</v>
       </c>
       <c r="N21" t="n">
         <v>219</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4462</v>
+        <v>1.402</v>
       </c>
       <c r="C22" t="n">
-        <v>0.333</v>
+        <v>0.3228</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0322</v>
+        <v>0.0329</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4462</v>
+        <v>1.402</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3767</v>
+        <v>2.41</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.9472</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3767</v>
+        <v>2.6057</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3767</v>
+        <v>1.463</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.9472</v>
       </c>
       <c r="K22" t="n">
         <v>170</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3767</v>
+        <v>0.5158</v>
       </c>
       <c r="N22" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2408</v>
+        <v>1.1907</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2857</v>
+        <v>0.2742</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0596</v>
+        <v>-0.0634</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2408</v>
+        <v>1.1907</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2556</v>
+        <v>1.1212</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.954</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.548</v>
+        <v>1.1212</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3759</v>
+        <v>1.1212</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.954</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>170</v>
       </c>
       <c r="L23" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4218999999999999</v>
+        <v>1.1212</v>
       </c>
       <c r="N23" t="n">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2214</v>
+        <v>1.1461</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2812</v>
+        <v>0.2639</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0682</v>
+        <v>-0.0837</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2214</v>
+        <v>1.1461</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0121</v>
+        <v>1.1873</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0121</v>
+        <v>1.1873</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0121</v>
+        <v>1.1873</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0121</v>
+        <v>1.1873</v>
       </c>
       <c r="N24" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1855</v>
+        <v>1.0717</v>
       </c>
       <c r="C25" t="n">
-        <v>0.273</v>
+        <v>0.2468</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0843</v>
+        <v>-0.1176</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1855</v>
+        <v>1.0717</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2267</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2267</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2267</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2267</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6948</v>
+        <v>0.6833</v>
       </c>
       <c r="C26" t="n">
-        <v>0.16</v>
+        <v>0.1573</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3035</v>
+        <v>-0.2945</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6948</v>
+        <v>0.6833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3788</v>
+        <v>0.3673</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3788</v>
+        <v>0.3673</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3788</v>
+        <v>0.3673</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3788</v>
+        <v>0.3673</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2623</v>
+        <v>0.2844</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0604</v>
+        <v>0.0655</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4967</v>
+        <v>-0.4762</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2623</v>
+        <v>0.2844</v>
       </c>
       <c r="F27" t="n">
-        <v>0.326</v>
+        <v>0.3481</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.326</v>
+        <v>0.3481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.326</v>
+        <v>0.3481</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.326</v>
+        <v>0.3481</v>
       </c>
       <c r="N27" t="n">
         <v>113</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0021</v>
+        <v>0.0074</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6098</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1149</v>
+        <v>0.1379</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1149</v>
+        <v>0.1379</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1149</v>
+        <v>0.1379</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1149</v>
+        <v>0.1379</v>
       </c>
       <c r="N28" t="n">
         <v>161</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0509</v>
+        <v>-0.1187</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0117</v>
+        <v>-0.0273</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.6599</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0509</v>
+        <v>-0.1187</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1765</v>
+        <v>0.1087</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1765</v>
+        <v>0.1087</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1765</v>
+        <v>0.1087</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1765</v>
+        <v>0.1087</v>
       </c>
       <c r="N29" t="n">
         <v>82</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0709</v>
+        <v>-0.1834</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0163</v>
+        <v>-0.0422</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6455</v>
+        <v>-0.6893</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0709</v>
+        <v>-0.1834</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3335</v>
+        <v>-0.0129</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5407</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3335</v>
+        <v>-0.0129</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1801</v>
+        <v>-0.0129</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5407</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3605999999999999</v>
+        <v>-0.0129</v>
       </c>
       <c r="N30" t="n">
-        <v>208</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.2472</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0227</v>
+        <v>-0.0569</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6579</v>
+        <v>-0.7184</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.2472</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2766</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2766</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2766</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2766</v>
       </c>
       <c r="N31" t="n">
         <v>113</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1798</v>
+        <v>-0.2529</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0414</v>
+        <v>-0.0582</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.721</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1798</v>
+        <v>-0.2529</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2092</v>
+        <v>0.0815</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2092</v>
+        <v>0.0815</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2092</v>
+        <v>0.0815</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2092</v>
+        <v>0.0815</v>
       </c>
       <c r="N32" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3083</v>
+        <v>-0.2839</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0654</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.7351</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3083</v>
+        <v>-0.2839</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0261</v>
+        <v>-0.4572</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.4514</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0261</v>
+        <v>-0.4572</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0261</v>
+        <v>-0.2567</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.4514</v>
       </c>
       <c r="K33" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0261</v>
+        <v>0.1947</v>
       </c>
       <c r="N33" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4856</v>
+        <v>-0.5335</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1118</v>
+        <v>-0.1228</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8307</v>
+        <v>-0.8488</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4856</v>
+        <v>-0.5335</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3289</v>
+        <v>-0.3768</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3289</v>
+        <v>-0.3768</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3289</v>
+        <v>-0.3768</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3289</v>
+        <v>-0.3768</v>
       </c>
       <c r="N34" t="n">
         <v>170</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7066</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1627</v>
+        <v>-0.1782</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9294</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7066</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6558</v>
+        <v>-0.7229</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6558</v>
+        <v>-0.7229</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6558</v>
+        <v>-0.7229</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6558</v>
+        <v>-0.7229</v>
       </c>
       <c r="N35" t="n">
         <v>161</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7348</v>
+        <v>-0.8391</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1692</v>
+        <v>-0.1932</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.988</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7348</v>
+        <v>-0.8391</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4537</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4537</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4537</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4537</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>82</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8354</v>
+        <v>-0.9418</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1924</v>
+        <v>-0.2169</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.987</v>
+        <v>-1.0348</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8354</v>
+        <v>-0.9418</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.653</v>
+        <v>-0.7594</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.653</v>
+        <v>-0.7594</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.653</v>
+        <v>-0.7594</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.653</v>
+        <v>-0.7594</v>
       </c>
       <c r="N37" t="n">
         <v>113</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0551</v>
+        <v>-1.0694</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.243</v>
+        <v>-0.2462</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0851</v>
+        <v>-1.093</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0551</v>
+        <v>-1.0694</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.887</v>
+        <v>-0.9013</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.887</v>
+        <v>-0.9013</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.887</v>
+        <v>-0.9013</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.887</v>
+        <v>-0.9013</v>
       </c>
       <c r="N38" t="n">
         <v>82</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5218</v>
+        <v>-1.4796</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3504</v>
+        <v>-0.3407</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2936</v>
+        <v>-1.2798</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5218</v>
+        <v>-1.4796</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3921</v>
+        <v>-1.3499</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3921</v>
+        <v>-1.3499</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3921</v>
+        <v>-1.3499</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3921</v>
+        <v>-1.3499</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3252</v>
+        <v>-2.0978</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5354</v>
+        <v>-0.483</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6524</v>
+        <v>-1.5614</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3252</v>
+        <v>-2.0978</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7304</v>
+        <v>-1.5337</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.589</v>
+        <v>-0.5583</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7304</v>
+        <v>-1.5337</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9344</v>
+        <v>-0.8611</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.589</v>
+        <v>-0.5583</v>
       </c>
       <c r="K40" t="n">
         <v>170</v>
@@ -2277,7 +2277,7 @@
         <v>35</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5234</v>
+        <v>-1.4194</v>
       </c>
       <c r="N40" t="n">
         <v>205</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.9143</v>
+        <v>-3.8001</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9013</v>
+        <v>-0.875</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3623</v>
+        <v>-2.3369</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.9143</v>
+        <v>-3.8001</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.3419</v>
+        <v>-4.2054</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7734</v>
+        <v>0.7511</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.3419</v>
+        <v>-4.2054</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3446</v>
+        <v>-2.3612</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7734</v>
+        <v>0.7511</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5712</v>
+        <v>-1.6101</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -2429,10 +2429,10 @@
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1319</v>
+        <v>1.1128</v>
       </c>
       <c r="J2" t="n">
-        <v>27.1656</v>
+        <v>26.7072</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3676</v>
+        <v>0.3128</v>
       </c>
       <c r="J3" t="n">
-        <v>8.8224</v>
+        <v>7.5072</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1341</v>
+        <v>-0.1152</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.2184</v>
+        <v>-2.7648</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.71</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.337</v>
+        <v>-0.3213</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.087999999999999</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5386</v>
+        <v>-0.5456</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.9264</v>
+        <v>-13.0944</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>17.2632</v>
+        <v>16.488</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6327</v>
+        <v>0.5958</v>
       </c>
       <c r="J8" t="n">
-        <v>15.1848</v>
+        <v>14.2992</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2745</v>
+        <v>0.2386</v>
       </c>
       <c r="J9" t="n">
-        <v>6.588</v>
+        <v>5.7264</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.93</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2745</v>
+        <v>-0.2343</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.588</v>
+        <v>-5.6232</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4097</v>
+        <v>-0.3667</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.832800000000001</v>
+        <v>-8.800800000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2391</v>
+        <v>0.1935</v>
       </c>
       <c r="J12" t="n">
-        <v>5.2602</v>
+        <v>4.257</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1298</v>
+        <v>0.0979</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8556</v>
+        <v>2.1538</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0779</v>
+        <v>0.0553</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7138</v>
+        <v>1.2166</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.88</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1663</v>
+        <v>-0.1464</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.6586</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2493</v>
+        <v>-0.2293</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.4846</v>
+        <v>-5.0446</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2012</v>
+        <v>1.2167</v>
       </c>
       <c r="J17" t="n">
-        <v>26.4264</v>
+        <v>26.7674</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2012</v>
+        <v>1.2167</v>
       </c>
       <c r="J18" t="n">
-        <v>26.4264</v>
+        <v>26.7674</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5471</v>
+        <v>0.512</v>
       </c>
       <c r="J19" t="n">
-        <v>12.0362</v>
+        <v>11.264</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3766</v>
+        <v>-0.3351</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.2852</v>
+        <v>-7.3722</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.756</v>
+        <v>-0.7311</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.632</v>
+        <v>-16.0842</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5659</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>9.6203</v>
+        <v>8.885899999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2959</v>
+        <v>0.2537</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0303</v>
+        <v>4.3129</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.213</v>
+        <v>-0.1965</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.621</v>
+        <v>-3.3405</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.61</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4065</v>
+        <v>-0.3955</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.9105</v>
+        <v>-6.7235</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8058</v>
+        <v>-0.8637</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.6986</v>
+        <v>-14.6829</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5672</v>
+        <v>1.5955</v>
       </c>
       <c r="J27" t="n">
-        <v>26.6424</v>
+        <v>27.1235</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.71</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4487</v>
+        <v>1.4845</v>
       </c>
       <c r="J28" t="n">
-        <v>24.6279</v>
+        <v>25.2365</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1781</v>
+        <v>1.1952</v>
       </c>
       <c r="J29" t="n">
-        <v>20.0277</v>
+        <v>20.3184</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2738</v>
+        <v>0.2413</v>
       </c>
       <c r="J30" t="n">
-        <v>4.6546</v>
+        <v>4.1021</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0704</v>
+        <v>-0.0687</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.1968</v>
+        <v>-1.1679</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7211</v>
+        <v>0.7053</v>
       </c>
       <c r="J32" t="n">
-        <v>15.8642</v>
+        <v>15.5166</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.48</v>
+        <v>0.4545</v>
       </c>
       <c r="J33" t="n">
-        <v>10.56</v>
+        <v>9.999000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2461</v>
+        <v>0.2125</v>
       </c>
       <c r="J34" t="n">
-        <v>5.4142</v>
+        <v>4.675</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1565</v>
+        <v>0.1301</v>
       </c>
       <c r="J35" t="n">
-        <v>3.443</v>
+        <v>2.8622</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4871</v>
+        <v>-0.4451</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.7162</v>
+        <v>-9.792199999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3975</v>
+        <v>0.3421</v>
       </c>
       <c r="J37" t="n">
-        <v>8.744999999999999</v>
+        <v>7.5262</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2456</v>
+        <v>0.1994</v>
       </c>
       <c r="J38" t="n">
-        <v>5.4032</v>
+        <v>4.3868</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0687</v>
+        <v>-0.0562</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5114</v>
+        <v>-1.2364</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1957</v>
+        <v>-0.1755</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.3054</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4229</v>
+        <v>-0.4144</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.303800000000001</v>
+        <v>-9.1168</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7212</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>15.1452</v>
+        <v>14.8281</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6181</v>
       </c>
       <c r="J43" t="n">
-        <v>13.2405</v>
+        <v>12.9801</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.27</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6181</v>
       </c>
       <c r="J44" t="n">
-        <v>13.2405</v>
+        <v>12.9801</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.8354</v>
+        <v>-1.3944</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1654</v>
+        <v>-0.1339</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.4734</v>
+        <v>-2.8119</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.15</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3715</v>
+        <v>0.318</v>
       </c>
       <c r="J47" t="n">
-        <v>7.8015</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1432</v>
+        <v>0.1093</v>
       </c>
       <c r="J48" t="n">
-        <v>3.0072</v>
+        <v>2.2953</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0149</v>
+        <v>0.0104</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3129</v>
+        <v>0.2184</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3196</v>
+        <v>-0.3025</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.7116</v>
+        <v>-6.3525</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.59</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4372</v>
+        <v>-0.4298</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.1812</v>
+        <v>-9.0258</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0184</v>
+        <v>1.0064</v>
       </c>
       <c r="J52" t="n">
-        <v>20.368</v>
+        <v>20.128</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6671</v>
+        <v>0.6552</v>
       </c>
       <c r="J53" t="n">
-        <v>13.342</v>
+        <v>13.104</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5554</v>
       </c>
       <c r="J54" t="n">
-        <v>11.24</v>
+        <v>11.108</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4826</v>
+        <v>0.4649</v>
       </c>
       <c r="J55" t="n">
-        <v>9.651999999999999</v>
+        <v>9.298</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.89</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4116</v>
+        <v>-0.3714</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.231999999999999</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.217</v>
+        <v>0.178</v>
       </c>
       <c r="J57" t="n">
-        <v>4.34</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.884</v>
+        <v>-1.614</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2822</v>
+        <v>-0.2645</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.644</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3287</v>
+        <v>-0.3125</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.574</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.61</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4101</v>
+        <v>-0.3995</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.202</v>
+        <v>-7.99</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.83</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3156</v>
+        <v>1.3198</v>
       </c>
       <c r="J62" t="n">
-        <v>19.734</v>
+        <v>19.797</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.78</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2561</v>
+        <v>1.2572</v>
       </c>
       <c r="J63" t="n">
-        <v>18.8415</v>
+        <v>18.858</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.54</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9634</v>
+        <v>0.957</v>
       </c>
       <c r="J64" t="n">
-        <v>14.451</v>
+        <v>14.355</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.35</v>
       </c>
       <c r="I65" t="n">
-        <v>0.711</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>10.665</v>
+        <v>10.5915</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.18</v>
       </c>
       <c r="I66" t="n">
-        <v>0.448</v>
+        <v>0.422</v>
       </c>
       <c r="J66" t="n">
-        <v>6.72</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7506</v>
+        <v>0.7529</v>
       </c>
       <c r="J67" t="n">
-        <v>11.259</v>
+        <v>11.2935</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.71</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3068</v>
+        <v>-0.2938</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.602</v>
+        <v>-4.407</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.51</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4826</v>
+        <v>-0.4789</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.239</v>
+        <v>-7.1835</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.44</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5477</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.1585</v>
+        <v>-8.2155</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5961</v>
+        <v>-0.6079</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.9415</v>
+        <v>-9.118499999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5458</v>
+        <v>0.605</v>
       </c>
       <c r="J72" t="n">
-        <v>8.186999999999999</v>
+        <v>9.074999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.82</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1939</v>
+        <v>-0.1781</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.9085</v>
+        <v>-2.6715</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.6</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4009</v>
+        <v>-0.3909</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.0135</v>
+        <v>-5.8635</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.38</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.594</v>
+        <v>-0.6052</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.91</v>
+        <v>-9.077999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.25</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7064</v>
+        <v>-0.7392</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.596</v>
+        <v>-11.088</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.29</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2145</v>
+        <v>1.1797</v>
       </c>
       <c r="J77" t="n">
-        <v>18.2175</v>
+        <v>17.6955</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.61</v>
       </c>
       <c r="I78" t="n">
-        <v>0.697</v>
+        <v>0.6276</v>
       </c>
       <c r="J78" t="n">
-        <v>10.455</v>
+        <v>9.414</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4974</v>
+        <v>0.4358</v>
       </c>
       <c r="J79" t="n">
-        <v>7.461</v>
+        <v>6.537</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2133</v>
+        <v>0.1719</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1995</v>
+        <v>2.5785</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0318</v>
+        <v>0.0159</v>
       </c>
       <c r="J81" t="n">
-        <v>0.477</v>
+        <v>0.2385</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.61</v>
       </c>
       <c r="I82" t="n">
-        <v>1.238</v>
+        <v>1.2544</v>
       </c>
       <c r="J82" t="n">
-        <v>23.522</v>
+        <v>23.8336</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9708</v>
+        <v>0.9644</v>
       </c>
       <c r="J83" t="n">
-        <v>18.4452</v>
+        <v>18.3236</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4933</v>
+        <v>0.4613</v>
       </c>
       <c r="J84" t="n">
-        <v>9.3727</v>
+        <v>8.764699999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.06</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J85" t="n">
-        <v>3.5891</v>
+        <v>3.0628</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1586</v>
+        <v>0.1327</v>
       </c>
       <c r="J86" t="n">
-        <v>3.0134</v>
+        <v>2.5213</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7937</v>
+        <v>0.7503</v>
       </c>
       <c r="J87" t="n">
-        <v>15.0803</v>
+        <v>14.2557</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.034</v>
+        <v>-0.0264</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.646</v>
+        <v>-0.5016</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.212</v>
+        <v>-0.1924</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.028</v>
+        <v>-3.6556</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2998</v>
+        <v>-0.2818</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.6962</v>
+        <v>-5.3542</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.5</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5142</v>
+        <v>-0.5164</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.7698</v>
+        <v>-9.8116</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.56</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1741</v>
+        <v>1.1879</v>
       </c>
       <c r="J92" t="n">
-        <v>23.482</v>
+        <v>23.758</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.34</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8226</v>
+        <v>0.8018</v>
       </c>
       <c r="J93" t="n">
-        <v>16.452</v>
+        <v>16.036</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5391</v>
+        <v>0.5075</v>
       </c>
       <c r="J94" t="n">
-        <v>10.782</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3526</v>
+        <v>0.32</v>
       </c>
       <c r="J95" t="n">
-        <v>7.052</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1603</v>
+        <v>0.1344</v>
       </c>
       <c r="J96" t="n">
-        <v>3.206</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4407</v>
+        <v>0.3875</v>
       </c>
       <c r="J97" t="n">
-        <v>8.814</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.84</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1993</v>
+        <v>-0.1806</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.986</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2389</v>
+        <v>-0.2199</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.778</v>
+        <v>-4.398</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.78</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2584</v>
+        <v>-0.2395</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.168</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3431</v>
+        <v>-0.3274</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.862</v>
+        <v>-6.548</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9856</v>
+        <v>0.98</v>
       </c>
       <c r="J102" t="n">
-        <v>22.6688</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.36</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8738</v>
+        <v>0.8545</v>
       </c>
       <c r="J103" t="n">
-        <v>20.0974</v>
+        <v>19.6535</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.19</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5244</v>
+        <v>0.4897</v>
       </c>
       <c r="J104" t="n">
-        <v>12.0612</v>
+        <v>11.2631</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0687</v>
+        <v>0.0525</v>
       </c>
       <c r="J105" t="n">
-        <v>1.5801</v>
+        <v>1.2075</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.98</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1338</v>
+        <v>-0.1066</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.0774</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.485</v>
+        <v>0.4276</v>
       </c>
       <c r="J107" t="n">
-        <v>11.155</v>
+        <v>9.8348</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0081</v>
+        <v>0.0049</v>
       </c>
       <c r="J108" t="n">
-        <v>0.1863</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.99</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.021</v>
+        <v>-0.0156</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.483</v>
+        <v>-0.3588</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.77</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2758</v>
+        <v>-0.2566</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.3434</v>
+        <v>-5.9018</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.7</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.8614</v>
+        <v>-7.5003</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7876</v>
+        <v>0.8851</v>
       </c>
       <c r="J112" t="n">
-        <v>14.1768</v>
+        <v>15.9318</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3149</v>
+        <v>-0.2989</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.6682</v>
+        <v>-5.3802</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.61</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4053</v>
+        <v>-0.3942</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.2954</v>
+        <v>-7.0956</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.53</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.476</v>
+        <v>-0.4718</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.568</v>
+        <v>-8.4924</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5021</v>
+        <v>-0.5012</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.037800000000001</v>
+        <v>-9.021599999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.9</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9696</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>17.4528</v>
+        <v>16.3026</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6879</v>
+        <v>0.6169</v>
       </c>
       <c r="J118" t="n">
-        <v>12.3822</v>
+        <v>11.1042</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.28</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3774</v>
+        <v>0.3217</v>
       </c>
       <c r="J119" t="n">
-        <v>6.7932</v>
+        <v>5.7906</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.26</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3549</v>
+        <v>0.301</v>
       </c>
       <c r="J120" t="n">
-        <v>6.3882</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1285</v>
+        <v>-0.1126</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.313</v>
+        <v>-2.0268</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.33</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8212</v>
+        <v>0.7972</v>
       </c>
       <c r="J122" t="n">
-        <v>17.2452</v>
+        <v>16.7412</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.29</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7399</v>
+        <v>0.7107</v>
       </c>
       <c r="J123" t="n">
-        <v>15.5379</v>
+        <v>14.9247</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5493</v>
+        <v>0.5133</v>
       </c>
       <c r="J124" t="n">
-        <v>11.5353</v>
+        <v>10.7793</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.4149</v>
+        <v>0.3788</v>
       </c>
       <c r="J125" t="n">
-        <v>8.712899999999999</v>
+        <v>7.9548</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4763</v>
+        <v>-0.4354</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.0023</v>
+        <v>-9.1434</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5551</v>
+        <v>0.5009</v>
       </c>
       <c r="J127" t="n">
-        <v>11.6571</v>
+        <v>10.5189</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.19</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4508</v>
+        <v>0.3962</v>
       </c>
       <c r="J128" t="n">
-        <v>9.466799999999999</v>
+        <v>8.3202</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2893</v>
+        <v>-0.271</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.0753</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3362</v>
+        <v>-0.32</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.0602</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5047</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.5987</v>
+        <v>-10.6155</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.87</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1549</v>
+        <v>-0.1394</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.7882</v>
+        <v>-2.5092</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.85</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.177</v>
+        <v>-0.1614</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.186</v>
+        <v>-2.9052</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.229</v>
+        <v>-0.2133</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.122</v>
+        <v>-3.8394</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.229</v>
+        <v>-0.2133</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.122</v>
+        <v>-3.8394</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5858</v>
+        <v>-0.5968</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.5444</v>
+        <v>-10.7424</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.75</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3955</v>
+        <v>1.42</v>
       </c>
       <c r="J137" t="n">
-        <v>25.119</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9878</v>
+        <v>0.988</v>
       </c>
       <c r="J138" t="n">
-        <v>17.7804</v>
+        <v>17.784</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.33</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7903</v>
+        <v>0.7734</v>
       </c>
       <c r="J139" t="n">
-        <v>14.2254</v>
+        <v>13.9212</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6091</v>
+        <v>0.5834</v>
       </c>
       <c r="J140" t="n">
-        <v>10.9638</v>
+        <v>10.5012</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.07</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2015</v>
+        <v>0.1718</v>
       </c>
       <c r="J141" t="n">
-        <v>3.627</v>
+        <v>3.0924</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.38</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7514</v>
+        <v>0.7026</v>
       </c>
       <c r="J142" t="n">
-        <v>17.2822</v>
+        <v>16.1598</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.08</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2297</v>
+        <v>0.1852</v>
       </c>
       <c r="J143" t="n">
-        <v>5.2831</v>
+        <v>4.2596</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2083</v>
+        <v>0.166</v>
       </c>
       <c r="J144" t="n">
-        <v>4.7909</v>
+        <v>3.818</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.54</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4822</v>
+        <v>-0.4803</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.0906</v>
+        <v>-11.0469</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5079</v>
+        <v>-0.5095</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6817</v>
+        <v>-11.7185</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.51</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1202</v>
+        <v>1.1324</v>
       </c>
       <c r="J147" t="n">
-        <v>25.7646</v>
+        <v>26.0452</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7141</v>
+        <v>0.6845</v>
       </c>
       <c r="J148" t="n">
-        <v>16.4243</v>
+        <v>15.7435</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4898</v>
       </c>
       <c r="J149" t="n">
-        <v>12.0681</v>
+        <v>11.2654</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2583</v>
+        <v>0.2272</v>
       </c>
       <c r="J150" t="n">
-        <v>5.9409</v>
+        <v>5.2256</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4047</v>
+        <v>-0.3635</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.3081</v>
+        <v>-8.3605</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.74</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4575</v>
+        <v>1.4955</v>
       </c>
       <c r="J152" t="n">
-        <v>34.98</v>
+        <v>35.892</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.12</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3744</v>
+        <v>0.3355</v>
       </c>
       <c r="J153" t="n">
-        <v>8.9856</v>
+        <v>8.052</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3744</v>
+        <v>0.3355</v>
       </c>
       <c r="J154" t="n">
-        <v>8.9856</v>
+        <v>8.052</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2182</v>
+        <v>-0.1813</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.2368</v>
+        <v>-4.3512</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.134</v>
+        <v>-1.1514</v>
       </c>
       <c r="J156" t="n">
-        <v>-27.216</v>
+        <v>-27.6336</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.18</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4084</v>
+        <v>0.3521</v>
       </c>
       <c r="J157" t="n">
-        <v>9.801600000000001</v>
+        <v>8.4504</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.98</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0408</v>
+        <v>-0.0315</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.9792</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0562</v>
+        <v>-0.0447</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.3488</v>
+        <v>-1.0728</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.0016</v>
+        <v>-1.6488</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.73</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3163</v>
+        <v>-0.2992</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.5912</v>
+        <v>-7.1808</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.49</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0896</v>
+        <v>1.0999</v>
       </c>
       <c r="J162" t="n">
-        <v>22.8816</v>
+        <v>23.0979</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.41</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9659</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>20.2839</v>
+        <v>20.1012</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7522</v>
+        <v>0.7252</v>
       </c>
       <c r="J164" t="n">
-        <v>15.7962</v>
+        <v>15.2292</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.16</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4563</v>
+        <v>0.4218</v>
       </c>
       <c r="J165" t="n">
-        <v>9.5823</v>
+        <v>8.857799999999999</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.929</v>
+        <v>-0.9224</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.509</v>
+        <v>-19.3704</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.09</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2505</v>
+        <v>0.204</v>
       </c>
       <c r="J167" t="n">
-        <v>5.2605</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.05</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1634</v>
+        <v>0.1265</v>
       </c>
       <c r="J168" t="n">
-        <v>3.4314</v>
+        <v>2.6565</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2042</v>
+        <v>-0.1842</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.2882</v>
+        <v>-3.8682</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2144</v>
+        <v>-0.1944</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.5024</v>
+        <v>-4.0824</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.7498</v>
+        <v>-5.3487</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.94</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6124</v>
+        <v>1.6528</v>
       </c>
       <c r="J172" t="n">
-        <v>27.4108</v>
+        <v>28.0976</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.553</v>
+        <v>1.5884</v>
       </c>
       <c r="J173" t="n">
-        <v>26.401</v>
+        <v>27.0028</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.26</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6418</v>
+        <v>0.619</v>
       </c>
       <c r="J174" t="n">
-        <v>10.9106</v>
+        <v>10.523</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.12</v>
       </c>
       <c r="I175" t="n">
-        <v>0.3251</v>
+        <v>0.2925</v>
       </c>
       <c r="J175" t="n">
-        <v>5.5267</v>
+        <v>4.9725</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3041</v>
+        <v>-0.2717</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.1697</v>
+        <v>-4.6189</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>0.91</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1087</v>
+        <v>-0.0939</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.8479</v>
+        <v>-1.5963</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.91</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1087</v>
+        <v>-0.0939</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.8479</v>
+        <v>-1.5963</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.78</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.249</v>
+        <v>-0.2332</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.233</v>
+        <v>-3.9644</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2678</v>
+        <v>-0.252</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.5526</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6173</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.2561</v>
+        <v>-10.4941</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5948</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>17.2492</v>
+        <v>18.0235</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.98</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0416</v>
+        <v>-0.0319</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.2064</v>
+        <v>-0.9251</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.92</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1217</v>
+        <v>-0.1036</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.5293</v>
+        <v>-3.0044</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.82</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2302</v>
+        <v>-0.2098</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.6758</v>
+        <v>-6.0842</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2892</v>
+        <v>-0.2706</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.386799999999999</v>
+        <v>-7.8474</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.92</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0271</v>
+        <v>0.9812</v>
       </c>
       <c r="J187" t="n">
-        <v>29.7859</v>
+        <v>28.4548</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.12</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2006</v>
+        <v>0.1596</v>
       </c>
       <c r="J188" t="n">
-        <v>5.8174</v>
+        <v>4.6284</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1584</v>
+        <v>0.1235</v>
       </c>
       <c r="J189" t="n">
-        <v>4.5936</v>
+        <v>3.5815</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0997</v>
+        <v>-0.0827</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.8913</v>
+        <v>-2.3983</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2957</v>
+        <v>-0.279</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.5753</v>
+        <v>-8.090999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.8</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4449</v>
+        <v>1.4726</v>
       </c>
       <c r="J192" t="n">
-        <v>21.6735</v>
+        <v>22.089</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.67</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2849</v>
+        <v>1.3045</v>
       </c>
       <c r="J193" t="n">
-        <v>19.2735</v>
+        <v>19.5675</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.54</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1202</v>
+        <v>1.1358</v>
       </c>
       <c r="J194" t="n">
-        <v>16.803</v>
+        <v>17.037</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3987</v>
+        <v>0.3669</v>
       </c>
       <c r="J195" t="n">
-        <v>5.9805</v>
+        <v>5.5035</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.98</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1713</v>
+        <v>-0.1487</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.5695</v>
+        <v>-2.2305</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1148</v>
+        <v>-0.0973</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.722</v>
+        <v>-1.4595</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.87</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.0805</v>
+        <v>-1.824</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2668</v>
+        <v>-0.2533</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.002</v>
+        <v>-3.7995</v>
       </c>
     </row>
     <row r="200">
@@ -10389,10 +10389,10 @@
         <v>0.35</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6363</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.307499999999999</v>
+        <v>-9.544499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6389</v>
+        <v>0.5671</v>
       </c>
       <c r="J202" t="n">
-        <v>14.0558</v>
+        <v>12.4762</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.36</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4738</v>
+        <v>0.4079</v>
       </c>
       <c r="J203" t="n">
-        <v>10.4236</v>
+        <v>8.973800000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.25</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3539</v>
+        <v>0.297</v>
       </c>
       <c r="J204" t="n">
-        <v>7.7858</v>
+        <v>6.534</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1806</v>
+        <v>0.1432</v>
       </c>
       <c r="J205" t="n">
-        <v>3.9732</v>
+        <v>3.1504</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.97</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.6896</v>
+        <v>-1.3816</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4709</v>
+        <v>0.4789</v>
       </c>
       <c r="J207" t="n">
-        <v>10.3598</v>
+        <v>10.5358</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3529</v>
+        <v>0.3461</v>
       </c>
       <c r="J208" t="n">
-        <v>7.7638</v>
+        <v>7.6142</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.79</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2563</v>
+        <v>-0.2366</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.6386</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.5196</v>
+        <v>-7.1742</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.7</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.5196</v>
+        <v>-7.1742</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6427</v>
       </c>
       <c r="J212" t="n">
-        <v>15.824</v>
+        <v>14.7821</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2927</v>
+        <v>0.2457</v>
       </c>
       <c r="J213" t="n">
-        <v>6.7321</v>
+        <v>5.6511</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.73</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3043</v>
+        <v>-0.2868</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.9989</v>
+        <v>-6.5964</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4577</v>
+        <v>-0.4521</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.5271</v>
+        <v>-10.3983</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5098</v>
+        <v>-0.5107</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.7254</v>
+        <v>-11.7461</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.34</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8313</v>
+        <v>0.8093</v>
       </c>
       <c r="J217" t="n">
-        <v>19.1199</v>
+        <v>18.6139</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.24</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6284</v>
+        <v>0.5965</v>
       </c>
       <c r="J218" t="n">
-        <v>14.4532</v>
+        <v>13.7195</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.23</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6075</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>13.9725</v>
+        <v>13.2273</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.17</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4786</v>
+        <v>0.4443</v>
       </c>
       <c r="J220" t="n">
-        <v>11.0078</v>
+        <v>10.2189</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1983</v>
+        <v>0.1703</v>
       </c>
       <c r="J221" t="n">
-        <v>4.5609</v>
+        <v>3.9169</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1796</v>
+        <v>0.1472</v>
       </c>
       <c r="J222" t="n">
-        <v>2.8736</v>
+        <v>2.3552</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.91</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1143</v>
+        <v>-0.0998</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.8288</v>
+        <v>-1.5968</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1715</v>
+        <v>-0.1555</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.744</v>
+        <v>-2.488</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.59</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4245</v>
+        <v>-0.4151</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.792</v>
+        <v>-6.6416</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.5</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5034</v>
+        <v>-0.5028</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.054399999999999</v>
+        <v>-8.0448</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.93</v>
       </c>
       <c r="I227" t="n">
-        <v>1.6086</v>
+        <v>1.649</v>
       </c>
       <c r="J227" t="n">
-        <v>25.7376</v>
+        <v>26.384</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.76</v>
       </c>
       <c r="I228" t="n">
-        <v>1.4024</v>
+        <v>1.4273</v>
       </c>
       <c r="J228" t="n">
-        <v>22.4384</v>
+        <v>22.8368</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.65</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2652</v>
+        <v>1.2835</v>
       </c>
       <c r="J229" t="n">
-        <v>20.2432</v>
+        <v>20.536</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5612</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.979200000000001</v>
+        <v>-8.475199999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.79</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6522</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.8304</v>
+        <v>-10.4352</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4513</v>
+        <v>1.4806</v>
       </c>
       <c r="J232" t="n">
-        <v>29.026</v>
+        <v>29.612</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8371</v>
+        <v>0.8186</v>
       </c>
       <c r="J233" t="n">
-        <v>16.742</v>
+        <v>16.372</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.27</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6817</v>
+        <v>0.6555</v>
       </c>
       <c r="J234" t="n">
-        <v>13.634</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.24</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.5923</v>
       </c>
       <c r="J235" t="n">
-        <v>12.41</v>
+        <v>11.846</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6564</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.68</v>
+        <v>-13.128</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.44</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8869</v>
       </c>
       <c r="J237" t="n">
-        <v>18.114</v>
+        <v>17.738</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3365</v>
+        <v>-0.3209</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.73</v>
+        <v>-6.418</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3638</v>
+        <v>-0.3497</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.276</v>
+        <v>-6.994</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.64</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3819</v>
+        <v>-0.369</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.638</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.453</v>
+        <v>-0.4466</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.06</v>
+        <v>-8.932</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.23</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3863</v>
+        <v>0.3823</v>
       </c>
       <c r="J242" t="n">
-        <v>11.2027</v>
+        <v>11.0867</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2913</v>
+        <v>0.2786</v>
       </c>
       <c r="J243" t="n">
-        <v>8.447699999999999</v>
+        <v>8.0794</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.06</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1378</v>
+        <v>0.1208</v>
       </c>
       <c r="J244" t="n">
-        <v>3.9962</v>
+        <v>3.5032</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2883</v>
+        <v>-0.2696</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.3607</v>
+        <v>-7.8184</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4167</v>
+        <v>-0.4079</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.0843</v>
+        <v>-11.8291</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.53</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6705</v>
+        <v>0.5995</v>
       </c>
       <c r="J247" t="n">
-        <v>19.4445</v>
+        <v>17.3855</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.35</v>
       </c>
       <c r="I248" t="n">
-        <v>0.479</v>
+        <v>0.4114</v>
       </c>
       <c r="J248" t="n">
-        <v>13.891</v>
+        <v>11.9306</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0083</v>
+        <v>-0.0061</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.2407</v>
+        <v>-0.1769</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.88</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1795</v>
+        <v>-0.1592</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.2055</v>
+        <v>-4.6168</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2222</v>
+        <v>-0.2022</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.4438</v>
+        <v>-5.8638</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.84</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5131</v>
+        <v>1.5463</v>
       </c>
       <c r="J252" t="n">
-        <v>25.7227</v>
+        <v>26.2871</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.46</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0232</v>
+        <v>1.0273</v>
       </c>
       <c r="J253" t="n">
-        <v>17.3944</v>
+        <v>17.4641</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.25</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6343</v>
+        <v>0.6087</v>
       </c>
       <c r="J254" t="n">
-        <v>10.7831</v>
+        <v>10.3479</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.22</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5708</v>
+        <v>0.5429</v>
       </c>
       <c r="J255" t="n">
-        <v>9.7036</v>
+        <v>9.2293</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3754</v>
+        <v>-0.3383</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.3818</v>
+        <v>-5.7511</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.14</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3867</v>
+        <v>0.3387</v>
       </c>
       <c r="J257" t="n">
-        <v>6.5739</v>
+        <v>5.7579</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0798</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.5861</v>
+        <v>-1.3566</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1954</v>
+        <v>-0.1785</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.3218</v>
+        <v>-3.0345</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.58</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4361</v>
+        <v>-0.4279</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.4137</v>
+        <v>-7.2743</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4799</v>
+        <v>-0.4766</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.158300000000001</v>
+        <v>-8.1022</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.54</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1454</v>
+        <v>1.1584</v>
       </c>
       <c r="J262" t="n">
-        <v>24.0534</v>
+        <v>24.3264</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9708</v>
+        <v>0.9644</v>
       </c>
       <c r="J263" t="n">
-        <v>20.3868</v>
+        <v>20.2524</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8403</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>17.6463</v>
+        <v>17.2431</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.25</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6434</v>
+        <v>0.6149</v>
       </c>
       <c r="J265" t="n">
-        <v>13.5114</v>
+        <v>12.9129</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.76</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7254</v>
+        <v>-0.7004</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.2334</v>
+        <v>-14.7084</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3721</v>
+        <v>0.3186</v>
       </c>
       <c r="J267" t="n">
-        <v>7.8141</v>
+        <v>6.6906</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.07</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2128</v>
+        <v>0.1703</v>
       </c>
       <c r="J268" t="n">
-        <v>4.4688</v>
+        <v>3.5763</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.95</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0791</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.6611</v>
+        <v>-1.3881</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.272</v>
+        <v>-0.2529</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.712</v>
+        <v>-5.3109</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.55</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4719</v>
+        <v>-0.4685</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.9099</v>
+        <v>-9.8385</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.49</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J272" t="n">
-        <v>38.744</v>
+        <v>39.636</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9646</v>
+        <v>0.9651</v>
       </c>
       <c r="J273" t="n">
-        <v>19.292</v>
+        <v>19.302</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.17</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4438</v>
+        <v>0.413</v>
       </c>
       <c r="J274" t="n">
-        <v>8.875999999999999</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3729</v>
+        <v>0.3406</v>
       </c>
       <c r="J275" t="n">
-        <v>7.458</v>
+        <v>6.812</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.97</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2095</v>
+        <v>-0.1834</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.19</v>
+        <v>-3.668</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.595</v>
+        <v>0.5514</v>
       </c>
       <c r="J277" t="n">
-        <v>11.9</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.95</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0645</v>
+        <v>-0.0525</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.29</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.66</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3629</v>
+        <v>-0.3488</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.258</v>
+        <v>-6.976</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.55</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4609</v>
+        <v>-0.4553</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.218</v>
+        <v>-9.106</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4697</v>
+        <v>-0.465</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.394</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.54</v>
       </c>
       <c r="I282" t="n">
-        <v>1.169</v>
+        <v>1.1834</v>
       </c>
       <c r="J282" t="n">
-        <v>33.901</v>
+        <v>34.3186</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.19</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5282</v>
+        <v>0.4916</v>
       </c>
       <c r="J283" t="n">
-        <v>15.3178</v>
+        <v>14.2564</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.18</v>
       </c>
       <c r="I284" t="n">
-        <v>0.506</v>
+        <v>0.4693</v>
       </c>
       <c r="J284" t="n">
-        <v>14.674</v>
+        <v>13.6097</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1274</v>
+        <v>-0.1001</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.6946</v>
+        <v>-2.9029</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.9</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3726</v>
+        <v>-0.3308</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.8054</v>
+        <v>-9.5932</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.12</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3091</v>
+        <v>0.2582</v>
       </c>
       <c r="J287" t="n">
-        <v>8.963900000000001</v>
+        <v>7.4878</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.06</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1854</v>
+        <v>0.1456</v>
       </c>
       <c r="J288" t="n">
-        <v>5.3766</v>
+        <v>4.2224</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.85</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1942</v>
+        <v>-0.1743</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.6318</v>
+        <v>-5.0547</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.8</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2449</v>
+        <v>-0.225</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.1021</v>
+        <v>-6.525</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.77</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2742</v>
+        <v>-0.2551</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.9518</v>
+        <v>-7.3979</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>2.39</v>
       </c>
       <c r="I292" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J292" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2262</v>
+        <v>1.2454</v>
       </c>
       <c r="J293" t="n">
-        <v>22.0716</v>
+        <v>22.4172</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.47</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0221</v>
+        <v>1.0327</v>
       </c>
       <c r="J294" t="n">
-        <v>18.3978</v>
+        <v>18.5886</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.09</v>
       </c>
       <c r="I295" t="n">
-        <v>0.238</v>
+        <v>0.2046</v>
       </c>
       <c r="J295" t="n">
-        <v>4.284</v>
+        <v>3.6828</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.89</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4504</v>
+        <v>-0.4188</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.107200000000001</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.09</v>
       </c>
       <c r="I297" t="n">
-        <v>0.368</v>
+        <v>0.3467</v>
       </c>
       <c r="J297" t="n">
-        <v>6.624</v>
+        <v>6.2406</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0441</v>
+        <v>-0.0249</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.7938</v>
+        <v>-0.4482</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.42</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5624</v>
       </c>
       <c r="J299" t="n">
-        <v>-10.026</v>
+        <v>-10.1232</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.39</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5833</v>
+        <v>-0.5925</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.4994</v>
+        <v>-10.665</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.39</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5833</v>
+        <v>-0.5925</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.4994</v>
+        <v>-10.665</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.59</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2438</v>
+        <v>1.2626</v>
       </c>
       <c r="J302" t="n">
-        <v>29.8512</v>
+        <v>30.3024</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.19</v>
       </c>
       <c r="I303" t="n">
-        <v>0.532</v>
+        <v>0.4942</v>
       </c>
       <c r="J303" t="n">
-        <v>12.768</v>
+        <v>11.8608</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.17</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4869</v>
+        <v>0.4487</v>
       </c>
       <c r="J304" t="n">
-        <v>11.6856</v>
+        <v>10.7688</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2674</v>
+        <v>0.2344</v>
       </c>
       <c r="J305" t="n">
-        <v>6.4176</v>
+        <v>5.6256</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.64</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.9542</v>
       </c>
       <c r="J306" t="n">
-        <v>-23.0208</v>
+        <v>-22.9008</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.66</v>
       </c>
       <c r="I307" t="n">
-        <v>1.092</v>
+        <v>1.0821</v>
       </c>
       <c r="J307" t="n">
-        <v>26.208</v>
+        <v>25.9704</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3984</v>
+        <v>0.3421</v>
       </c>
       <c r="J308" t="n">
-        <v>9.5616</v>
+        <v>8.2104</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.76</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.0032</v>
+        <v>-6.564</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.76</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.0032</v>
+        <v>-6.564</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3844</v>
+        <v>-0.3727</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.2256</v>
+        <v>-8.944800000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0712</v>
+        <v>1.0797</v>
       </c>
       <c r="J312" t="n">
-        <v>29.9936</v>
+        <v>30.2316</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8277</v>
+        <v>0.8061</v>
       </c>
       <c r="J313" t="n">
-        <v>23.1756</v>
+        <v>22.5708</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5642</v>
+        <v>0.5317</v>
       </c>
       <c r="J314" t="n">
-        <v>15.7976</v>
+        <v>14.8876</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.09</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2795</v>
+        <v>0.2481</v>
       </c>
       <c r="J315" t="n">
-        <v>7.826</v>
+        <v>6.9468</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.01</v>
       </c>
       <c r="I316" t="n">
-        <v>0.0217</v>
+        <v>0.0119</v>
       </c>
       <c r="J316" t="n">
-        <v>0.6076</v>
+        <v>0.3332</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.14</v>
       </c>
       <c r="I317" t="n">
-        <v>0.354</v>
+        <v>0.3013</v>
       </c>
       <c r="J317" t="n">
-        <v>9.912000000000001</v>
+        <v>8.436400000000001</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.09</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2557</v>
+        <v>0.2092</v>
       </c>
       <c r="J318" t="n">
-        <v>7.1596</v>
+        <v>5.8576</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.96</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0536</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.8228</v>
+        <v>-1.5008</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2327</v>
+        <v>-0.2129</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.5156</v>
+        <v>-5.9612</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5317</v>
+        <v>-0.5365</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.8876</v>
+        <v>-15.022</v>
       </c>
     </row>
   </sheetData>
